--- a/LAPORAN 1 MARET.xlsx
+++ b/LAPORAN 1 MARET.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="11028"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\stefa\Downloads\simple-dashboard\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/stefanusjason/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C7885CA-47B3-48A8-9B25-764EC600FF9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11CB25D7-EE24-BE47-84DF-D2572C5AC070}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16280" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Table 1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="46">
   <si>
     <r>
       <rPr>
@@ -324,6 +324,145 @@
   <si>
     <t>Table Number</t>
   </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Table 12</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Table 8</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Table 9</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Table VIP</t>
+    </r>
+  </si>
+  <si>
+    <t>HAPPY HOUR WEEKEND</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>DLHH</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>HAPPY HOUR WEEKD</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>REGAN</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>TIKA</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>WEEKDAY NORMAL</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>HAMB</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>FARID</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>RYAN</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>VIP WEEKDAY NORM</t>
+    </r>
+  </si>
+  <si>
+    <t>VIP HAPPY HOUR WEE</t>
+  </si>
+  <si>
+    <t>FARID</t>
+  </si>
 </sst>
 </file>
 
@@ -332,27 +471,12 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="h:mm:ss;@"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Times New Roman"/>
       <charset val="204"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Times New Roman"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <name val="Times New Roman"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Times New Roman"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -364,6 +488,12 @@
       <sz val="10"/>
       <name val="Times New Roman"/>
       <family val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -427,7 +557,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -447,6 +577,9 @@
       <alignment horizontal="center" vertical="top" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -464,11 +597,29 @@
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" indent="1" shrinkToFit="1"/>
     </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" indent="2" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" indent="3" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" indent="2" shrinkToFit="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
@@ -487,12 +638,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="2"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -861,37 +1006,37 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L42"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:L97"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="17.33203125" customWidth="1"/>
-    <col min="2" max="2" width="20.5" customWidth="1"/>
-    <col min="3" max="3" width="19.83203125" customWidth="1"/>
-    <col min="4" max="4" width="3.33203125" customWidth="1"/>
-    <col min="5" max="5" width="7.5" customWidth="1"/>
-    <col min="6" max="6" width="26.6640625" customWidth="1"/>
-    <col min="7" max="7" width="16.1640625" customWidth="1"/>
-    <col min="8" max="8" width="13.5" customWidth="1"/>
-    <col min="9" max="10" width="12.1640625" customWidth="1"/>
-    <col min="11" max="11" width="12.6640625" customWidth="1"/>
-    <col min="12" max="12" width="16.83203125" customWidth="1"/>
-    <col min="13" max="13" width="3.5" customWidth="1"/>
+    <col min="1" max="1" width="17.3984375" customWidth="1"/>
+    <col min="2" max="2" width="20.3984375" customWidth="1"/>
+    <col min="3" max="3" width="13.19921875" customWidth="1"/>
+    <col min="4" max="4" width="3.3984375" customWidth="1"/>
+    <col min="5" max="5" width="7.59765625" customWidth="1"/>
+    <col min="6" max="6" width="26.59765625" customWidth="1"/>
+    <col min="7" max="7" width="16.19921875" customWidth="1"/>
+    <col min="8" max="8" width="13.59765625" customWidth="1"/>
+    <col min="9" max="10" width="12.19921875" customWidth="1"/>
+    <col min="11" max="11" width="12.59765625" customWidth="1"/>
+    <col min="12" max="12" width="16.796875" customWidth="1"/>
+    <col min="13" max="13" width="3.59765625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:12" ht="19.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="21" t="s">
+      <c r="C1" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="D1" s="18" t="s">
+      <c r="D1" s="25" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="19"/>
+      <c r="E1" s="26"/>
       <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
@@ -914,1416 +1059,3304 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="5">
         <v>202603012864</v>
       </c>
-      <c r="B2" s="20">
+      <c r="B2" s="13">
         <v>46082</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="12"/>
-      <c r="E2" s="13"/>
-      <c r="F2" s="6" t="s">
+      <c r="D2" s="17"/>
+      <c r="E2" s="18"/>
+      <c r="F2" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="G2" s="7">
+      <c r="G2" s="8">
         <v>0.53524300000000002</v>
       </c>
-      <c r="H2" s="8">
+      <c r="H2" s="9">
         <v>0.57691000000000003</v>
       </c>
-      <c r="I2" s="9">
+      <c r="I2" s="10">
         <v>35000</v>
       </c>
-      <c r="J2" s="10">
+      <c r="J2" s="11">
         <v>0</v>
       </c>
-      <c r="K2" s="9">
+      <c r="K2" s="10">
         <v>35000</v>
       </c>
-      <c r="L2" s="9">
+      <c r="L2" s="10">
         <v>35000</v>
       </c>
     </row>
-    <row r="3" spans="1:12" ht="18.2" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:12" ht="18.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="5">
         <v>202603012865</v>
       </c>
-      <c r="B3" s="20">
+      <c r="B3" s="13">
         <v>46082</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="D3" s="12"/>
-      <c r="E3" s="13"/>
-      <c r="F3" s="6" t="s">
+      <c r="D3" s="17"/>
+      <c r="E3" s="18"/>
+      <c r="F3" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="G3" s="7">
+      <c r="G3" s="8">
         <v>0.53669</v>
       </c>
-      <c r="H3" s="8">
+      <c r="H3" s="9">
         <v>0.64537</v>
       </c>
-      <c r="I3" s="9">
+      <c r="I3" s="10">
         <v>90948</v>
       </c>
-      <c r="J3" s="10">
+      <c r="J3" s="11">
         <v>0</v>
       </c>
-      <c r="K3" s="9">
+      <c r="K3" s="10">
         <v>90948</v>
       </c>
-      <c r="L3" s="9">
+      <c r="L3" s="10">
         <v>91000</v>
       </c>
     </row>
-    <row r="4" spans="1:12" ht="18.2" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:12" ht="18.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="5">
         <v>202603012866</v>
       </c>
-      <c r="B4" s="20">
+      <c r="B4" s="13">
         <v>46082</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="C4" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="D4" s="12"/>
-      <c r="E4" s="13"/>
-      <c r="F4" s="6" t="s">
+      <c r="D4" s="17"/>
+      <c r="E4" s="18"/>
+      <c r="F4" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="G4" s="7">
+      <c r="G4" s="8">
         <v>0.54925900000000005</v>
       </c>
-      <c r="H4" s="8">
+      <c r="H4" s="9">
         <v>0.67425900000000005</v>
       </c>
-      <c r="I4" s="9">
+      <c r="I4" s="10">
         <v>105000</v>
       </c>
-      <c r="J4" s="10">
+      <c r="J4" s="11">
         <v>0</v>
       </c>
-      <c r="K4" s="9">
+      <c r="K4" s="10">
         <v>105000</v>
       </c>
-      <c r="L4" s="9">
+      <c r="L4" s="10">
         <v>105000</v>
       </c>
     </row>
-    <row r="5" spans="1:12" ht="18.2" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:12" ht="18.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="5">
         <v>202603012867</v>
       </c>
-      <c r="B5" s="20">
+      <c r="B5" s="13">
         <v>46082</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="D5" s="12"/>
-      <c r="E5" s="13"/>
-      <c r="F5" s="6" t="s">
+      <c r="D5" s="17"/>
+      <c r="E5" s="18"/>
+      <c r="F5" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="G5" s="7">
+      <c r="G5" s="8">
         <v>0.57822899999999999</v>
       </c>
-      <c r="H5" s="8">
+      <c r="H5" s="9">
         <v>0.619896</v>
       </c>
-      <c r="I5" s="9">
+      <c r="I5" s="10">
         <v>35000</v>
       </c>
-      <c r="J5" s="10">
+      <c r="J5" s="11">
         <v>0</v>
       </c>
-      <c r="K5" s="9">
+      <c r="K5" s="10">
         <v>35000</v>
       </c>
-      <c r="L5" s="9">
+      <c r="L5" s="10">
         <v>35000</v>
       </c>
     </row>
-    <row r="6" spans="1:12" ht="18.2" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:12" ht="18.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="5">
         <v>202603012868</v>
       </c>
-      <c r="B6" s="20">
+      <c r="B6" s="13">
         <v>46082</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="C6" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="D6" s="12"/>
-      <c r="E6" s="13"/>
-      <c r="F6" s="6" t="s">
+      <c r="D6" s="17"/>
+      <c r="E6" s="18"/>
+      <c r="F6" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="G6" s="7">
+      <c r="G6" s="8">
         <v>0.57835599999999998</v>
       </c>
-      <c r="H6" s="8">
+      <c r="H6" s="9">
         <v>0.65639999999999998</v>
       </c>
-      <c r="I6" s="9">
+      <c r="I6" s="10">
         <v>65296</v>
       </c>
-      <c r="J6" s="9">
+      <c r="J6" s="10">
         <v>5000</v>
       </c>
-      <c r="K6" s="9">
+      <c r="K6" s="10">
         <v>70296</v>
       </c>
-      <c r="L6" s="9">
+      <c r="L6" s="10">
         <v>70500</v>
       </c>
     </row>
-    <row r="7" spans="1:12" ht="18.2" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:12" ht="18.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="5">
         <v>202603012869</v>
       </c>
-      <c r="B7" s="20">
+      <c r="B7" s="13">
         <v>46082</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="C7" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="D7" s="12"/>
-      <c r="E7" s="13"/>
-      <c r="F7" s="6" t="s">
+      <c r="D7" s="17"/>
+      <c r="E7" s="18"/>
+      <c r="F7" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="G7" s="7">
+      <c r="G7" s="8">
         <v>0.59758100000000003</v>
       </c>
-      <c r="H7" s="8">
+      <c r="H7" s="9">
         <v>0.63924800000000004</v>
       </c>
-      <c r="I7" s="9">
+      <c r="I7" s="10">
         <v>35000</v>
       </c>
-      <c r="J7" s="10">
+      <c r="J7" s="11">
         <v>0</v>
       </c>
-      <c r="K7" s="9">
+      <c r="K7" s="10">
         <v>35000</v>
       </c>
-      <c r="L7" s="9">
+      <c r="L7" s="10">
         <v>35000</v>
       </c>
     </row>
-    <row r="8" spans="1:12" ht="18.2" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:12" ht="18.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="5">
         <v>202603012870</v>
       </c>
-      <c r="B8" s="20">
+      <c r="B8" s="13">
         <v>46082</v>
       </c>
-      <c r="C8" s="6" t="s">
+      <c r="C8" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="D8" s="12"/>
-      <c r="E8" s="13"/>
-      <c r="F8" s="6" t="s">
+      <c r="D8" s="17"/>
+      <c r="E8" s="18"/>
+      <c r="F8" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="G8" s="7">
+      <c r="G8" s="8">
         <v>0.60011599999999998</v>
       </c>
-      <c r="H8" s="8">
+      <c r="H8" s="9">
         <v>0.66472200000000004</v>
       </c>
-      <c r="I8" s="9">
+      <c r="I8" s="10">
         <v>54219</v>
       </c>
-      <c r="J8" s="9">
+      <c r="J8" s="10">
         <v>5000</v>
       </c>
-      <c r="K8" s="9">
+      <c r="K8" s="10">
         <v>59219</v>
       </c>
-      <c r="L8" s="9">
+      <c r="L8" s="10">
         <v>59500</v>
       </c>
     </row>
-    <row r="9" spans="1:12" ht="18.2" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:12" ht="18.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="5">
         <v>202603012871</v>
       </c>
-      <c r="B9" s="20">
+      <c r="B9" s="13">
         <v>46082</v>
       </c>
-      <c r="C9" s="6" t="s">
+      <c r="C9" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="D9" s="12"/>
-      <c r="E9" s="13"/>
-      <c r="F9" s="6" t="s">
+      <c r="D9" s="17"/>
+      <c r="E9" s="18"/>
+      <c r="F9" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="G9" s="7">
+      <c r="G9" s="8">
         <v>0.63158599999999998</v>
       </c>
-      <c r="H9" s="8">
+      <c r="H9" s="9">
         <v>0.71251200000000003</v>
       </c>
-      <c r="I9" s="9">
+      <c r="I9" s="10">
         <v>67628</v>
       </c>
-      <c r="J9" s="9">
+      <c r="J9" s="10">
         <v>40000</v>
       </c>
-      <c r="K9" s="9">
+      <c r="K9" s="10">
         <v>107628</v>
       </c>
-      <c r="L9" s="9">
+      <c r="L9" s="10">
         <v>108000</v>
       </c>
     </row>
-    <row r="10" spans="1:12" ht="18.2" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:12" ht="18.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="5">
         <v>202603012872</v>
       </c>
-      <c r="B10" s="20">
+      <c r="B10" s="13">
         <v>46082</v>
       </c>
-      <c r="C10" s="6" t="s">
+      <c r="C10" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="D10" s="12"/>
-      <c r="E10" s="13"/>
-      <c r="F10" s="6" t="s">
+      <c r="D10" s="17"/>
+      <c r="E10" s="18"/>
+      <c r="F10" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="G10" s="7">
+      <c r="G10" s="8">
         <v>0.63957200000000003</v>
       </c>
-      <c r="H10" s="8">
+      <c r="H10" s="9">
         <v>0.68123800000000001</v>
       </c>
-      <c r="I10" s="9">
+      <c r="I10" s="10">
         <v>35000</v>
       </c>
-      <c r="J10" s="9">
+      <c r="J10" s="10">
         <v>20000</v>
       </c>
-      <c r="K10" s="9">
+      <c r="K10" s="10">
         <v>55000</v>
       </c>
-      <c r="L10" s="9">
+      <c r="L10" s="10">
         <v>55000</v>
       </c>
     </row>
-    <row r="11" spans="1:12" ht="18.2" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:12" ht="18.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="5">
         <v>202603012873</v>
       </c>
-      <c r="B11" s="20">
+      <c r="B11" s="13">
         <v>46082</v>
       </c>
-      <c r="C11" s="6" t="s">
+      <c r="C11" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="D11" s="12"/>
-      <c r="E11" s="13"/>
-      <c r="F11" s="6" t="s">
+      <c r="D11" s="17"/>
+      <c r="E11" s="18"/>
+      <c r="F11" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="G11" s="7">
+      <c r="G11" s="8">
         <v>0.64502300000000001</v>
       </c>
-      <c r="H11" s="8">
+      <c r="H11" s="9">
         <v>0.83153900000000003</v>
       </c>
-      <c r="I11" s="9">
+      <c r="I11" s="10">
         <v>156244</v>
       </c>
-      <c r="J11" s="9">
+      <c r="J11" s="10">
         <v>5000</v>
       </c>
-      <c r="K11" s="9">
+      <c r="K11" s="10">
         <v>161244</v>
       </c>
-      <c r="L11" s="9">
+      <c r="L11" s="10">
         <v>161500</v>
       </c>
     </row>
-    <row r="12" spans="1:12" ht="18.2" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:12" ht="18.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="5">
         <v>202603012874</v>
       </c>
-      <c r="B12" s="20">
+      <c r="B12" s="13">
         <v>46082</v>
       </c>
-      <c r="C12" s="6" t="s">
+      <c r="C12" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="D12" s="12"/>
-      <c r="E12" s="13"/>
-      <c r="F12" s="6" t="s">
+      <c r="D12" s="17"/>
+      <c r="E12" s="18"/>
+      <c r="F12" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="G12" s="7">
+      <c r="G12" s="8">
         <v>0.66379600000000005</v>
       </c>
-      <c r="H12" s="8">
+      <c r="H12" s="9">
         <v>0.76167799999999997</v>
       </c>
-      <c r="I12" s="9">
+      <c r="I12" s="10">
         <v>81620</v>
       </c>
-      <c r="J12" s="9">
+      <c r="J12" s="10">
         <v>35000</v>
       </c>
-      <c r="K12" s="9">
+      <c r="K12" s="10">
         <v>116620</v>
       </c>
-      <c r="L12" s="9">
+      <c r="L12" s="10">
         <v>117000</v>
       </c>
     </row>
-    <row r="13" spans="1:12" ht="18.2" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:12" ht="18.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="5">
         <v>202603012875</v>
       </c>
-      <c r="B13" s="20">
+      <c r="B13" s="13">
         <v>46082</v>
       </c>
-      <c r="C13" s="6" t="s">
+      <c r="C13" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="D13" s="12"/>
-      <c r="E13" s="13"/>
-      <c r="F13" s="6" t="s">
+      <c r="D13" s="17"/>
+      <c r="E13" s="18"/>
+      <c r="F13" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="G13" s="7">
+      <c r="G13" s="8">
         <v>0.66718699999999997</v>
       </c>
-      <c r="H13" s="8">
+      <c r="H13" s="9">
         <v>0.70885399999999998</v>
       </c>
-      <c r="I13" s="9">
+      <c r="I13" s="10">
         <v>45000</v>
       </c>
-      <c r="J13" s="10">
+      <c r="J13" s="11">
         <v>0</v>
       </c>
-      <c r="K13" s="9">
+      <c r="K13" s="10">
         <v>45000</v>
       </c>
-      <c r="L13" s="9">
+      <c r="L13" s="10">
         <v>45000</v>
       </c>
     </row>
-    <row r="14" spans="1:12" ht="18.2" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:12" ht="18.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="5">
         <v>202603012876</v>
       </c>
-      <c r="B14" s="20">
+      <c r="B14" s="13">
         <v>46082</v>
       </c>
-      <c r="C14" s="6" t="s">
+      <c r="C14" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="D14" s="12"/>
-      <c r="E14" s="13"/>
-      <c r="F14" s="6" t="s">
+      <c r="D14" s="17"/>
+      <c r="E14" s="18"/>
+      <c r="F14" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="G14" s="7">
+      <c r="G14" s="8">
         <v>0.67262699999999997</v>
       </c>
-      <c r="H14" s="8">
+      <c r="H14" s="9">
         <v>0.74916700000000003</v>
       </c>
-      <c r="I14" s="9">
+      <c r="I14" s="10">
         <v>82500</v>
       </c>
-      <c r="J14" s="10">
+      <c r="J14" s="11">
         <v>0</v>
       </c>
-      <c r="K14" s="9">
+      <c r="K14" s="10">
         <v>82500</v>
       </c>
-      <c r="L14" s="9">
+      <c r="L14" s="10">
         <v>82500</v>
       </c>
     </row>
-    <row r="15" spans="1:12" ht="18.2" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:12" ht="18.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="5">
         <v>202603012877</v>
       </c>
-      <c r="B15" s="20">
+      <c r="B15" s="13">
         <v>46082</v>
       </c>
-      <c r="C15" s="6" t="s">
+      <c r="C15" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="D15" s="16" t="s">
+      <c r="D15" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="E15" s="17"/>
-      <c r="F15" s="6" t="s">
+      <c r="E15" s="24"/>
+      <c r="F15" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="G15" s="7">
+      <c r="G15" s="8">
         <v>0.67906200000000005</v>
       </c>
-      <c r="H15" s="8">
+      <c r="H15" s="9">
         <v>0.75284700000000004</v>
       </c>
-      <c r="I15" s="9">
+      <c r="I15" s="10">
         <v>71550</v>
       </c>
-      <c r="J15" s="10">
+      <c r="J15" s="11">
         <v>0</v>
       </c>
-      <c r="K15" s="9">
+      <c r="K15" s="10">
         <v>71550</v>
       </c>
-      <c r="L15" s="9">
+      <c r="L15" s="10">
         <v>72000</v>
       </c>
     </row>
-    <row r="16" spans="1:12" ht="18.2" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:12" ht="18.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="5">
         <v>202603012878</v>
       </c>
-      <c r="B16" s="20">
+      <c r="B16" s="13">
         <v>46082</v>
       </c>
-      <c r="C16" s="6" t="s">
+      <c r="C16" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="D16" s="16" t="s">
+      <c r="D16" s="23" t="s">
         <v>22</v>
       </c>
-      <c r="E16" s="17"/>
-      <c r="F16" s="6" t="s">
+      <c r="E16" s="24"/>
+      <c r="F16" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="G16" s="7">
+      <c r="G16" s="8">
         <v>0.68286999999999998</v>
       </c>
-      <c r="H16" s="8">
+      <c r="H16" s="9">
         <v>0.80718699999999999</v>
       </c>
-      <c r="I16" s="9">
+      <c r="I16" s="10">
         <v>120825</v>
       </c>
-      <c r="J16" s="10">
+      <c r="J16" s="11">
         <v>0</v>
       </c>
-      <c r="K16" s="9">
+      <c r="K16" s="10">
         <v>120825</v>
       </c>
-      <c r="L16" s="9">
+      <c r="L16" s="10">
         <v>121000</v>
       </c>
     </row>
-    <row r="17" spans="1:12" ht="18.2" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:12" ht="18.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A17" s="5">
         <v>202603012879</v>
       </c>
-      <c r="B17" s="20">
+      <c r="B17" s="13">
         <v>46082</v>
       </c>
-      <c r="C17" s="6" t="s">
+      <c r="C17" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="D17" s="12"/>
-      <c r="E17" s="13"/>
-      <c r="F17" s="6" t="s">
+      <c r="D17" s="17"/>
+      <c r="E17" s="18"/>
+      <c r="F17" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="G17" s="7">
+      <c r="G17" s="8">
         <v>0.78545100000000001</v>
       </c>
-      <c r="H17" s="8">
+      <c r="H17" s="9">
         <v>0.93947899999999995</v>
       </c>
-      <c r="I17" s="9">
+      <c r="I17" s="10">
         <v>165750</v>
       </c>
-      <c r="J17" s="9">
+      <c r="J17" s="10">
         <v>70000</v>
       </c>
-      <c r="K17" s="9">
+      <c r="K17" s="10">
         <v>235750</v>
       </c>
-      <c r="L17" s="9">
+      <c r="L17" s="10">
         <v>236000</v>
       </c>
     </row>
-    <row r="18" spans="1:12" ht="18.2" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:12" ht="18.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="5">
         <v>202603012880</v>
       </c>
-      <c r="B18" s="20">
+      <c r="B18" s="13">
         <v>46082</v>
       </c>
-      <c r="C18" s="6" t="s">
+      <c r="C18" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="D18" s="12"/>
-      <c r="E18" s="13"/>
-      <c r="F18" s="6" t="s">
+      <c r="D18" s="17"/>
+      <c r="E18" s="18"/>
+      <c r="F18" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="G18" s="7">
+      <c r="G18" s="8">
         <v>0.80120400000000003</v>
       </c>
-      <c r="H18" s="8">
+      <c r="H18" s="9">
         <v>0.88453700000000002</v>
       </c>
-      <c r="I18" s="9">
+      <c r="I18" s="10">
         <v>90000</v>
       </c>
-      <c r="J18" s="9">
+      <c r="J18" s="10">
         <v>36000</v>
       </c>
-      <c r="K18" s="9">
+      <c r="K18" s="10">
         <v>126000</v>
       </c>
-      <c r="L18" s="9">
+      <c r="L18" s="10">
         <v>126000</v>
       </c>
     </row>
-    <row r="19" spans="1:12" ht="18.2" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:12" ht="18.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A19" s="5">
         <v>202603012881</v>
       </c>
-      <c r="B19" s="20">
+      <c r="B19" s="13">
         <v>46082</v>
       </c>
-      <c r="C19" s="6" t="s">
+      <c r="C19" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="D19" s="12"/>
-      <c r="E19" s="13"/>
-      <c r="F19" s="6" t="s">
+      <c r="D19" s="17"/>
+      <c r="E19" s="18"/>
+      <c r="F19" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="G19" s="7">
+      <c r="G19" s="8">
         <v>0.807361</v>
       </c>
-      <c r="H19" s="8">
+      <c r="H19" s="9">
         <v>0.89278900000000005</v>
       </c>
-      <c r="I19" s="9">
+      <c r="I19" s="10">
         <v>92250</v>
       </c>
-      <c r="J19" s="9">
+      <c r="J19" s="10">
         <v>10000</v>
       </c>
-      <c r="K19" s="9">
+      <c r="K19" s="10">
         <v>102250</v>
       </c>
-      <c r="L19" s="9">
+      <c r="L19" s="10">
         <v>102500</v>
       </c>
     </row>
-    <row r="20" spans="1:12" ht="18.2" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:12" ht="18.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A20" s="5">
         <v>202603012882</v>
       </c>
-      <c r="B20" s="20">
+      <c r="B20" s="13">
         <v>46082</v>
       </c>
-      <c r="C20" s="6" t="s">
+      <c r="C20" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="12"/>
-      <c r="E20" s="13"/>
-      <c r="F20" s="6" t="s">
+      <c r="D20" s="17"/>
+      <c r="E20" s="18"/>
+      <c r="F20" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="G20" s="7">
+      <c r="G20" s="8">
         <v>0.8075</v>
       </c>
-      <c r="H20" s="8">
+      <c r="H20" s="9">
         <v>0.89267399999999997</v>
       </c>
-      <c r="I20" s="9">
+      <c r="I20" s="10">
         <v>91500</v>
       </c>
-      <c r="J20" s="9">
+      <c r="J20" s="10">
         <v>28000</v>
       </c>
-      <c r="K20" s="9">
+      <c r="K20" s="10">
         <v>119500</v>
       </c>
-      <c r="L20" s="9">
+      <c r="L20" s="10">
         <v>119500</v>
       </c>
     </row>
-    <row r="21" spans="1:12" ht="18.2" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:12" ht="18.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A21" s="5">
         <v>202603012883</v>
       </c>
-      <c r="B21" s="20">
+      <c r="B21" s="13">
         <v>46082</v>
       </c>
-      <c r="C21" s="6" t="s">
+      <c r="C21" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="D21" s="16" t="s">
+      <c r="D21" s="23" t="s">
         <v>24</v>
       </c>
-      <c r="E21" s="17"/>
-      <c r="F21" s="6" t="s">
+      <c r="E21" s="24"/>
+      <c r="F21" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="G21" s="7">
+      <c r="G21" s="8">
         <v>0.80957199999999996</v>
       </c>
-      <c r="H21" s="8">
+      <c r="H21" s="9">
         <v>0.875162</v>
       </c>
-      <c r="I21" s="9">
+      <c r="I21" s="10">
         <v>63450</v>
       </c>
-      <c r="J21" s="10">
+      <c r="J21" s="11">
         <v>0</v>
       </c>
-      <c r="K21" s="9">
+      <c r="K21" s="10">
         <v>63450</v>
       </c>
-      <c r="L21" s="9">
+      <c r="L21" s="10">
         <v>63500</v>
       </c>
     </row>
-    <row r="22" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A22" s="5">
         <v>202603012884</v>
       </c>
-      <c r="B22" s="20">
+      <c r="B22" s="13">
         <v>46082</v>
       </c>
-      <c r="C22" s="6" t="s">
+      <c r="C22" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="D22" s="12"/>
-      <c r="E22" s="13"/>
-      <c r="F22" s="6" t="s">
+      <c r="D22" s="17"/>
+      <c r="E22" s="18"/>
+      <c r="F22" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="G22" s="7">
+      <c r="G22" s="8">
         <v>0.81082200000000004</v>
       </c>
-      <c r="H22" s="11">
+      <c r="H22" s="12">
         <v>0.89415500000000003</v>
       </c>
-      <c r="I22" s="9">
+      <c r="I22" s="10">
         <v>90000</v>
       </c>
-      <c r="J22" s="9">
+      <c r="J22" s="10">
         <v>30000</v>
       </c>
-      <c r="K22" s="9">
+      <c r="K22" s="10">
         <v>120000</v>
       </c>
-      <c r="L22" s="9">
+      <c r="L22" s="10">
         <v>120000</v>
       </c>
     </row>
-    <row r="23" spans="1:12" ht="18.2" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:12" ht="18.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A23" s="5">
         <v>202603012885</v>
       </c>
-      <c r="B23" s="20">
+      <c r="B23" s="13">
         <v>46082</v>
       </c>
-      <c r="C23" s="6" t="s">
+      <c r="C23" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="D23" s="12"/>
-      <c r="E23" s="13"/>
-      <c r="F23" s="6" t="s">
+      <c r="D23" s="17"/>
+      <c r="E23" s="18"/>
+      <c r="F23" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="G23" s="7">
+      <c r="G23" s="8">
         <v>0.81592600000000004</v>
       </c>
-      <c r="H23" s="11">
+      <c r="H23" s="12">
         <v>0.90855300000000006</v>
       </c>
-      <c r="I23" s="9">
+      <c r="I23" s="10">
         <v>99750</v>
       </c>
-      <c r="J23" s="9">
+      <c r="J23" s="10">
         <v>16000</v>
       </c>
-      <c r="K23" s="9">
+      <c r="K23" s="10">
         <v>115750</v>
       </c>
-      <c r="L23" s="9">
+      <c r="L23" s="10">
         <v>116000</v>
       </c>
     </row>
-    <row r="24" spans="1:12" ht="18.2" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:12" ht="18.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A24" s="5">
         <v>202603012886</v>
       </c>
-      <c r="B24" s="20">
+      <c r="B24" s="13">
         <v>46082</v>
       </c>
-      <c r="C24" s="6" t="s">
+      <c r="C24" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="D24" s="12"/>
-      <c r="E24" s="13"/>
-      <c r="F24" s="6" t="s">
+      <c r="D24" s="17"/>
+      <c r="E24" s="18"/>
+      <c r="F24" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="G24" s="7">
+      <c r="G24" s="8">
         <v>0.83721100000000004</v>
       </c>
-      <c r="H24" s="11">
+      <c r="H24" s="12">
         <v>0.87887700000000002</v>
       </c>
-      <c r="I24" s="9">
+      <c r="I24" s="10">
         <v>45000</v>
       </c>
-      <c r="J24" s="10">
+      <c r="J24" s="11">
         <v>0</v>
       </c>
-      <c r="K24" s="9">
+      <c r="K24" s="10">
         <v>45000</v>
       </c>
-      <c r="L24" s="9">
+      <c r="L24" s="10">
         <v>45000</v>
       </c>
     </row>
-    <row r="25" spans="1:12" ht="18.2" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:12" ht="18.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A25" s="5">
         <v>202603012887</v>
       </c>
-      <c r="B25" s="20">
+      <c r="B25" s="13">
         <v>46082</v>
       </c>
-      <c r="C25" s="6" t="s">
+      <c r="C25" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="D25" s="12"/>
-      <c r="E25" s="13"/>
-      <c r="F25" s="6" t="s">
+      <c r="D25" s="17"/>
+      <c r="E25" s="18"/>
+      <c r="F25" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="G25" s="7">
+      <c r="G25" s="8">
         <v>0.83736100000000002</v>
       </c>
-      <c r="H25" s="11">
+      <c r="H25" s="12">
         <v>0.87902800000000003</v>
       </c>
-      <c r="I25" s="9">
+      <c r="I25" s="10">
         <v>45000</v>
       </c>
-      <c r="J25" s="10">
+      <c r="J25" s="11">
         <v>0</v>
       </c>
-      <c r="K25" s="9">
+      <c r="K25" s="10">
         <v>45000</v>
       </c>
-      <c r="L25" s="9">
+      <c r="L25" s="10">
         <v>45000</v>
       </c>
     </row>
-    <row r="26" spans="1:12" ht="18.2" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:12" ht="18.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A26" s="5">
         <v>202603012888</v>
       </c>
-      <c r="B26" s="20">
+      <c r="B26" s="13">
         <v>46082</v>
       </c>
-      <c r="C26" s="6" t="s">
+      <c r="C26" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="D26" s="14" t="s">
+      <c r="D26" s="21" t="s">
         <v>26</v>
       </c>
-      <c r="E26" s="15"/>
-      <c r="F26" s="6" t="s">
+      <c r="E26" s="22"/>
+      <c r="F26" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="G26" s="7">
+      <c r="G26" s="8">
         <v>0.84181700000000004</v>
       </c>
-      <c r="H26" s="11">
+      <c r="H26" s="12">
         <v>0.94203700000000001</v>
       </c>
-      <c r="I26" s="9">
+      <c r="I26" s="10">
         <v>97200</v>
       </c>
-      <c r="J26" s="9">
+      <c r="J26" s="10">
         <v>25000</v>
       </c>
-      <c r="K26" s="9">
+      <c r="K26" s="10">
         <v>122200</v>
       </c>
-      <c r="L26" s="9">
+      <c r="L26" s="10">
         <v>122500</v>
       </c>
     </row>
-    <row r="27" spans="1:12" ht="18.2" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:12" ht="18.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A27" s="5">
         <v>202603012889</v>
       </c>
-      <c r="B27" s="20">
+      <c r="B27" s="13">
         <v>46082</v>
       </c>
-      <c r="C27" s="6" t="s">
+      <c r="C27" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="D27" s="12"/>
-      <c r="E27" s="13"/>
-      <c r="F27" s="6" t="s">
+      <c r="D27" s="17"/>
+      <c r="E27" s="18"/>
+      <c r="F27" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="G27" s="7">
+      <c r="G27" s="8">
         <v>0.84920099999999998</v>
       </c>
-      <c r="H27" s="11">
+      <c r="H27" s="12">
         <v>0.932535</v>
       </c>
-      <c r="I27" s="9">
+      <c r="I27" s="10">
         <v>90000</v>
       </c>
-      <c r="J27" s="9">
+      <c r="J27" s="10">
         <v>20000</v>
       </c>
-      <c r="K27" s="9">
+      <c r="K27" s="10">
         <v>110000</v>
       </c>
-      <c r="L27" s="9">
+      <c r="L27" s="10">
         <v>110000</v>
       </c>
     </row>
-    <row r="28" spans="1:12" ht="18.2" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:12" ht="18.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="5">
         <v>202603012890</v>
       </c>
-      <c r="B28" s="20">
+      <c r="B28" s="13">
         <v>46082</v>
       </c>
-      <c r="C28" s="6" t="s">
+      <c r="C28" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="D28" s="12"/>
-      <c r="E28" s="13"/>
-      <c r="F28" s="6" t="s">
+      <c r="D28" s="17"/>
+      <c r="E28" s="18"/>
+      <c r="F28" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="G28" s="7">
+      <c r="G28" s="8">
         <v>0.87590299999999999</v>
       </c>
-      <c r="H28" s="11">
+      <c r="H28" s="12">
         <v>0.97043999999999997</v>
       </c>
-      <c r="I28" s="9">
+      <c r="I28" s="10">
         <v>102000</v>
       </c>
-      <c r="J28" s="10">
+      <c r="J28" s="11">
         <v>0</v>
       </c>
-      <c r="K28" s="9">
+      <c r="K28" s="10">
         <v>102000</v>
       </c>
-      <c r="L28" s="9">
+      <c r="L28" s="10">
         <v>102000</v>
       </c>
     </row>
-    <row r="29" spans="1:12" ht="18.2" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:12" ht="18.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A29" s="5">
         <v>202603012891</v>
       </c>
-      <c r="B29" s="20">
-        <v>46083</v>
-      </c>
-      <c r="C29" s="6" t="s">
+      <c r="B29" s="13">
+        <v>46083</v>
+      </c>
+      <c r="C29" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="D29" s="12"/>
-      <c r="E29" s="13"/>
-      <c r="F29" s="6" t="s">
+      <c r="D29" s="17"/>
+      <c r="E29" s="18"/>
+      <c r="F29" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="G29" s="7">
+      <c r="G29" s="8">
         <v>0.88721099999999997</v>
       </c>
-      <c r="H29" s="11">
+      <c r="H29" s="12">
         <v>2.6088E-2</v>
       </c>
-      <c r="I29" s="9">
+      <c r="I29" s="10">
         <v>149250</v>
       </c>
-      <c r="J29" s="10">
+      <c r="J29" s="11">
         <v>0</v>
       </c>
-      <c r="K29" s="9">
+      <c r="K29" s="10">
         <v>149250</v>
       </c>
-      <c r="L29" s="9">
+      <c r="L29" s="10">
         <v>149500</v>
       </c>
     </row>
-    <row r="30" spans="1:12" ht="18.2" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:12" ht="18.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A30" s="5">
         <v>202603012892</v>
       </c>
-      <c r="B30" s="20">
-        <v>46083</v>
-      </c>
-      <c r="C30" s="6" t="s">
+      <c r="B30" s="13">
+        <v>46083</v>
+      </c>
+      <c r="C30" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="D30" s="14" t="s">
+      <c r="D30" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="E30" s="15"/>
-      <c r="F30" s="6" t="s">
+      <c r="E30" s="22"/>
+      <c r="F30" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="G30" s="7">
+      <c r="G30" s="8">
         <v>0.89483800000000002</v>
       </c>
-      <c r="H30" s="11">
+      <c r="H30" s="12">
         <v>4.2025E-2</v>
       </c>
-      <c r="I30" s="9">
+      <c r="I30" s="10">
         <v>142425</v>
       </c>
-      <c r="J30" s="9">
+      <c r="J30" s="10">
         <v>46000</v>
       </c>
-      <c r="K30" s="9">
+      <c r="K30" s="10">
         <v>188425</v>
       </c>
-      <c r="L30" s="9">
+      <c r="L30" s="10">
         <v>188500</v>
       </c>
     </row>
-    <row r="31" spans="1:12" ht="18.2" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:12" ht="18.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A31" s="5">
         <v>202603012893</v>
       </c>
-      <c r="B31" s="20">
-        <v>46083</v>
-      </c>
-      <c r="C31" s="6" t="s">
+      <c r="B31" s="13">
+        <v>46083</v>
+      </c>
+      <c r="C31" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="D31" s="14" t="s">
+      <c r="D31" s="21" t="s">
         <v>28</v>
       </c>
-      <c r="E31" s="15"/>
-      <c r="F31" s="6" t="s">
+      <c r="E31" s="22"/>
+      <c r="F31" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="G31" s="7">
+      <c r="G31" s="8">
         <v>0.89491900000000002</v>
       </c>
-      <c r="H31" s="11">
+      <c r="H31" s="12">
         <v>4.0903000000000002E-2</v>
       </c>
-      <c r="I31" s="9">
+      <c r="I31" s="10">
         <v>141750</v>
       </c>
-      <c r="J31" s="9">
+      <c r="J31" s="10">
         <v>20000</v>
       </c>
-      <c r="K31" s="9">
+      <c r="K31" s="10">
         <v>161750</v>
       </c>
-      <c r="L31" s="9">
+      <c r="L31" s="10">
         <v>162000</v>
       </c>
     </row>
-    <row r="32" spans="1:12" ht="18.2" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:12" ht="18.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="5">
         <v>202603012894</v>
       </c>
-      <c r="B32" s="20">
-        <v>46083</v>
-      </c>
-      <c r="C32" s="6" t="s">
+      <c r="B32" s="13">
+        <v>46083</v>
+      </c>
+      <c r="C32" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="D32" s="14" t="s">
+      <c r="D32" s="21" t="s">
         <v>22</v>
       </c>
-      <c r="E32" s="15"/>
-      <c r="F32" s="6" t="s">
+      <c r="E32" s="22"/>
+      <c r="F32" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="G32" s="7">
+      <c r="G32" s="8">
         <v>0.89501200000000003</v>
       </c>
-      <c r="H32" s="11">
+      <c r="H32" s="12">
         <v>4.1944000000000002E-2</v>
       </c>
-      <c r="I32" s="9">
+      <c r="I32" s="10">
         <v>142425</v>
       </c>
-      <c r="J32" s="9">
+      <c r="J32" s="10">
         <v>60000</v>
       </c>
-      <c r="K32" s="9">
+      <c r="K32" s="10">
         <v>202425</v>
       </c>
-      <c r="L32" s="9">
+      <c r="L32" s="10">
         <v>202500</v>
       </c>
     </row>
-    <row r="33" spans="1:12" ht="18.2" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:12" ht="18.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A33" s="5">
         <v>202603012895</v>
       </c>
-      <c r="B33" s="20">
-        <v>46083</v>
-      </c>
-      <c r="C33" s="6" t="s">
+      <c r="B33" s="13">
+        <v>46083</v>
+      </c>
+      <c r="C33" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="D33" s="12"/>
-      <c r="E33" s="13"/>
-      <c r="F33" s="6" t="s">
+      <c r="D33" s="17"/>
+      <c r="E33" s="18"/>
+      <c r="F33" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="G33" s="7">
+      <c r="G33" s="8">
         <v>0.90634300000000001</v>
       </c>
-      <c r="H33" s="11">
+      <c r="H33" s="12">
         <v>0.94800899999999999</v>
       </c>
-      <c r="I33" s="9">
+      <c r="I33" s="10">
         <v>45000</v>
       </c>
-      <c r="J33" s="9">
+      <c r="J33" s="10">
         <v>5000</v>
       </c>
-      <c r="K33" s="9">
+      <c r="K33" s="10">
         <v>50000</v>
       </c>
-      <c r="L33" s="9">
+      <c r="L33" s="10">
         <v>50000</v>
       </c>
     </row>
-    <row r="34" spans="1:12" ht="18.2" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:12" ht="18.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A34" s="5">
         <v>202603012896</v>
       </c>
-      <c r="B34" s="20">
-        <v>46083</v>
-      </c>
-      <c r="C34" s="6" t="s">
+      <c r="B34" s="13">
+        <v>46083</v>
+      </c>
+      <c r="C34" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="D34" s="12"/>
-      <c r="E34" s="13"/>
-      <c r="F34" s="6" t="s">
+      <c r="D34" s="17"/>
+      <c r="E34" s="18"/>
+      <c r="F34" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="G34" s="7">
+      <c r="G34" s="8">
         <v>0.91400499999999996</v>
       </c>
-      <c r="H34" s="11">
+      <c r="H34" s="12">
         <v>0.98011599999999999</v>
       </c>
-      <c r="I34" s="9">
+      <c r="I34" s="10">
         <v>71250</v>
       </c>
-      <c r="J34" s="9">
+      <c r="J34" s="10">
         <v>32000</v>
       </c>
-      <c r="K34" s="9">
+      <c r="K34" s="10">
         <v>103250</v>
       </c>
-      <c r="L34" s="9">
+      <c r="L34" s="10">
         <v>103500</v>
       </c>
     </row>
-    <row r="35" spans="1:12" ht="18.2" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:12" ht="18.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A35" s="5">
         <v>202603012897</v>
       </c>
-      <c r="B35" s="20">
-        <v>46083</v>
-      </c>
-      <c r="C35" s="6" t="s">
+      <c r="B35" s="13">
+        <v>46083</v>
+      </c>
+      <c r="C35" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="D35" s="12"/>
-      <c r="E35" s="13"/>
-      <c r="F35" s="6" t="s">
+      <c r="D35" s="17"/>
+      <c r="E35" s="18"/>
+      <c r="F35" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="G35" s="7">
+      <c r="G35" s="8">
         <v>0.93620400000000004</v>
       </c>
-      <c r="H35" s="11">
+      <c r="H35" s="12">
         <v>4.2049000000000003E-2</v>
       </c>
-      <c r="I35" s="9">
+      <c r="I35" s="10">
         <v>114000</v>
       </c>
-      <c r="J35" s="9">
+      <c r="J35" s="10">
         <v>23000</v>
       </c>
-      <c r="K35" s="9">
+      <c r="K35" s="10">
         <v>137000</v>
       </c>
-      <c r="L35" s="9">
+      <c r="L35" s="10">
         <v>137000</v>
       </c>
     </row>
-    <row r="36" spans="1:12" ht="18.2" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:12" ht="18.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A36" s="5">
         <v>202603012898</v>
       </c>
-      <c r="B36" s="20">
-        <v>46083</v>
-      </c>
-      <c r="C36" s="6" t="s">
+      <c r="B36" s="13">
+        <v>46083</v>
+      </c>
+      <c r="C36" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="D36" s="12"/>
-      <c r="E36" s="13"/>
-      <c r="F36" s="6" t="s">
+      <c r="D36" s="17"/>
+      <c r="E36" s="18"/>
+      <c r="F36" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="G36" s="7">
+      <c r="G36" s="8">
         <v>0.95109999999999995</v>
       </c>
-      <c r="H36" s="11">
+      <c r="H36" s="12">
         <v>3.4432999999999998E-2</v>
       </c>
-      <c r="I36" s="9">
+      <c r="I36" s="10">
         <v>90000</v>
       </c>
-      <c r="J36" s="9">
+      <c r="J36" s="10">
         <v>20000</v>
       </c>
-      <c r="K36" s="9">
+      <c r="K36" s="10">
         <v>110000</v>
       </c>
-      <c r="L36" s="9">
+      <c r="L36" s="10">
         <v>110000</v>
       </c>
     </row>
-    <row r="37" spans="1:12" ht="18.2" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:12" ht="18.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A37" s="5">
         <v>202603012899</v>
       </c>
-      <c r="B37" s="20">
-        <v>46083</v>
-      </c>
-      <c r="C37" s="6" t="s">
+      <c r="B37" s="13">
+        <v>46083</v>
+      </c>
+      <c r="C37" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="D37" s="12"/>
-      <c r="E37" s="13"/>
-      <c r="F37" s="6" t="s">
+      <c r="D37" s="17"/>
+      <c r="E37" s="18"/>
+      <c r="F37" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="G37" s="7">
+      <c r="G37" s="8">
         <v>0.95123800000000003</v>
       </c>
-      <c r="H37" s="11">
+      <c r="H37" s="12">
         <v>4.1991000000000001E-2</v>
       </c>
-      <c r="I37" s="9">
+      <c r="I37" s="10">
         <v>97500</v>
       </c>
-      <c r="J37" s="9">
+      <c r="J37" s="10">
         <v>25000</v>
       </c>
-      <c r="K37" s="9">
+      <c r="K37" s="10">
         <v>122500</v>
       </c>
-      <c r="L37" s="9">
+      <c r="L37" s="10">
         <v>122500</v>
       </c>
     </row>
-    <row r="38" spans="1:12" ht="18.2" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:12" ht="18.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A38" s="5">
         <v>202603012900</v>
       </c>
-      <c r="B38" s="20">
-        <v>46083</v>
-      </c>
-      <c r="C38" s="6" t="s">
+      <c r="B38" s="13">
+        <v>46083</v>
+      </c>
+      <c r="C38" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="D38" s="12"/>
-      <c r="E38" s="13"/>
-      <c r="F38" s="6" t="s">
+      <c r="D38" s="17"/>
+      <c r="E38" s="18"/>
+      <c r="F38" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="G38" s="7">
+      <c r="G38" s="8">
         <v>0.95736100000000002</v>
       </c>
-      <c r="H38" s="11">
+      <c r="H38" s="12">
         <v>4.2014000000000003E-2</v>
       </c>
-      <c r="I38" s="9">
+      <c r="I38" s="10">
         <v>90750</v>
       </c>
-      <c r="J38" s="9">
+      <c r="J38" s="10">
         <v>20000</v>
       </c>
-      <c r="K38" s="9">
+      <c r="K38" s="10">
         <v>110750</v>
       </c>
-      <c r="L38" s="9">
+      <c r="L38" s="10">
         <v>111000</v>
       </c>
     </row>
-    <row r="39" spans="1:12" ht="18.2" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:12" ht="18.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A39" s="5">
         <v>202603012901</v>
       </c>
-      <c r="B39" s="20">
-        <v>46083</v>
-      </c>
-      <c r="C39" s="6" t="s">
+      <c r="B39" s="13">
+        <v>46083</v>
+      </c>
+      <c r="C39" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="D39" s="12"/>
-      <c r="E39" s="13"/>
-      <c r="F39" s="6" t="s">
+      <c r="D39" s="17"/>
+      <c r="E39" s="18"/>
+      <c r="F39" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="G39" s="7">
+      <c r="G39" s="8">
         <v>0.97253500000000004</v>
       </c>
-      <c r="H39" s="11">
+      <c r="H39" s="12">
         <v>1.3079999999999999E-3</v>
       </c>
-      <c r="I39" s="9">
+      <c r="I39" s="10">
         <v>45000</v>
       </c>
-      <c r="J39" s="10">
+      <c r="J39" s="11">
         <v>0</v>
       </c>
-      <c r="K39" s="9">
+      <c r="K39" s="10">
         <v>45000</v>
       </c>
-      <c r="L39" s="9">
+      <c r="L39" s="10">
         <v>45000</v>
       </c>
     </row>
-    <row r="40" spans="1:12" ht="18.2" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:12" ht="18.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A40" s="5">
         <v>202603012902</v>
       </c>
-      <c r="B40" s="20">
-        <v>46083</v>
-      </c>
-      <c r="C40" s="6" t="s">
+      <c r="B40" s="13">
+        <v>46083</v>
+      </c>
+      <c r="C40" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="D40" s="12"/>
-      <c r="E40" s="13"/>
-      <c r="F40" s="6" t="s">
+      <c r="D40" s="17"/>
+      <c r="E40" s="18"/>
+      <c r="F40" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="G40" s="7">
+      <c r="G40" s="8">
         <v>0.97442099999999998</v>
       </c>
-      <c r="H40" s="11">
+      <c r="H40" s="12">
         <v>4.1967999999999998E-2</v>
       </c>
-      <c r="I40" s="9">
+      <c r="I40" s="10">
         <v>72750</v>
       </c>
-      <c r="J40" s="9">
+      <c r="J40" s="10">
         <v>20000</v>
       </c>
-      <c r="K40" s="9">
+      <c r="K40" s="10">
         <v>92750</v>
       </c>
-      <c r="L40" s="9">
+      <c r="L40" s="10">
         <v>93000</v>
       </c>
     </row>
-    <row r="41" spans="1:12" ht="18.2" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:12" ht="18.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A41" s="5">
         <v>202603012903</v>
       </c>
-      <c r="B41" s="20">
-        <v>46083</v>
-      </c>
-      <c r="C41" s="6" t="s">
+      <c r="B41" s="13">
+        <v>46083</v>
+      </c>
+      <c r="C41" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="D41" s="12"/>
-      <c r="E41" s="13"/>
-      <c r="F41" s="6" t="s">
+      <c r="D41" s="17"/>
+      <c r="E41" s="18"/>
+      <c r="F41" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="G41" s="7">
+      <c r="G41" s="8">
         <v>0.984259</v>
       </c>
-      <c r="H41" s="11">
+      <c r="H41" s="12">
         <v>2.5926000000000001E-2</v>
       </c>
-      <c r="I41" s="9">
+      <c r="I41" s="10">
         <v>45000</v>
       </c>
-      <c r="J41" s="10">
+      <c r="J41" s="11">
         <v>0</v>
       </c>
-      <c r="K41" s="9">
+      <c r="K41" s="10">
         <v>45000</v>
       </c>
-      <c r="L41" s="9">
+      <c r="L41" s="10">
         <v>45000</v>
       </c>
     </row>
-    <row r="42" spans="1:12" ht="18.2" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:12" ht="18.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A42" s="5">
         <v>202603022904</v>
       </c>
-      <c r="B42" s="20">
-        <v>46083</v>
-      </c>
-      <c r="C42" s="6" t="s">
+      <c r="B42" s="13">
+        <v>46083</v>
+      </c>
+      <c r="C42" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="D42" s="12"/>
-      <c r="E42" s="13"/>
-      <c r="F42" s="6" t="s">
+      <c r="D42" s="17"/>
+      <c r="E42" s="18"/>
+      <c r="F42" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="G42" s="7">
+      <c r="G42" s="8">
         <v>1.2881999999999999E-2</v>
       </c>
-      <c r="H42" s="11">
+      <c r="H42" s="12">
         <v>4.2071999999999998E-2</v>
       </c>
-      <c r="I42" s="9">
+      <c r="I42" s="10">
         <v>45000</v>
       </c>
-      <c r="J42" s="10">
+      <c r="J42" s="11">
         <v>0</v>
       </c>
-      <c r="K42" s="9">
+      <c r="K42" s="10">
         <v>45000</v>
       </c>
-      <c r="L42" s="9">
+      <c r="L42" s="10">
         <v>45000</v>
       </c>
     </row>
+    <row r="43" spans="1:12" ht="14" x14ac:dyDescent="0.15">
+      <c r="A43" s="14">
+        <v>20260301843</v>
+      </c>
+      <c r="B43" s="13">
+        <v>46082</v>
+      </c>
+      <c r="C43" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="D43" s="17"/>
+      <c r="E43" s="18"/>
+      <c r="F43" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="G43" s="15">
+        <v>0.63826400000000005</v>
+      </c>
+      <c r="H43" s="8">
+        <v>0.697546</v>
+      </c>
+      <c r="I43" s="10">
+        <v>49555</v>
+      </c>
+      <c r="J43" s="11">
+        <v>0</v>
+      </c>
+      <c r="K43" s="10">
+        <v>49555</v>
+      </c>
+      <c r="L43" s="16">
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="44" spans="1:12" ht="14" x14ac:dyDescent="0.15">
+      <c r="A44" s="14">
+        <v>20260301844</v>
+      </c>
+      <c r="B44" s="13">
+        <v>46082</v>
+      </c>
+      <c r="C44" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="D44" s="17"/>
+      <c r="E44" s="18"/>
+      <c r="F44" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="G44" s="15">
+        <v>0.67366899999999996</v>
+      </c>
+      <c r="H44" s="8">
+        <v>0.83510399999999996</v>
+      </c>
+      <c r="I44" s="10">
+        <v>174000</v>
+      </c>
+      <c r="J44" s="10">
+        <v>62000</v>
+      </c>
+      <c r="K44" s="10">
+        <v>236000</v>
+      </c>
+      <c r="L44" s="16">
+        <v>236000</v>
+      </c>
+    </row>
+    <row r="45" spans="1:12" ht="14" x14ac:dyDescent="0.15">
+      <c r="A45" s="14">
+        <v>20260301845</v>
+      </c>
+      <c r="B45" s="13">
+        <v>46082</v>
+      </c>
+      <c r="C45" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="D45" s="17"/>
+      <c r="E45" s="18"/>
+      <c r="F45" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="G45" s="15">
+        <v>0.693519</v>
+      </c>
+      <c r="H45" s="8">
+        <v>0.74922500000000003</v>
+      </c>
+      <c r="I45" s="10">
+        <v>60000</v>
+      </c>
+      <c r="J45" s="11">
+        <v>0</v>
+      </c>
+      <c r="K45" s="10">
+        <v>60000</v>
+      </c>
+      <c r="L45" s="16">
+        <v>60000</v>
+      </c>
+    </row>
+    <row r="46" spans="1:12" ht="14" x14ac:dyDescent="0.15">
+      <c r="A46" s="14">
+        <v>20260301846</v>
+      </c>
+      <c r="B46" s="13">
+        <v>46082</v>
+      </c>
+      <c r="C46" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="D46" s="17"/>
+      <c r="E46" s="18"/>
+      <c r="F46" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="G46" s="15">
+        <v>0.72903899999999999</v>
+      </c>
+      <c r="H46" s="8">
+        <v>0.770706</v>
+      </c>
+      <c r="I46" s="10">
+        <v>45000</v>
+      </c>
+      <c r="J46" s="11">
+        <v>0</v>
+      </c>
+      <c r="K46" s="10">
+        <v>45000</v>
+      </c>
+      <c r="L46" s="16">
+        <v>45000</v>
+      </c>
+    </row>
+    <row r="47" spans="1:12" ht="14" x14ac:dyDescent="0.15">
+      <c r="A47" s="14">
+        <v>20260301847</v>
+      </c>
+      <c r="B47" s="13">
+        <v>46082</v>
+      </c>
+      <c r="C47" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="D47" s="17"/>
+      <c r="E47" s="18"/>
+      <c r="F47" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="G47" s="15">
+        <v>0.80446799999999996</v>
+      </c>
+      <c r="H47" s="8">
+        <v>0.88780099999999995</v>
+      </c>
+      <c r="I47" s="10">
+        <v>90000</v>
+      </c>
+      <c r="J47" s="10">
+        <v>15000</v>
+      </c>
+      <c r="K47" s="10">
+        <v>105000</v>
+      </c>
+      <c r="L47" s="16">
+        <v>105000</v>
+      </c>
+    </row>
+    <row r="48" spans="1:12" ht="14" x14ac:dyDescent="0.15">
+      <c r="A48" s="14">
+        <v>20260301848</v>
+      </c>
+      <c r="B48" s="13">
+        <v>46082</v>
+      </c>
+      <c r="C48" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="D48" s="17"/>
+      <c r="E48" s="18"/>
+      <c r="F48" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="G48" s="15">
+        <v>0.81403899999999996</v>
+      </c>
+      <c r="H48" s="8">
+        <v>0.89737299999999998</v>
+      </c>
+      <c r="I48" s="10">
+        <v>90000</v>
+      </c>
+      <c r="J48" s="10">
+        <v>34000</v>
+      </c>
+      <c r="K48" s="10">
+        <v>124000</v>
+      </c>
+      <c r="L48" s="16">
+        <v>124000</v>
+      </c>
+    </row>
+    <row r="49" spans="1:12" ht="14" x14ac:dyDescent="0.15">
+      <c r="A49" s="14">
+        <v>20260301849</v>
+      </c>
+      <c r="B49" s="13">
+        <v>46082</v>
+      </c>
+      <c r="C49" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="D49" s="17"/>
+      <c r="E49" s="18"/>
+      <c r="F49" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="G49" s="15">
+        <v>0.838785</v>
+      </c>
+      <c r="H49" s="8">
+        <v>0.99857600000000002</v>
+      </c>
+      <c r="I49" s="10">
+        <v>172500</v>
+      </c>
+      <c r="J49" s="10">
+        <v>35000</v>
+      </c>
+      <c r="K49" s="10">
+        <v>207500</v>
+      </c>
+      <c r="L49" s="16">
+        <v>207500</v>
+      </c>
+    </row>
+    <row r="50" spans="1:12" ht="14" x14ac:dyDescent="0.15">
+      <c r="A50" s="14">
+        <v>20260301850</v>
+      </c>
+      <c r="B50" s="13">
+        <v>46083</v>
+      </c>
+      <c r="C50" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="D50" s="17"/>
+      <c r="E50" s="18"/>
+      <c r="F50" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="G50" s="15">
+        <v>0.84087999999999996</v>
+      </c>
+      <c r="H50" s="8">
+        <v>3.0173999999999999E-2</v>
+      </c>
+      <c r="I50" s="10">
+        <v>204000</v>
+      </c>
+      <c r="J50" s="10">
+        <v>66000</v>
+      </c>
+      <c r="K50" s="10">
+        <v>270000</v>
+      </c>
+      <c r="L50" s="16">
+        <v>270000</v>
+      </c>
+    </row>
+    <row r="51" spans="1:12" ht="14" x14ac:dyDescent="0.15">
+      <c r="A51" s="14">
+        <v>20260301851</v>
+      </c>
+      <c r="B51" s="13">
+        <v>46082</v>
+      </c>
+      <c r="C51" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="D51" s="17"/>
+      <c r="E51" s="18"/>
+      <c r="F51" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="G51" s="15">
+        <v>0.86985000000000001</v>
+      </c>
+      <c r="H51" s="8">
+        <v>0.953183</v>
+      </c>
+      <c r="I51" s="10">
+        <v>90000</v>
+      </c>
+      <c r="J51" s="11">
+        <v>0</v>
+      </c>
+      <c r="K51" s="10">
+        <v>90000</v>
+      </c>
+      <c r="L51" s="16">
+        <v>90000</v>
+      </c>
+    </row>
+    <row r="52" spans="1:12" ht="14" x14ac:dyDescent="0.15">
+      <c r="A52" s="14">
+        <v>20260301852</v>
+      </c>
+      <c r="B52" s="13">
+        <v>46083</v>
+      </c>
+      <c r="C52" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="D52" s="17"/>
+      <c r="E52" s="18"/>
+      <c r="F52" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="G52" s="15">
+        <v>0.91068300000000002</v>
+      </c>
+      <c r="H52" s="8">
+        <v>3.2835999999999997E-2</v>
+      </c>
+      <c r="I52" s="10">
+        <v>131250</v>
+      </c>
+      <c r="J52" s="10">
+        <v>18000</v>
+      </c>
+      <c r="K52" s="10">
+        <v>149250</v>
+      </c>
+      <c r="L52" s="16">
+        <v>149500</v>
+      </c>
+    </row>
+    <row r="53" spans="1:12" ht="14" x14ac:dyDescent="0.15">
+      <c r="A53" s="14">
+        <v>20260301853</v>
+      </c>
+      <c r="B53" s="13">
+        <v>46083</v>
+      </c>
+      <c r="C53" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="D53" s="17"/>
+      <c r="E53" s="18"/>
+      <c r="F53" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="G53" s="15">
+        <v>0.96832200000000002</v>
+      </c>
+      <c r="H53" s="8">
+        <v>5.1655E-2</v>
+      </c>
+      <c r="I53" s="10">
+        <v>90000</v>
+      </c>
+      <c r="J53" s="10">
+        <v>16000</v>
+      </c>
+      <c r="K53" s="10">
+        <v>106000</v>
+      </c>
+      <c r="L53" s="16">
+        <v>106000</v>
+      </c>
+    </row>
+    <row r="54" spans="1:12" ht="14" x14ac:dyDescent="0.15">
+      <c r="A54" s="5">
+        <v>202603022905</v>
+      </c>
+      <c r="B54" s="13">
+        <v>46083</v>
+      </c>
+      <c r="C54" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="D54" s="17"/>
+      <c r="E54" s="18"/>
+      <c r="F54" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="G54" s="8">
+        <v>0.510185</v>
+      </c>
+      <c r="H54" s="9">
+        <v>0.60430600000000001</v>
+      </c>
+      <c r="I54" s="10">
+        <v>101250</v>
+      </c>
+      <c r="J54" s="11">
+        <v>0</v>
+      </c>
+      <c r="K54" s="10">
+        <v>101250</v>
+      </c>
+      <c r="L54" s="10">
+        <v>101500</v>
+      </c>
+    </row>
+    <row r="55" spans="1:12" ht="14" x14ac:dyDescent="0.15">
+      <c r="A55" s="5">
+        <v>202603022906</v>
+      </c>
+      <c r="B55" s="13">
+        <v>46083</v>
+      </c>
+      <c r="C55" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D55" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="E55" s="22"/>
+      <c r="F55" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="G55" s="8">
+        <v>0.510602</v>
+      </c>
+      <c r="H55" s="9">
+        <v>0.59393499999999999</v>
+      </c>
+      <c r="I55" s="10">
+        <v>63000</v>
+      </c>
+      <c r="J55" s="11">
+        <v>0</v>
+      </c>
+      <c r="K55" s="10">
+        <v>63000</v>
+      </c>
+      <c r="L55" s="10">
+        <v>63000</v>
+      </c>
+    </row>
+    <row r="56" spans="1:12" ht="14" x14ac:dyDescent="0.15">
+      <c r="A56" s="5">
+        <v>202603022907</v>
+      </c>
+      <c r="B56" s="13">
+        <v>46083</v>
+      </c>
+      <c r="C56" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D56" s="17"/>
+      <c r="E56" s="18"/>
+      <c r="F56" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="G56" s="8">
+        <v>0.52311300000000005</v>
+      </c>
+      <c r="H56" s="9">
+        <v>0.58381899999999998</v>
+      </c>
+      <c r="I56" s="10">
+        <v>50721</v>
+      </c>
+      <c r="J56" s="10">
+        <v>10000</v>
+      </c>
+      <c r="K56" s="10">
+        <v>60721</v>
+      </c>
+      <c r="L56" s="10">
+        <v>61000</v>
+      </c>
+    </row>
+    <row r="57" spans="1:12" ht="14" x14ac:dyDescent="0.15">
+      <c r="A57" s="5">
+        <v>202603022908</v>
+      </c>
+      <c r="B57" s="13">
+        <v>46083</v>
+      </c>
+      <c r="C57" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="D57" s="17"/>
+      <c r="E57" s="18"/>
+      <c r="F57" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="G57" s="8">
+        <v>0.53841399999999995</v>
+      </c>
+      <c r="H57" s="9">
+        <v>0.58008099999999996</v>
+      </c>
+      <c r="I57" s="10">
+        <v>20000</v>
+      </c>
+      <c r="J57" s="11">
+        <v>0</v>
+      </c>
+      <c r="K57" s="10">
+        <v>20000</v>
+      </c>
+      <c r="L57" s="10">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="58" spans="1:12" ht="14" x14ac:dyDescent="0.15">
+      <c r="A58" s="5">
+        <v>202603022909</v>
+      </c>
+      <c r="B58" s="13">
+        <v>46083</v>
+      </c>
+      <c r="C58" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="D58" s="17"/>
+      <c r="E58" s="18"/>
+      <c r="F58" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="G58" s="8">
+        <v>0.56173600000000001</v>
+      </c>
+      <c r="H58" s="9">
+        <v>0.645069</v>
+      </c>
+      <c r="I58" s="10">
+        <v>40000</v>
+      </c>
+      <c r="J58" s="11">
+        <v>0</v>
+      </c>
+      <c r="K58" s="10">
+        <v>40000</v>
+      </c>
+      <c r="L58" s="10">
+        <v>40000</v>
+      </c>
+    </row>
+    <row r="59" spans="1:12" ht="14" x14ac:dyDescent="0.15">
+      <c r="A59" s="5">
+        <v>202603022910</v>
+      </c>
+      <c r="B59" s="13">
+        <v>46083</v>
+      </c>
+      <c r="C59" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D59" s="17"/>
+      <c r="E59" s="18"/>
+      <c r="F59" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="G59" s="8">
+        <v>0.58789400000000003</v>
+      </c>
+      <c r="H59" s="9">
+        <v>0.67122700000000002</v>
+      </c>
+      <c r="I59" s="10">
+        <v>40000</v>
+      </c>
+      <c r="J59" s="11">
+        <v>0</v>
+      </c>
+      <c r="K59" s="10">
+        <v>40000</v>
+      </c>
+      <c r="L59" s="10">
+        <v>40000</v>
+      </c>
+    </row>
+    <row r="60" spans="1:12" ht="14" x14ac:dyDescent="0.15">
+      <c r="A60" s="5">
+        <v>202603022911</v>
+      </c>
+      <c r="B60" s="13">
+        <v>46083</v>
+      </c>
+      <c r="C60" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D60" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="E60" s="22"/>
+      <c r="F60" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="G60" s="8">
+        <v>0.59736100000000003</v>
+      </c>
+      <c r="H60" s="9">
+        <v>0.75083299999999997</v>
+      </c>
+      <c r="I60" s="10">
+        <v>66234</v>
+      </c>
+      <c r="J60" s="11">
+        <v>0</v>
+      </c>
+      <c r="K60" s="10">
+        <v>66234</v>
+      </c>
+      <c r="L60" s="10">
+        <v>66500</v>
+      </c>
+    </row>
+    <row r="61" spans="1:12" ht="14" x14ac:dyDescent="0.15">
+      <c r="A61" s="5">
+        <v>202603022912</v>
+      </c>
+      <c r="B61" s="13">
+        <v>46083</v>
+      </c>
+      <c r="C61" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="D61" s="17"/>
+      <c r="E61" s="18"/>
+      <c r="F61" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="G61" s="8">
+        <v>0.60461799999999999</v>
+      </c>
+      <c r="H61" s="9">
+        <v>0.65978000000000003</v>
+      </c>
+      <c r="I61" s="10">
+        <v>26307</v>
+      </c>
+      <c r="J61" s="10">
+        <v>8000</v>
+      </c>
+      <c r="K61" s="10">
+        <v>34307</v>
+      </c>
+      <c r="L61" s="10">
+        <v>34500</v>
+      </c>
+    </row>
+    <row r="62" spans="1:12" ht="14" x14ac:dyDescent="0.15">
+      <c r="A62" s="5">
+        <v>202603022913</v>
+      </c>
+      <c r="B62" s="13">
+        <v>46083</v>
+      </c>
+      <c r="C62" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D62" s="17"/>
+      <c r="E62" s="18"/>
+      <c r="F62" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="G62" s="8">
+        <v>0.60675900000000005</v>
+      </c>
+      <c r="H62" s="9">
+        <v>0.64842599999999995</v>
+      </c>
+      <c r="I62" s="10">
+        <v>20000</v>
+      </c>
+      <c r="J62" s="11">
+        <v>0</v>
+      </c>
+      <c r="K62" s="10">
+        <v>20000</v>
+      </c>
+      <c r="L62" s="10">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="63" spans="1:12" ht="14" x14ac:dyDescent="0.15">
+      <c r="A63" s="5">
+        <v>202603022914</v>
+      </c>
+      <c r="B63" s="13">
+        <v>46083</v>
+      </c>
+      <c r="C63" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="D63" s="17"/>
+      <c r="E63" s="18"/>
+      <c r="F63" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="G63" s="8">
+        <v>0.62175899999999995</v>
+      </c>
+      <c r="H63" s="9">
+        <v>0.70509299999999997</v>
+      </c>
+      <c r="I63" s="10">
+        <v>40000</v>
+      </c>
+      <c r="J63" s="10">
+        <v>5000</v>
+      </c>
+      <c r="K63" s="10">
+        <v>45000</v>
+      </c>
+      <c r="L63" s="10">
+        <v>45000</v>
+      </c>
+    </row>
+    <row r="64" spans="1:12" ht="14" x14ac:dyDescent="0.15">
+      <c r="A64" s="5">
+        <v>202603022915</v>
+      </c>
+      <c r="B64" s="13">
+        <v>46083</v>
+      </c>
+      <c r="C64" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D64" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="E64" s="22"/>
+      <c r="F64" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="G64" s="8">
+        <v>0.79901599999999995</v>
+      </c>
+      <c r="H64" s="9">
+        <v>0.91598400000000002</v>
+      </c>
+      <c r="I64" s="10">
+        <v>88150</v>
+      </c>
+      <c r="J64" s="10">
+        <v>36000</v>
+      </c>
+      <c r="K64" s="10">
+        <v>124150</v>
+      </c>
+      <c r="L64" s="10">
+        <v>124500</v>
+      </c>
+    </row>
+    <row r="65" spans="1:12" ht="14" x14ac:dyDescent="0.15">
+      <c r="A65" s="5">
+        <v>202603022916</v>
+      </c>
+      <c r="B65" s="13">
+        <v>46083</v>
+      </c>
+      <c r="C65" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="D65" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="E65" s="22"/>
+      <c r="F65" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="G65" s="8">
+        <v>0.80394699999999997</v>
+      </c>
+      <c r="H65" s="9">
+        <v>0.93235000000000001</v>
+      </c>
+      <c r="I65" s="10">
+        <v>96545</v>
+      </c>
+      <c r="J65" s="10">
+        <v>38000</v>
+      </c>
+      <c r="K65" s="10">
+        <v>134545</v>
+      </c>
+      <c r="L65" s="10">
+        <v>135000</v>
+      </c>
+    </row>
+    <row r="66" spans="1:12" ht="14" x14ac:dyDescent="0.15">
+      <c r="A66" s="5">
+        <v>202603022917</v>
+      </c>
+      <c r="B66" s="13">
+        <v>46083</v>
+      </c>
+      <c r="C66" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="D66" s="17"/>
+      <c r="E66" s="18"/>
+      <c r="F66" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="G66" s="8">
+        <v>0.807037</v>
+      </c>
+      <c r="H66" s="9">
+        <v>0.89036999999999999</v>
+      </c>
+      <c r="I66" s="10">
+        <v>70000</v>
+      </c>
+      <c r="J66" s="10">
+        <v>55000</v>
+      </c>
+      <c r="K66" s="10">
+        <v>125000</v>
+      </c>
+      <c r="L66" s="10">
+        <v>125000</v>
+      </c>
+    </row>
+    <row r="67" spans="1:12" ht="14" x14ac:dyDescent="0.15">
+      <c r="A67" s="5">
+        <v>202603022918</v>
+      </c>
+      <c r="B67" s="13">
+        <v>46083</v>
+      </c>
+      <c r="C67" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D67" s="17"/>
+      <c r="E67" s="18"/>
+      <c r="F67" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="G67" s="8">
+        <v>0.80881899999999995</v>
+      </c>
+      <c r="H67" s="9">
+        <v>0.87068299999999998</v>
+      </c>
+      <c r="I67" s="10">
+        <v>51887</v>
+      </c>
+      <c r="J67" s="10">
+        <v>22000</v>
+      </c>
+      <c r="K67" s="10">
+        <v>73887</v>
+      </c>
+      <c r="L67" s="10">
+        <v>74000</v>
+      </c>
+    </row>
+    <row r="68" spans="1:12" ht="14" x14ac:dyDescent="0.15">
+      <c r="A68" s="5">
+        <v>202603022919</v>
+      </c>
+      <c r="B68" s="13">
+        <v>46083</v>
+      </c>
+      <c r="C68" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="D68" s="17"/>
+      <c r="E68" s="18"/>
+      <c r="F68" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="G68" s="8">
+        <v>0.82744200000000001</v>
+      </c>
+      <c r="H68" s="9">
+        <v>0.896065</v>
+      </c>
+      <c r="I68" s="10">
+        <v>57134</v>
+      </c>
+      <c r="J68" s="10">
+        <v>5000</v>
+      </c>
+      <c r="K68" s="10">
+        <v>62134</v>
+      </c>
+      <c r="L68" s="10">
+        <v>62500</v>
+      </c>
+    </row>
+    <row r="69" spans="1:12" ht="14" x14ac:dyDescent="0.15">
+      <c r="A69" s="5">
+        <v>202603022920</v>
+      </c>
+      <c r="B69" s="13">
+        <v>46083</v>
+      </c>
+      <c r="C69" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D69" s="17"/>
+      <c r="E69" s="18"/>
+      <c r="F69" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="G69" s="8">
+        <v>0.82923599999999997</v>
+      </c>
+      <c r="H69" s="9">
+        <v>0.87693299999999996</v>
+      </c>
+      <c r="I69" s="10">
+        <v>39644</v>
+      </c>
+      <c r="J69" s="11">
+        <v>0</v>
+      </c>
+      <c r="K69" s="10">
+        <v>39644</v>
+      </c>
+      <c r="L69" s="10">
+        <v>40000</v>
+      </c>
+    </row>
+    <row r="70" spans="1:12" ht="14" x14ac:dyDescent="0.15">
+      <c r="A70" s="5">
+        <v>202603022921</v>
+      </c>
+      <c r="B70" s="13">
+        <v>46083</v>
+      </c>
+      <c r="C70" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D70" s="17"/>
+      <c r="E70" s="18"/>
+      <c r="F70" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="G70" s="8">
+        <v>0.85557899999999998</v>
+      </c>
+      <c r="H70" s="9">
+        <v>0.89724499999999996</v>
+      </c>
+      <c r="I70" s="10">
+        <v>35000</v>
+      </c>
+      <c r="J70" s="11">
+        <v>0</v>
+      </c>
+      <c r="K70" s="10">
+        <v>35000</v>
+      </c>
+      <c r="L70" s="10">
+        <v>35000</v>
+      </c>
+    </row>
+    <row r="71" spans="1:12" ht="14" x14ac:dyDescent="0.15">
+      <c r="A71" s="5">
+        <v>202603022922</v>
+      </c>
+      <c r="B71" s="13">
+        <v>46083</v>
+      </c>
+      <c r="C71" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="D71" s="21" t="s">
+        <v>40</v>
+      </c>
+      <c r="E71" s="22"/>
+      <c r="F71" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="G71" s="8">
+        <v>0.86092599999999997</v>
+      </c>
+      <c r="H71" s="9">
+        <v>0.932674</v>
+      </c>
+      <c r="I71" s="10">
+        <v>54044</v>
+      </c>
+      <c r="J71" s="10">
+        <v>12000</v>
+      </c>
+      <c r="K71" s="10">
+        <v>66044</v>
+      </c>
+      <c r="L71" s="10">
+        <v>66500</v>
+      </c>
+    </row>
+    <row r="72" spans="1:12" ht="14" x14ac:dyDescent="0.15">
+      <c r="A72" s="5">
+        <v>202603022923</v>
+      </c>
+      <c r="B72" s="13">
+        <v>46083</v>
+      </c>
+      <c r="C72" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D72" s="17"/>
+      <c r="E72" s="18"/>
+      <c r="F72" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="G72" s="8">
+        <v>0.86571799999999999</v>
+      </c>
+      <c r="H72" s="9">
+        <v>0.90738399999999997</v>
+      </c>
+      <c r="I72" s="10">
+        <v>35000</v>
+      </c>
+      <c r="J72" s="10">
+        <v>10000</v>
+      </c>
+      <c r="K72" s="10">
+        <v>45000</v>
+      </c>
+      <c r="L72" s="10">
+        <v>45000</v>
+      </c>
+    </row>
+    <row r="73" spans="1:12" ht="14" x14ac:dyDescent="0.15">
+      <c r="A73" s="5">
+        <v>202603022924</v>
+      </c>
+      <c r="B73" s="13">
+        <v>46083</v>
+      </c>
+      <c r="C73" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D73" s="17"/>
+      <c r="E73" s="18"/>
+      <c r="F73" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="G73" s="8">
+        <v>0.87425900000000001</v>
+      </c>
+      <c r="H73" s="9">
+        <v>0.99892400000000003</v>
+      </c>
+      <c r="I73" s="10">
+        <v>104357</v>
+      </c>
+      <c r="J73" s="10">
+        <v>28000</v>
+      </c>
+      <c r="K73" s="10">
+        <v>132357</v>
+      </c>
+      <c r="L73" s="10">
+        <v>132500</v>
+      </c>
+    </row>
+    <row r="74" spans="1:12" ht="14" x14ac:dyDescent="0.15">
+      <c r="A74" s="5">
+        <v>202603022925</v>
+      </c>
+      <c r="B74" s="13">
+        <v>46083</v>
+      </c>
+      <c r="C74" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="D74" s="19" t="s">
+        <v>41</v>
+      </c>
+      <c r="E74" s="20"/>
+      <c r="F74" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="G74" s="8">
+        <v>0.87993100000000002</v>
+      </c>
+      <c r="H74" s="12">
+        <v>3.2520000000000001E-3</v>
+      </c>
+      <c r="I74" s="10">
+        <v>92872</v>
+      </c>
+      <c r="J74" s="10">
+        <v>32000</v>
+      </c>
+      <c r="K74" s="10">
+        <v>124872</v>
+      </c>
+      <c r="L74" s="10">
+        <v>125000</v>
+      </c>
+    </row>
+    <row r="75" spans="1:12" ht="14" x14ac:dyDescent="0.15">
+      <c r="A75" s="5">
+        <v>202603022926</v>
+      </c>
+      <c r="B75" s="13">
+        <v>46083</v>
+      </c>
+      <c r="C75" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D75" s="17"/>
+      <c r="E75" s="18"/>
+      <c r="F75" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="G75" s="8">
+        <v>0.89011600000000002</v>
+      </c>
+      <c r="H75" s="12">
+        <v>0.97344900000000001</v>
+      </c>
+      <c r="I75" s="10">
+        <v>70000</v>
+      </c>
+      <c r="J75" s="10">
+        <v>10000</v>
+      </c>
+      <c r="K75" s="10">
+        <v>80000</v>
+      </c>
+      <c r="L75" s="10">
+        <v>80000</v>
+      </c>
+    </row>
+    <row r="76" spans="1:12" ht="14" x14ac:dyDescent="0.15">
+      <c r="A76" s="5">
+        <v>202603022927</v>
+      </c>
+      <c r="B76" s="13">
+        <v>46083</v>
+      </c>
+      <c r="C76" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="D76" s="17"/>
+      <c r="E76" s="18"/>
+      <c r="F76" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="G76" s="8">
+        <v>0.89775499999999997</v>
+      </c>
+      <c r="H76" s="12">
+        <v>0.93942099999999995</v>
+      </c>
+      <c r="I76" s="10">
+        <v>35000</v>
+      </c>
+      <c r="J76" s="10">
+        <v>16000</v>
+      </c>
+      <c r="K76" s="10">
+        <v>51000</v>
+      </c>
+      <c r="L76" s="10">
+        <v>51000</v>
+      </c>
+    </row>
+    <row r="77" spans="1:12" ht="14" x14ac:dyDescent="0.15">
+      <c r="A77" s="5">
+        <v>202603022928</v>
+      </c>
+      <c r="B77" s="13">
+        <v>46084</v>
+      </c>
+      <c r="C77" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D77" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="E77" s="20"/>
+      <c r="F77" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="G77" s="8">
+        <v>0.93898099999999995</v>
+      </c>
+      <c r="H77" s="12">
+        <v>3.7048999999999999E-2</v>
+      </c>
+      <c r="I77" s="10">
+        <v>73983</v>
+      </c>
+      <c r="J77" s="10">
+        <v>26000</v>
+      </c>
+      <c r="K77" s="10">
+        <v>99983</v>
+      </c>
+      <c r="L77" s="10">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="78" spans="1:12" ht="14" x14ac:dyDescent="0.15">
+      <c r="A78" s="5">
+        <v>202603022929</v>
+      </c>
+      <c r="B78" s="13">
+        <v>46084</v>
+      </c>
+      <c r="C78" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D78" s="17"/>
+      <c r="E78" s="18"/>
+      <c r="F78" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="G78" s="8">
+        <v>0.94304399999999999</v>
+      </c>
+      <c r="H78" s="12">
+        <v>2.6424E-2</v>
+      </c>
+      <c r="I78" s="10">
+        <v>69960</v>
+      </c>
+      <c r="J78" s="10">
+        <v>16000</v>
+      </c>
+      <c r="K78" s="10">
+        <v>85960</v>
+      </c>
+      <c r="L78" s="10">
+        <v>86000</v>
+      </c>
+    </row>
+    <row r="79" spans="1:12" ht="14" x14ac:dyDescent="0.15">
+      <c r="A79" s="5">
+        <v>202603022930</v>
+      </c>
+      <c r="B79" s="13">
+        <v>46084</v>
+      </c>
+      <c r="C79" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="D79" s="19" t="s">
+        <v>22</v>
+      </c>
+      <c r="E79" s="20"/>
+      <c r="F79" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="G79" s="8">
+        <v>0.94370399999999999</v>
+      </c>
+      <c r="H79" s="12">
+        <v>2.4650000000000002E-3</v>
+      </c>
+      <c r="I79" s="10">
+        <v>44075</v>
+      </c>
+      <c r="J79" s="11">
+        <v>0</v>
+      </c>
+      <c r="K79" s="10">
+        <v>44075</v>
+      </c>
+      <c r="L79" s="10">
+        <v>44500</v>
+      </c>
+    </row>
+    <row r="80" spans="1:12" ht="14" x14ac:dyDescent="0.15">
+      <c r="A80" s="5">
+        <v>202603022931</v>
+      </c>
+      <c r="B80" s="13">
+        <v>46084</v>
+      </c>
+      <c r="C80" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D80" s="17"/>
+      <c r="E80" s="18"/>
+      <c r="F80" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="G80" s="8">
+        <v>0.94821800000000001</v>
+      </c>
+      <c r="H80" s="12">
+        <v>1.4803E-2</v>
+      </c>
+      <c r="I80" s="10">
+        <v>55385</v>
+      </c>
+      <c r="J80" s="10">
+        <v>40000</v>
+      </c>
+      <c r="K80" s="10">
+        <v>95385</v>
+      </c>
+      <c r="L80" s="10">
+        <v>95500</v>
+      </c>
+    </row>
+    <row r="81" spans="1:12" ht="14" x14ac:dyDescent="0.15">
+      <c r="A81" s="5">
+        <v>202603022932</v>
+      </c>
+      <c r="B81" s="13">
+        <v>46084</v>
+      </c>
+      <c r="C81" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D81" s="17"/>
+      <c r="E81" s="18"/>
+      <c r="F81" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="G81" s="8">
+        <v>0.94922499999999999</v>
+      </c>
+      <c r="H81" s="12">
+        <v>2.3599999999999999E-2</v>
+      </c>
+      <c r="I81" s="10">
+        <v>62381</v>
+      </c>
+      <c r="J81" s="10">
+        <v>20000</v>
+      </c>
+      <c r="K81" s="10">
+        <v>82381</v>
+      </c>
+      <c r="L81" s="10">
+        <v>82500</v>
+      </c>
+    </row>
+    <row r="82" spans="1:12" ht="14" x14ac:dyDescent="0.15">
+      <c r="A82" s="5">
+        <v>202603022933</v>
+      </c>
+      <c r="B82" s="13">
+        <v>46084</v>
+      </c>
+      <c r="C82" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="D82" s="17"/>
+      <c r="E82" s="18"/>
+      <c r="F82" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="G82" s="8">
+        <v>0.95225700000000002</v>
+      </c>
+      <c r="H82" s="12">
+        <v>1.9132E-2</v>
+      </c>
+      <c r="I82" s="10">
+        <v>55968</v>
+      </c>
+      <c r="J82" s="10">
+        <v>20000</v>
+      </c>
+      <c r="K82" s="10">
+        <v>75968</v>
+      </c>
+      <c r="L82" s="10">
+        <v>76000</v>
+      </c>
+    </row>
+    <row r="83" spans="1:12" ht="14" x14ac:dyDescent="0.15">
+      <c r="A83" s="5">
+        <v>202603022934</v>
+      </c>
+      <c r="B83" s="13">
+        <v>46083</v>
+      </c>
+      <c r="C83" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="D83" s="17"/>
+      <c r="E83" s="18"/>
+      <c r="F83" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="G83" s="8">
+        <v>0.95493099999999997</v>
+      </c>
+      <c r="H83" s="12">
+        <v>0.99659699999999996</v>
+      </c>
+      <c r="I83" s="10">
+        <v>35000</v>
+      </c>
+      <c r="J83" s="11">
+        <v>0</v>
+      </c>
+      <c r="K83" s="10">
+        <v>35000</v>
+      </c>
+      <c r="L83" s="10">
+        <v>35000</v>
+      </c>
+    </row>
+    <row r="84" spans="1:12" ht="14" x14ac:dyDescent="0.15">
+      <c r="A84" s="5">
+        <v>202603022935</v>
+      </c>
+      <c r="B84" s="13">
+        <v>46084</v>
+      </c>
+      <c r="C84" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="D84" s="17"/>
+      <c r="E84" s="18"/>
+      <c r="F84" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="G84" s="8">
+        <v>0.96503499999999998</v>
+      </c>
+      <c r="H84" s="12">
+        <v>4.2835999999999999E-2</v>
+      </c>
+      <c r="I84" s="10">
+        <v>65296</v>
+      </c>
+      <c r="J84" s="11">
+        <v>0</v>
+      </c>
+      <c r="K84" s="10">
+        <v>65296</v>
+      </c>
+      <c r="L84" s="10">
+        <v>65500</v>
+      </c>
+    </row>
+    <row r="85" spans="1:12" ht="14" x14ac:dyDescent="0.15">
+      <c r="A85" s="14">
+        <v>20260302854</v>
+      </c>
+      <c r="B85" s="13">
+        <v>46083</v>
+      </c>
+      <c r="C85" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="D85" s="17"/>
+      <c r="E85" s="18"/>
+      <c r="F85" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="G85" s="15">
+        <v>0.54884299999999997</v>
+      </c>
+      <c r="H85" s="8">
+        <v>0.67384299999999997</v>
+      </c>
+      <c r="I85" s="10">
+        <v>90000</v>
+      </c>
+      <c r="J85" s="10">
+        <v>60000</v>
+      </c>
+      <c r="K85" s="10">
+        <v>150000</v>
+      </c>
+      <c r="L85" s="16">
+        <v>150000</v>
+      </c>
+    </row>
+    <row r="86" spans="1:12" ht="14" x14ac:dyDescent="0.15">
+      <c r="A86" s="14">
+        <v>20260302855</v>
+      </c>
+      <c r="B86" s="13">
+        <v>46083</v>
+      </c>
+      <c r="C86" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="D86" s="17"/>
+      <c r="E86" s="18"/>
+      <c r="F86" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="G86" s="15">
+        <v>0.57535899999999995</v>
+      </c>
+      <c r="H86" s="8">
+        <v>0.65869200000000006</v>
+      </c>
+      <c r="I86" s="10">
+        <v>40000</v>
+      </c>
+      <c r="J86" s="10">
+        <v>16000</v>
+      </c>
+      <c r="K86" s="10">
+        <v>56000</v>
+      </c>
+      <c r="L86" s="16">
+        <v>56000</v>
+      </c>
+    </row>
+    <row r="87" spans="1:12" ht="14" x14ac:dyDescent="0.15">
+      <c r="A87" s="14">
+        <v>20260302856</v>
+      </c>
+      <c r="B87" s="13">
+        <v>46083</v>
+      </c>
+      <c r="C87" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="D87" s="17"/>
+      <c r="E87" s="18"/>
+      <c r="F87" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="G87" s="15">
+        <v>0.60737300000000005</v>
+      </c>
+      <c r="H87" s="8">
+        <v>0.64903900000000003</v>
+      </c>
+      <c r="I87" s="10">
+        <v>20000</v>
+      </c>
+      <c r="J87" s="10">
+        <v>8000</v>
+      </c>
+      <c r="K87" s="10">
+        <v>28000</v>
+      </c>
+      <c r="L87" s="16">
+        <v>28000</v>
+      </c>
+    </row>
+    <row r="88" spans="1:12" ht="14" x14ac:dyDescent="0.15">
+      <c r="A88" s="14">
+        <v>20260302857</v>
+      </c>
+      <c r="B88" s="13">
+        <v>46083</v>
+      </c>
+      <c r="C88" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="D88" s="17"/>
+      <c r="E88" s="18"/>
+      <c r="F88" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="G88" s="15">
+        <v>0.65005800000000002</v>
+      </c>
+      <c r="H88" s="8">
+        <v>0.69172500000000003</v>
+      </c>
+      <c r="I88" s="10">
+        <v>20000</v>
+      </c>
+      <c r="J88" s="11">
+        <v>0</v>
+      </c>
+      <c r="K88" s="10">
+        <v>20000</v>
+      </c>
+      <c r="L88" s="16">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="89" spans="1:12" ht="14" x14ac:dyDescent="0.15">
+      <c r="A89" s="14">
+        <v>20260302858</v>
+      </c>
+      <c r="B89" s="13">
+        <v>46083</v>
+      </c>
+      <c r="C89" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="D89" s="17"/>
+      <c r="E89" s="18"/>
+      <c r="F89" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="G89" s="15">
+        <v>0.84517399999999998</v>
+      </c>
+      <c r="H89" s="8">
+        <v>0.89557900000000001</v>
+      </c>
+      <c r="I89" s="10">
+        <v>41976</v>
+      </c>
+      <c r="J89" s="10">
+        <v>5000</v>
+      </c>
+      <c r="K89" s="10">
+        <v>46976</v>
+      </c>
+      <c r="L89" s="16">
+        <v>47000</v>
+      </c>
+    </row>
+    <row r="90" spans="1:12" ht="14" x14ac:dyDescent="0.15">
+      <c r="A90" s="14">
+        <v>20260302859</v>
+      </c>
+      <c r="B90" s="13">
+        <v>46083</v>
+      </c>
+      <c r="C90" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="D90" s="17"/>
+      <c r="E90" s="18"/>
+      <c r="F90" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="G90" s="15">
+        <v>0.85474499999999998</v>
+      </c>
+      <c r="H90" s="8">
+        <v>0.938079</v>
+      </c>
+      <c r="I90" s="10">
+        <v>70000</v>
+      </c>
+      <c r="J90" s="10">
+        <v>16000</v>
+      </c>
+      <c r="K90" s="10">
+        <v>86000</v>
+      </c>
+      <c r="L90" s="16">
+        <v>86000</v>
+      </c>
+    </row>
+    <row r="91" spans="1:12" ht="14" x14ac:dyDescent="0.15">
+      <c r="A91" s="14">
+        <v>20260302860</v>
+      </c>
+      <c r="B91" s="13">
+        <v>46083</v>
+      </c>
+      <c r="C91" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="D91" s="17"/>
+      <c r="E91" s="18"/>
+      <c r="F91" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="G91" s="15">
+        <v>0.88667799999999997</v>
+      </c>
+      <c r="H91" s="8">
+        <v>0.97001199999999999</v>
+      </c>
+      <c r="I91" s="10">
+        <v>90000</v>
+      </c>
+      <c r="J91" s="10">
+        <v>18000</v>
+      </c>
+      <c r="K91" s="10">
+        <v>108000</v>
+      </c>
+      <c r="L91" s="16">
+        <v>108000</v>
+      </c>
+    </row>
+    <row r="92" spans="1:12" ht="14" x14ac:dyDescent="0.15">
+      <c r="A92" s="14">
+        <v>20260302861</v>
+      </c>
+      <c r="B92" s="13">
+        <v>46083</v>
+      </c>
+      <c r="C92" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="D92" s="17"/>
+      <c r="E92" s="18"/>
+      <c r="F92" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="G92" s="15">
+        <v>0.88875000000000004</v>
+      </c>
+      <c r="H92" s="8">
+        <v>0.93041700000000005</v>
+      </c>
+      <c r="I92" s="10">
+        <v>35000</v>
+      </c>
+      <c r="J92" s="10">
+        <v>20000</v>
+      </c>
+      <c r="K92" s="10">
+        <v>55000</v>
+      </c>
+      <c r="L92" s="16">
+        <v>55000</v>
+      </c>
+    </row>
+    <row r="93" spans="1:12" ht="14" x14ac:dyDescent="0.15">
+      <c r="A93" s="14">
+        <v>20260302862</v>
+      </c>
+      <c r="B93" s="13">
+        <v>46083</v>
+      </c>
+      <c r="C93" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="D93" s="17"/>
+      <c r="E93" s="18"/>
+      <c r="F93" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="G93" s="15">
+        <v>0.89759299999999997</v>
+      </c>
+      <c r="H93" s="8">
+        <v>0.93925899999999996</v>
+      </c>
+      <c r="I93" s="10">
+        <v>35000</v>
+      </c>
+      <c r="J93" s="10">
+        <v>25000</v>
+      </c>
+      <c r="K93" s="10">
+        <v>60000</v>
+      </c>
+      <c r="L93" s="16">
+        <v>60000</v>
+      </c>
+    </row>
+    <row r="94" spans="1:12" ht="14" x14ac:dyDescent="0.15">
+      <c r="A94" s="14">
+        <v>20260302863</v>
+      </c>
+      <c r="B94" s="13">
+        <v>46083</v>
+      </c>
+      <c r="C94" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="D94" s="17"/>
+      <c r="E94" s="18"/>
+      <c r="F94" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="G94" s="15">
+        <v>0.93209500000000001</v>
+      </c>
+      <c r="H94" s="8">
+        <v>0.97376200000000002</v>
+      </c>
+      <c r="I94" s="10">
+        <v>35000</v>
+      </c>
+      <c r="J94" s="10">
+        <v>51000</v>
+      </c>
+      <c r="K94" s="10">
+        <v>86000</v>
+      </c>
+      <c r="L94" s="16">
+        <v>86000</v>
+      </c>
+    </row>
+    <row r="95" spans="1:12" ht="14" x14ac:dyDescent="0.15">
+      <c r="A95" s="14">
+        <v>20260302864</v>
+      </c>
+      <c r="B95" s="13">
+        <v>46084</v>
+      </c>
+      <c r="C95" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="D95" s="17"/>
+      <c r="E95" s="18"/>
+      <c r="F95" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="G95" s="15">
+        <v>0.97517399999999999</v>
+      </c>
+      <c r="H95" s="8">
+        <v>5.8507000000000003E-2</v>
+      </c>
+      <c r="I95" s="10">
+        <v>70000</v>
+      </c>
+      <c r="J95" s="10">
+        <v>20000</v>
+      </c>
+      <c r="K95" s="10">
+        <v>90000</v>
+      </c>
+      <c r="L95" s="16">
+        <v>90000</v>
+      </c>
+    </row>
+    <row r="96" spans="1:12" ht="14" x14ac:dyDescent="0.15">
+      <c r="A96" s="14">
+        <v>20260302865</v>
+      </c>
+      <c r="B96" s="13">
+        <v>46084</v>
+      </c>
+      <c r="C96" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="D96" s="17"/>
+      <c r="E96" s="18"/>
+      <c r="F96" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="G96" s="15">
+        <v>0.97772000000000003</v>
+      </c>
+      <c r="H96" s="8">
+        <v>1.9387000000000001E-2</v>
+      </c>
+      <c r="I96" s="10">
+        <v>35000</v>
+      </c>
+      <c r="J96" s="11">
+        <v>0</v>
+      </c>
+      <c r="K96" s="10">
+        <v>35000</v>
+      </c>
+      <c r="L96" s="16">
+        <v>35000</v>
+      </c>
+    </row>
+    <row r="97" spans="1:12" ht="14" x14ac:dyDescent="0.15">
+      <c r="A97" s="14">
+        <v>20260302866</v>
+      </c>
+      <c r="B97" s="13">
+        <v>46084</v>
+      </c>
+      <c r="C97" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="D97" s="17" t="s">
+        <v>45</v>
+      </c>
+      <c r="E97" s="18"/>
+      <c r="F97" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="G97" s="15">
+        <v>0.99612299999999998</v>
+      </c>
+      <c r="H97" s="8">
+        <v>3.3946999999999998E-2</v>
+      </c>
+      <c r="I97" s="10">
+        <v>31500</v>
+      </c>
+      <c r="J97" s="11">
+        <v>0</v>
+      </c>
+      <c r="K97" s="10">
+        <v>31500</v>
+      </c>
+      <c r="L97" s="16">
+        <v>31500</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="42">
+  <mergeCells count="97">
     <mergeCell ref="D1:E1"/>
     <mergeCell ref="D2:E2"/>
     <mergeCell ref="D3:E3"/>
@@ -2361,11 +4394,66 @@
     <mergeCell ref="D35:E35"/>
     <mergeCell ref="D36:E36"/>
     <mergeCell ref="D37:E37"/>
+    <mergeCell ref="D43:E43"/>
+    <mergeCell ref="D44:E44"/>
+    <mergeCell ref="D45:E45"/>
+    <mergeCell ref="D46:E46"/>
     <mergeCell ref="D38:E38"/>
     <mergeCell ref="D39:E39"/>
     <mergeCell ref="D40:E40"/>
     <mergeCell ref="D41:E41"/>
     <mergeCell ref="D42:E42"/>
+    <mergeCell ref="D47:E47"/>
+    <mergeCell ref="D48:E48"/>
+    <mergeCell ref="D49:E49"/>
+    <mergeCell ref="D50:E50"/>
+    <mergeCell ref="D51:E51"/>
+    <mergeCell ref="D52:E52"/>
+    <mergeCell ref="D53:E53"/>
+    <mergeCell ref="D54:E54"/>
+    <mergeCell ref="D55:E55"/>
+    <mergeCell ref="D56:E56"/>
+    <mergeCell ref="D57:E57"/>
+    <mergeCell ref="D58:E58"/>
+    <mergeCell ref="D59:E59"/>
+    <mergeCell ref="D60:E60"/>
+    <mergeCell ref="D61:E61"/>
+    <mergeCell ref="D62:E62"/>
+    <mergeCell ref="D63:E63"/>
+    <mergeCell ref="D64:E64"/>
+    <mergeCell ref="D65:E65"/>
+    <mergeCell ref="D66:E66"/>
+    <mergeCell ref="D67:E67"/>
+    <mergeCell ref="D68:E68"/>
+    <mergeCell ref="D69:E69"/>
+    <mergeCell ref="D70:E70"/>
+    <mergeCell ref="D71:E71"/>
+    <mergeCell ref="D72:E72"/>
+    <mergeCell ref="D73:E73"/>
+    <mergeCell ref="D74:E74"/>
+    <mergeCell ref="D75:E75"/>
+    <mergeCell ref="D76:E76"/>
+    <mergeCell ref="D77:E77"/>
+    <mergeCell ref="D78:E78"/>
+    <mergeCell ref="D79:E79"/>
+    <mergeCell ref="D80:E80"/>
+    <mergeCell ref="D81:E81"/>
+    <mergeCell ref="D82:E82"/>
+    <mergeCell ref="D83:E83"/>
+    <mergeCell ref="D84:E84"/>
+    <mergeCell ref="D85:E85"/>
+    <mergeCell ref="D86:E86"/>
+    <mergeCell ref="D87:E87"/>
+    <mergeCell ref="D88:E88"/>
+    <mergeCell ref="D89:E89"/>
+    <mergeCell ref="D90:E90"/>
+    <mergeCell ref="D91:E91"/>
+    <mergeCell ref="D97:E97"/>
+    <mergeCell ref="D92:E92"/>
+    <mergeCell ref="D93:E93"/>
+    <mergeCell ref="D94:E94"/>
+    <mergeCell ref="D95:E95"/>
+    <mergeCell ref="D96:E96"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>

--- a/LAPORAN 1 MARET.xlsx
+++ b/LAPORAN 1 MARET.xlsx
@@ -5,16 +5,19 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/stefanusjason/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/stefanusjason/Desktop/KBC-Dashboard/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11CB25D7-EE24-BE47-84DF-D2572C5AC070}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F0EA90E-9AF8-D54D-B06D-1AF4F6DE09CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16280" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Table 1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Table 1'!$A$1:$L$97</definedName>
+  </definedNames>
   <calcPr calcId="124519"/>
 </workbook>
 </file>
@@ -355,16 +358,6 @@
     </r>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>Table VIP</t>
-    </r>
-  </si>
-  <si>
     <t>HAPPY HOUR WEEKEND</t>
   </si>
   <si>
@@ -463,13 +456,16 @@
   <si>
     <t>FARID</t>
   </si>
+  <si>
+    <t>Table 7</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="h:mm:ss;@"/>
+    <numFmt numFmtId="167" formatCode="[$-F400]h:mm:ss\ AM/PM"/>
   </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
@@ -582,20 +578,11 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" indent="2" shrinkToFit="1"/>
-    </xf>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="1" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" indent="1" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -603,11 +590,14 @@
     <xf numFmtId="1" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" indent="2" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" indent="3" shrinkToFit="1"/>
-    </xf>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" indent="2" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -616,10 +606,10 @@
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1" indent="1"/>
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1" indent="1"/>
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
@@ -628,16 +618,22 @@
       <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <alignment horizontal="right" vertical="top" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <alignment horizontal="right" vertical="top" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    <xf numFmtId="167" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    <xf numFmtId="167" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" indent="2" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" indent="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" indent="3" shrinkToFit="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1033,10 +1029,10 @@
       <c r="C1" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="D1" s="25" t="s">
+      <c r="D1" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="26"/>
+      <c r="E1" s="14"/>
       <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
@@ -1063,33 +1059,33 @@
       <c r="A2" s="5">
         <v>202603012864</v>
       </c>
-      <c r="B2" s="13">
+      <c r="B2" s="10">
         <v>46082</v>
       </c>
       <c r="C2" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="17"/>
-      <c r="E2" s="18"/>
+      <c r="D2" s="15"/>
+      <c r="E2" s="16"/>
       <c r="F2" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="G2" s="8">
+      <c r="G2" s="23">
         <v>0.53524300000000002</v>
       </c>
-      <c r="H2" s="9">
+      <c r="H2" s="24">
         <v>0.57691000000000003</v>
       </c>
-      <c r="I2" s="10">
+      <c r="I2" s="8">
         <v>35000</v>
       </c>
-      <c r="J2" s="11">
+      <c r="J2" s="9">
         <v>0</v>
       </c>
-      <c r="K2" s="10">
+      <c r="K2" s="8">
         <v>35000</v>
       </c>
-      <c r="L2" s="10">
+      <c r="L2" s="8">
         <v>35000</v>
       </c>
     </row>
@@ -1097,33 +1093,33 @@
       <c r="A3" s="5">
         <v>202603012865</v>
       </c>
-      <c r="B3" s="13">
+      <c r="B3" s="10">
         <v>46082</v>
       </c>
       <c r="C3" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="D3" s="17"/>
-      <c r="E3" s="18"/>
+      <c r="D3" s="15"/>
+      <c r="E3" s="16"/>
       <c r="F3" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="G3" s="8">
+      <c r="G3" s="23">
         <v>0.53669</v>
       </c>
-      <c r="H3" s="9">
+      <c r="H3" s="24">
         <v>0.64537</v>
       </c>
-      <c r="I3" s="10">
+      <c r="I3" s="8">
         <v>90948</v>
       </c>
-      <c r="J3" s="11">
+      <c r="J3" s="9">
         <v>0</v>
       </c>
-      <c r="K3" s="10">
+      <c r="K3" s="8">
         <v>90948</v>
       </c>
-      <c r="L3" s="10">
+      <c r="L3" s="8">
         <v>91000</v>
       </c>
     </row>
@@ -1131,33 +1127,33 @@
       <c r="A4" s="5">
         <v>202603012866</v>
       </c>
-      <c r="B4" s="13">
+      <c r="B4" s="10">
         <v>46082</v>
       </c>
       <c r="C4" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="D4" s="17"/>
-      <c r="E4" s="18"/>
+      <c r="D4" s="15"/>
+      <c r="E4" s="16"/>
       <c r="F4" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="G4" s="8">
+      <c r="G4" s="23">
         <v>0.54925900000000005</v>
       </c>
-      <c r="H4" s="9">
+      <c r="H4" s="24">
         <v>0.67425900000000005</v>
       </c>
-      <c r="I4" s="10">
+      <c r="I4" s="8">
         <v>105000</v>
       </c>
-      <c r="J4" s="11">
+      <c r="J4" s="9">
         <v>0</v>
       </c>
-      <c r="K4" s="10">
+      <c r="K4" s="8">
         <v>105000</v>
       </c>
-      <c r="L4" s="10">
+      <c r="L4" s="8">
         <v>105000</v>
       </c>
     </row>
@@ -1165,33 +1161,33 @@
       <c r="A5" s="5">
         <v>202603012867</v>
       </c>
-      <c r="B5" s="13">
+      <c r="B5" s="10">
         <v>46082</v>
       </c>
       <c r="C5" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="D5" s="17"/>
-      <c r="E5" s="18"/>
+      <c r="D5" s="15"/>
+      <c r="E5" s="16"/>
       <c r="F5" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="G5" s="8">
+      <c r="G5" s="23">
         <v>0.57822899999999999</v>
       </c>
-      <c r="H5" s="9">
+      <c r="H5" s="24">
         <v>0.619896</v>
       </c>
-      <c r="I5" s="10">
+      <c r="I5" s="8">
         <v>35000</v>
       </c>
-      <c r="J5" s="11">
+      <c r="J5" s="9">
         <v>0</v>
       </c>
-      <c r="K5" s="10">
+      <c r="K5" s="8">
         <v>35000</v>
       </c>
-      <c r="L5" s="10">
+      <c r="L5" s="8">
         <v>35000</v>
       </c>
     </row>
@@ -1199,33 +1195,33 @@
       <c r="A6" s="5">
         <v>202603012868</v>
       </c>
-      <c r="B6" s="13">
+      <c r="B6" s="10">
         <v>46082</v>
       </c>
       <c r="C6" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="D6" s="17"/>
-      <c r="E6" s="18"/>
+      <c r="D6" s="15"/>
+      <c r="E6" s="16"/>
       <c r="F6" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="G6" s="8">
+      <c r="G6" s="23">
         <v>0.57835599999999998</v>
       </c>
-      <c r="H6" s="9">
+      <c r="H6" s="24">
         <v>0.65639999999999998</v>
       </c>
-      <c r="I6" s="10">
+      <c r="I6" s="8">
         <v>65296</v>
       </c>
-      <c r="J6" s="10">
+      <c r="J6" s="8">
         <v>5000</v>
       </c>
-      <c r="K6" s="10">
+      <c r="K6" s="8">
         <v>70296</v>
       </c>
-      <c r="L6" s="10">
+      <c r="L6" s="8">
         <v>70500</v>
       </c>
     </row>
@@ -1233,33 +1229,33 @@
       <c r="A7" s="5">
         <v>202603012869</v>
       </c>
-      <c r="B7" s="13">
+      <c r="B7" s="10">
         <v>46082</v>
       </c>
       <c r="C7" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="D7" s="17"/>
-      <c r="E7" s="18"/>
+      <c r="D7" s="15"/>
+      <c r="E7" s="16"/>
       <c r="F7" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="G7" s="8">
+      <c r="G7" s="23">
         <v>0.59758100000000003</v>
       </c>
-      <c r="H7" s="9">
+      <c r="H7" s="24">
         <v>0.63924800000000004</v>
       </c>
-      <c r="I7" s="10">
+      <c r="I7" s="8">
         <v>35000</v>
       </c>
-      <c r="J7" s="11">
+      <c r="J7" s="9">
         <v>0</v>
       </c>
-      <c r="K7" s="10">
+      <c r="K7" s="8">
         <v>35000</v>
       </c>
-      <c r="L7" s="10">
+      <c r="L7" s="8">
         <v>35000</v>
       </c>
     </row>
@@ -1267,33 +1263,33 @@
       <c r="A8" s="5">
         <v>202603012870</v>
       </c>
-      <c r="B8" s="13">
+      <c r="B8" s="10">
         <v>46082</v>
       </c>
       <c r="C8" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="D8" s="17"/>
-      <c r="E8" s="18"/>
+      <c r="D8" s="15"/>
+      <c r="E8" s="16"/>
       <c r="F8" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="G8" s="8">
+      <c r="G8" s="23">
         <v>0.60011599999999998</v>
       </c>
-      <c r="H8" s="9">
+      <c r="H8" s="24">
         <v>0.66472200000000004</v>
       </c>
-      <c r="I8" s="10">
+      <c r="I8" s="8">
         <v>54219</v>
       </c>
-      <c r="J8" s="10">
+      <c r="J8" s="8">
         <v>5000</v>
       </c>
-      <c r="K8" s="10">
+      <c r="K8" s="8">
         <v>59219</v>
       </c>
-      <c r="L8" s="10">
+      <c r="L8" s="8">
         <v>59500</v>
       </c>
     </row>
@@ -1301,33 +1297,33 @@
       <c r="A9" s="5">
         <v>202603012871</v>
       </c>
-      <c r="B9" s="13">
+      <c r="B9" s="10">
         <v>46082</v>
       </c>
       <c r="C9" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="D9" s="17"/>
-      <c r="E9" s="18"/>
+      <c r="D9" s="15"/>
+      <c r="E9" s="16"/>
       <c r="F9" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="G9" s="8">
+      <c r="G9" s="23">
         <v>0.63158599999999998</v>
       </c>
-      <c r="H9" s="9">
+      <c r="H9" s="24">
         <v>0.71251200000000003</v>
       </c>
-      <c r="I9" s="10">
+      <c r="I9" s="8">
         <v>67628</v>
       </c>
-      <c r="J9" s="10">
+      <c r="J9" s="8">
         <v>40000</v>
       </c>
-      <c r="K9" s="10">
+      <c r="K9" s="8">
         <v>107628</v>
       </c>
-      <c r="L9" s="10">
+      <c r="L9" s="8">
         <v>108000</v>
       </c>
     </row>
@@ -1335,33 +1331,33 @@
       <c r="A10" s="5">
         <v>202603012872</v>
       </c>
-      <c r="B10" s="13">
+      <c r="B10" s="10">
         <v>46082</v>
       </c>
       <c r="C10" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="D10" s="17"/>
-      <c r="E10" s="18"/>
+      <c r="D10" s="15"/>
+      <c r="E10" s="16"/>
       <c r="F10" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="G10" s="8">
+      <c r="G10" s="23">
         <v>0.63957200000000003</v>
       </c>
-      <c r="H10" s="9">
+      <c r="H10" s="24">
         <v>0.68123800000000001</v>
       </c>
-      <c r="I10" s="10">
+      <c r="I10" s="8">
         <v>35000</v>
       </c>
-      <c r="J10" s="10">
+      <c r="J10" s="8">
         <v>20000</v>
       </c>
-      <c r="K10" s="10">
+      <c r="K10" s="8">
         <v>55000</v>
       </c>
-      <c r="L10" s="10">
+      <c r="L10" s="8">
         <v>55000</v>
       </c>
     </row>
@@ -1369,33 +1365,33 @@
       <c r="A11" s="5">
         <v>202603012873</v>
       </c>
-      <c r="B11" s="13">
+      <c r="B11" s="10">
         <v>46082</v>
       </c>
       <c r="C11" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="D11" s="17"/>
-      <c r="E11" s="18"/>
+      <c r="D11" s="15"/>
+      <c r="E11" s="16"/>
       <c r="F11" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="G11" s="8">
+      <c r="G11" s="23">
         <v>0.64502300000000001</v>
       </c>
-      <c r="H11" s="9">
+      <c r="H11" s="24">
         <v>0.83153900000000003</v>
       </c>
-      <c r="I11" s="10">
+      <c r="I11" s="8">
         <v>156244</v>
       </c>
-      <c r="J11" s="10">
+      <c r="J11" s="8">
         <v>5000</v>
       </c>
-      <c r="K11" s="10">
+      <c r="K11" s="8">
         <v>161244</v>
       </c>
-      <c r="L11" s="10">
+      <c r="L11" s="8">
         <v>161500</v>
       </c>
     </row>
@@ -1403,33 +1399,33 @@
       <c r="A12" s="5">
         <v>202603012874</v>
       </c>
-      <c r="B12" s="13">
+      <c r="B12" s="10">
         <v>46082</v>
       </c>
       <c r="C12" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="D12" s="17"/>
-      <c r="E12" s="18"/>
+      <c r="D12" s="15"/>
+      <c r="E12" s="16"/>
       <c r="F12" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="G12" s="8">
+      <c r="G12" s="23">
         <v>0.66379600000000005</v>
       </c>
-      <c r="H12" s="9">
+      <c r="H12" s="24">
         <v>0.76167799999999997</v>
       </c>
-      <c r="I12" s="10">
+      <c r="I12" s="8">
         <v>81620</v>
       </c>
-      <c r="J12" s="10">
+      <c r="J12" s="8">
         <v>35000</v>
       </c>
-      <c r="K12" s="10">
+      <c r="K12" s="8">
         <v>116620</v>
       </c>
-      <c r="L12" s="10">
+      <c r="L12" s="8">
         <v>117000</v>
       </c>
     </row>
@@ -1437,33 +1433,33 @@
       <c r="A13" s="5">
         <v>202603012875</v>
       </c>
-      <c r="B13" s="13">
+      <c r="B13" s="10">
         <v>46082</v>
       </c>
       <c r="C13" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="D13" s="17"/>
-      <c r="E13" s="18"/>
+      <c r="D13" s="15"/>
+      <c r="E13" s="16"/>
       <c r="F13" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="G13" s="8">
+      <c r="G13" s="23">
         <v>0.66718699999999997</v>
       </c>
-      <c r="H13" s="9">
+      <c r="H13" s="24">
         <v>0.70885399999999998</v>
       </c>
-      <c r="I13" s="10">
+      <c r="I13" s="8">
         <v>45000</v>
       </c>
-      <c r="J13" s="11">
+      <c r="J13" s="9">
         <v>0</v>
       </c>
-      <c r="K13" s="10">
+      <c r="K13" s="8">
         <v>45000</v>
       </c>
-      <c r="L13" s="10">
+      <c r="L13" s="8">
         <v>45000</v>
       </c>
     </row>
@@ -1471,33 +1467,33 @@
       <c r="A14" s="5">
         <v>202603012876</v>
       </c>
-      <c r="B14" s="13">
+      <c r="B14" s="10">
         <v>46082</v>
       </c>
       <c r="C14" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="D14" s="17"/>
-      <c r="E14" s="18"/>
+      <c r="D14" s="15"/>
+      <c r="E14" s="16"/>
       <c r="F14" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="G14" s="8">
+      <c r="G14" s="23">
         <v>0.67262699999999997</v>
       </c>
-      <c r="H14" s="9">
+      <c r="H14" s="24">
         <v>0.74916700000000003</v>
       </c>
-      <c r="I14" s="10">
+      <c r="I14" s="8">
         <v>82500</v>
       </c>
-      <c r="J14" s="11">
+      <c r="J14" s="9">
         <v>0</v>
       </c>
-      <c r="K14" s="10">
+      <c r="K14" s="8">
         <v>82500</v>
       </c>
-      <c r="L14" s="10">
+      <c r="L14" s="8">
         <v>82500</v>
       </c>
     </row>
@@ -1505,35 +1501,35 @@
       <c r="A15" s="5">
         <v>202603012877</v>
       </c>
-      <c r="B15" s="13">
+      <c r="B15" s="10">
         <v>46082</v>
       </c>
       <c r="C15" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="D15" s="23" t="s">
+      <c r="D15" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="E15" s="24"/>
+      <c r="E15" s="18"/>
       <c r="F15" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="G15" s="8">
+      <c r="G15" s="23">
         <v>0.67906200000000005</v>
       </c>
-      <c r="H15" s="9">
+      <c r="H15" s="24">
         <v>0.75284700000000004</v>
       </c>
-      <c r="I15" s="10">
+      <c r="I15" s="8">
         <v>71550</v>
       </c>
-      <c r="J15" s="11">
+      <c r="J15" s="9">
         <v>0</v>
       </c>
-      <c r="K15" s="10">
+      <c r="K15" s="8">
         <v>71550</v>
       </c>
-      <c r="L15" s="10">
+      <c r="L15" s="8">
         <v>72000</v>
       </c>
     </row>
@@ -1541,35 +1537,35 @@
       <c r="A16" s="5">
         <v>202603012878</v>
       </c>
-      <c r="B16" s="13">
+      <c r="B16" s="10">
         <v>46082</v>
       </c>
       <c r="C16" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="D16" s="23" t="s">
+      <c r="D16" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="E16" s="24"/>
+      <c r="E16" s="18"/>
       <c r="F16" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="G16" s="8">
+      <c r="G16" s="23">
         <v>0.68286999999999998</v>
       </c>
-      <c r="H16" s="9">
+      <c r="H16" s="24">
         <v>0.80718699999999999</v>
       </c>
-      <c r="I16" s="10">
+      <c r="I16" s="8">
         <v>120825</v>
       </c>
-      <c r="J16" s="11">
+      <c r="J16" s="9">
         <v>0</v>
       </c>
-      <c r="K16" s="10">
+      <c r="K16" s="8">
         <v>120825</v>
       </c>
-      <c r="L16" s="10">
+      <c r="L16" s="8">
         <v>121000</v>
       </c>
     </row>
@@ -1577,33 +1573,33 @@
       <c r="A17" s="5">
         <v>202603012879</v>
       </c>
-      <c r="B17" s="13">
+      <c r="B17" s="10">
         <v>46082</v>
       </c>
       <c r="C17" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="D17" s="17"/>
-      <c r="E17" s="18"/>
+      <c r="D17" s="15"/>
+      <c r="E17" s="16"/>
       <c r="F17" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="G17" s="8">
+      <c r="G17" s="23">
         <v>0.78545100000000001</v>
       </c>
-      <c r="H17" s="9">
+      <c r="H17" s="24">
         <v>0.93947899999999995</v>
       </c>
-      <c r="I17" s="10">
+      <c r="I17" s="8">
         <v>165750</v>
       </c>
-      <c r="J17" s="10">
+      <c r="J17" s="8">
         <v>70000</v>
       </c>
-      <c r="K17" s="10">
+      <c r="K17" s="8">
         <v>235750</v>
       </c>
-      <c r="L17" s="10">
+      <c r="L17" s="8">
         <v>236000</v>
       </c>
     </row>
@@ -1611,33 +1607,33 @@
       <c r="A18" s="5">
         <v>202603012880</v>
       </c>
-      <c r="B18" s="13">
+      <c r="B18" s="10">
         <v>46082</v>
       </c>
       <c r="C18" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="D18" s="17"/>
-      <c r="E18" s="18"/>
+      <c r="D18" s="15"/>
+      <c r="E18" s="16"/>
       <c r="F18" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="G18" s="8">
+      <c r="G18" s="23">
         <v>0.80120400000000003</v>
       </c>
-      <c r="H18" s="9">
+      <c r="H18" s="24">
         <v>0.88453700000000002</v>
       </c>
-      <c r="I18" s="10">
+      <c r="I18" s="8">
         <v>90000</v>
       </c>
-      <c r="J18" s="10">
+      <c r="J18" s="8">
         <v>36000</v>
       </c>
-      <c r="K18" s="10">
+      <c r="K18" s="8">
         <v>126000</v>
       </c>
-      <c r="L18" s="10">
+      <c r="L18" s="8">
         <v>126000</v>
       </c>
     </row>
@@ -1645,33 +1641,33 @@
       <c r="A19" s="5">
         <v>202603012881</v>
       </c>
-      <c r="B19" s="13">
+      <c r="B19" s="10">
         <v>46082</v>
       </c>
       <c r="C19" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="D19" s="17"/>
-      <c r="E19" s="18"/>
+      <c r="D19" s="15"/>
+      <c r="E19" s="16"/>
       <c r="F19" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="G19" s="8">
+      <c r="G19" s="23">
         <v>0.807361</v>
       </c>
-      <c r="H19" s="9">
+      <c r="H19" s="24">
         <v>0.89278900000000005</v>
       </c>
-      <c r="I19" s="10">
+      <c r="I19" s="8">
         <v>92250</v>
       </c>
-      <c r="J19" s="10">
+      <c r="J19" s="8">
         <v>10000</v>
       </c>
-      <c r="K19" s="10">
+      <c r="K19" s="8">
         <v>102250</v>
       </c>
-      <c r="L19" s="10">
+      <c r="L19" s="8">
         <v>102500</v>
       </c>
     </row>
@@ -1679,33 +1675,33 @@
       <c r="A20" s="5">
         <v>202603012882</v>
       </c>
-      <c r="B20" s="13">
+      <c r="B20" s="10">
         <v>46082</v>
       </c>
       <c r="C20" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="17"/>
-      <c r="E20" s="18"/>
+      <c r="D20" s="15"/>
+      <c r="E20" s="16"/>
       <c r="F20" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="G20" s="8">
+      <c r="G20" s="23">
         <v>0.8075</v>
       </c>
-      <c r="H20" s="9">
+      <c r="H20" s="24">
         <v>0.89267399999999997</v>
       </c>
-      <c r="I20" s="10">
+      <c r="I20" s="8">
         <v>91500</v>
       </c>
-      <c r="J20" s="10">
+      <c r="J20" s="8">
         <v>28000</v>
       </c>
-      <c r="K20" s="10">
+      <c r="K20" s="8">
         <v>119500</v>
       </c>
-      <c r="L20" s="10">
+      <c r="L20" s="8">
         <v>119500</v>
       </c>
     </row>
@@ -1713,35 +1709,35 @@
       <c r="A21" s="5">
         <v>202603012883</v>
       </c>
-      <c r="B21" s="13">
+      <c r="B21" s="10">
         <v>46082</v>
       </c>
       <c r="C21" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="D21" s="23" t="s">
+      <c r="D21" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="E21" s="24"/>
+      <c r="E21" s="18"/>
       <c r="F21" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="G21" s="8">
+      <c r="G21" s="23">
         <v>0.80957199999999996</v>
       </c>
-      <c r="H21" s="9">
+      <c r="H21" s="24">
         <v>0.875162</v>
       </c>
-      <c r="I21" s="10">
+      <c r="I21" s="8">
         <v>63450</v>
       </c>
-      <c r="J21" s="11">
+      <c r="J21" s="9">
         <v>0</v>
       </c>
-      <c r="K21" s="10">
+      <c r="K21" s="8">
         <v>63450</v>
       </c>
-      <c r="L21" s="10">
+      <c r="L21" s="8">
         <v>63500</v>
       </c>
     </row>
@@ -1749,33 +1745,33 @@
       <c r="A22" s="5">
         <v>202603012884</v>
       </c>
-      <c r="B22" s="13">
+      <c r="B22" s="10">
         <v>46082</v>
       </c>
       <c r="C22" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="D22" s="17"/>
-      <c r="E22" s="18"/>
+      <c r="D22" s="15"/>
+      <c r="E22" s="16"/>
       <c r="F22" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="G22" s="8">
+      <c r="G22" s="23">
         <v>0.81082200000000004</v>
       </c>
-      <c r="H22" s="12">
+      <c r="H22" s="25">
         <v>0.89415500000000003</v>
       </c>
-      <c r="I22" s="10">
+      <c r="I22" s="8">
         <v>90000</v>
       </c>
-      <c r="J22" s="10">
+      <c r="J22" s="8">
         <v>30000</v>
       </c>
-      <c r="K22" s="10">
+      <c r="K22" s="8">
         <v>120000</v>
       </c>
-      <c r="L22" s="10">
+      <c r="L22" s="8">
         <v>120000</v>
       </c>
     </row>
@@ -1783,33 +1779,33 @@
       <c r="A23" s="5">
         <v>202603012885</v>
       </c>
-      <c r="B23" s="13">
+      <c r="B23" s="10">
         <v>46082</v>
       </c>
       <c r="C23" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="D23" s="17"/>
-      <c r="E23" s="18"/>
+      <c r="D23" s="15"/>
+      <c r="E23" s="16"/>
       <c r="F23" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="G23" s="8">
+      <c r="G23" s="23">
         <v>0.81592600000000004</v>
       </c>
-      <c r="H23" s="12">
+      <c r="H23" s="25">
         <v>0.90855300000000006</v>
       </c>
-      <c r="I23" s="10">
+      <c r="I23" s="8">
         <v>99750</v>
       </c>
-      <c r="J23" s="10">
+      <c r="J23" s="8">
         <v>16000</v>
       </c>
-      <c r="K23" s="10">
+      <c r="K23" s="8">
         <v>115750</v>
       </c>
-      <c r="L23" s="10">
+      <c r="L23" s="8">
         <v>116000</v>
       </c>
     </row>
@@ -1817,33 +1813,33 @@
       <c r="A24" s="5">
         <v>202603012886</v>
       </c>
-      <c r="B24" s="13">
+      <c r="B24" s="10">
         <v>46082</v>
       </c>
       <c r="C24" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="D24" s="17"/>
-      <c r="E24" s="18"/>
+      <c r="D24" s="15"/>
+      <c r="E24" s="16"/>
       <c r="F24" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="G24" s="8">
+      <c r="G24" s="23">
         <v>0.83721100000000004</v>
       </c>
-      <c r="H24" s="12">
+      <c r="H24" s="25">
         <v>0.87887700000000002</v>
       </c>
-      <c r="I24" s="10">
+      <c r="I24" s="8">
         <v>45000</v>
       </c>
-      <c r="J24" s="11">
+      <c r="J24" s="9">
         <v>0</v>
       </c>
-      <c r="K24" s="10">
+      <c r="K24" s="8">
         <v>45000</v>
       </c>
-      <c r="L24" s="10">
+      <c r="L24" s="8">
         <v>45000</v>
       </c>
     </row>
@@ -1851,33 +1847,33 @@
       <c r="A25" s="5">
         <v>202603012887</v>
       </c>
-      <c r="B25" s="13">
+      <c r="B25" s="10">
         <v>46082</v>
       </c>
       <c r="C25" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="D25" s="17"/>
-      <c r="E25" s="18"/>
+      <c r="D25" s="15"/>
+      <c r="E25" s="16"/>
       <c r="F25" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="G25" s="8">
+      <c r="G25" s="23">
         <v>0.83736100000000002</v>
       </c>
-      <c r="H25" s="12">
+      <c r="H25" s="25">
         <v>0.87902800000000003</v>
       </c>
-      <c r="I25" s="10">
+      <c r="I25" s="8">
         <v>45000</v>
       </c>
-      <c r="J25" s="11">
+      <c r="J25" s="9">
         <v>0</v>
       </c>
-      <c r="K25" s="10">
+      <c r="K25" s="8">
         <v>45000</v>
       </c>
-      <c r="L25" s="10">
+      <c r="L25" s="8">
         <v>45000</v>
       </c>
     </row>
@@ -1885,35 +1881,35 @@
       <c r="A26" s="5">
         <v>202603012888</v>
       </c>
-      <c r="B26" s="13">
+      <c r="B26" s="10">
         <v>46082</v>
       </c>
       <c r="C26" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="D26" s="21" t="s">
+      <c r="D26" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="E26" s="22"/>
+      <c r="E26" s="20"/>
       <c r="F26" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="G26" s="8">
+      <c r="G26" s="23">
         <v>0.84181700000000004</v>
       </c>
-      <c r="H26" s="12">
+      <c r="H26" s="25">
         <v>0.94203700000000001</v>
       </c>
-      <c r="I26" s="10">
+      <c r="I26" s="8">
         <v>97200</v>
       </c>
-      <c r="J26" s="10">
+      <c r="J26" s="8">
         <v>25000</v>
       </c>
-      <c r="K26" s="10">
+      <c r="K26" s="8">
         <v>122200</v>
       </c>
-      <c r="L26" s="10">
+      <c r="L26" s="8">
         <v>122500</v>
       </c>
     </row>
@@ -1921,33 +1917,33 @@
       <c r="A27" s="5">
         <v>202603012889</v>
       </c>
-      <c r="B27" s="13">
+      <c r="B27" s="10">
         <v>46082</v>
       </c>
       <c r="C27" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="D27" s="17"/>
-      <c r="E27" s="18"/>
+      <c r="D27" s="15"/>
+      <c r="E27" s="16"/>
       <c r="F27" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="G27" s="8">
+      <c r="G27" s="23">
         <v>0.84920099999999998</v>
       </c>
-      <c r="H27" s="12">
+      <c r="H27" s="25">
         <v>0.932535</v>
       </c>
-      <c r="I27" s="10">
+      <c r="I27" s="8">
         <v>90000</v>
       </c>
-      <c r="J27" s="10">
+      <c r="J27" s="8">
         <v>20000</v>
       </c>
-      <c r="K27" s="10">
+      <c r="K27" s="8">
         <v>110000</v>
       </c>
-      <c r="L27" s="10">
+      <c r="L27" s="8">
         <v>110000</v>
       </c>
     </row>
@@ -1955,33 +1951,33 @@
       <c r="A28" s="5">
         <v>202603012890</v>
       </c>
-      <c r="B28" s="13">
+      <c r="B28" s="10">
         <v>46082</v>
       </c>
       <c r="C28" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="D28" s="17"/>
-      <c r="E28" s="18"/>
+      <c r="D28" s="15"/>
+      <c r="E28" s="16"/>
       <c r="F28" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="G28" s="8">
+      <c r="G28" s="23">
         <v>0.87590299999999999</v>
       </c>
-      <c r="H28" s="12">
+      <c r="H28" s="25">
         <v>0.97043999999999997</v>
       </c>
-      <c r="I28" s="10">
+      <c r="I28" s="8">
         <v>102000</v>
       </c>
-      <c r="J28" s="11">
+      <c r="J28" s="9">
         <v>0</v>
       </c>
-      <c r="K28" s="10">
+      <c r="K28" s="8">
         <v>102000</v>
       </c>
-      <c r="L28" s="10">
+      <c r="L28" s="8">
         <v>102000</v>
       </c>
     </row>
@@ -1989,33 +1985,33 @@
       <c r="A29" s="5">
         <v>202603012891</v>
       </c>
-      <c r="B29" s="13">
+      <c r="B29" s="10">
         <v>46083</v>
       </c>
       <c r="C29" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="D29" s="17"/>
-      <c r="E29" s="18"/>
+      <c r="D29" s="15"/>
+      <c r="E29" s="16"/>
       <c r="F29" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="G29" s="8">
+      <c r="G29" s="23">
         <v>0.88721099999999997</v>
       </c>
-      <c r="H29" s="12">
+      <c r="H29" s="25">
         <v>2.6088E-2</v>
       </c>
-      <c r="I29" s="10">
+      <c r="I29" s="8">
         <v>149250</v>
       </c>
-      <c r="J29" s="11">
+      <c r="J29" s="9">
         <v>0</v>
       </c>
-      <c r="K29" s="10">
+      <c r="K29" s="8">
         <v>149250</v>
       </c>
-      <c r="L29" s="10">
+      <c r="L29" s="8">
         <v>149500</v>
       </c>
     </row>
@@ -2023,35 +2019,35 @@
       <c r="A30" s="5">
         <v>202603012892</v>
       </c>
-      <c r="B30" s="13">
+      <c r="B30" s="10">
         <v>46083</v>
       </c>
       <c r="C30" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="D30" s="21" t="s">
+      <c r="D30" s="19" t="s">
         <v>27</v>
       </c>
-      <c r="E30" s="22"/>
+      <c r="E30" s="20"/>
       <c r="F30" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="G30" s="8">
+      <c r="G30" s="23">
         <v>0.89483800000000002</v>
       </c>
-      <c r="H30" s="12">
+      <c r="H30" s="25">
         <v>4.2025E-2</v>
       </c>
-      <c r="I30" s="10">
+      <c r="I30" s="8">
         <v>142425</v>
       </c>
-      <c r="J30" s="10">
+      <c r="J30" s="8">
         <v>46000</v>
       </c>
-      <c r="K30" s="10">
+      <c r="K30" s="8">
         <v>188425</v>
       </c>
-      <c r="L30" s="10">
+      <c r="L30" s="8">
         <v>188500</v>
       </c>
     </row>
@@ -2059,35 +2055,35 @@
       <c r="A31" s="5">
         <v>202603012893</v>
       </c>
-      <c r="B31" s="13">
+      <c r="B31" s="10">
         <v>46083</v>
       </c>
       <c r="C31" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="D31" s="21" t="s">
+      <c r="D31" s="19" t="s">
         <v>28</v>
       </c>
-      <c r="E31" s="22"/>
+      <c r="E31" s="20"/>
       <c r="F31" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="G31" s="8">
+      <c r="G31" s="23">
         <v>0.89491900000000002</v>
       </c>
-      <c r="H31" s="12">
+      <c r="H31" s="25">
         <v>4.0903000000000002E-2</v>
       </c>
-      <c r="I31" s="10">
+      <c r="I31" s="8">
         <v>141750</v>
       </c>
-      <c r="J31" s="10">
+      <c r="J31" s="8">
         <v>20000</v>
       </c>
-      <c r="K31" s="10">
+      <c r="K31" s="8">
         <v>161750</v>
       </c>
-      <c r="L31" s="10">
+      <c r="L31" s="8">
         <v>162000</v>
       </c>
     </row>
@@ -2095,35 +2091,35 @@
       <c r="A32" s="5">
         <v>202603012894</v>
       </c>
-      <c r="B32" s="13">
+      <c r="B32" s="10">
         <v>46083</v>
       </c>
       <c r="C32" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="D32" s="21" t="s">
+      <c r="D32" s="19" t="s">
         <v>22</v>
       </c>
-      <c r="E32" s="22"/>
+      <c r="E32" s="20"/>
       <c r="F32" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="G32" s="8">
+      <c r="G32" s="23">
         <v>0.89501200000000003</v>
       </c>
-      <c r="H32" s="12">
+      <c r="H32" s="25">
         <v>4.1944000000000002E-2</v>
       </c>
-      <c r="I32" s="10">
+      <c r="I32" s="8">
         <v>142425</v>
       </c>
-      <c r="J32" s="10">
+      <c r="J32" s="8">
         <v>60000</v>
       </c>
-      <c r="K32" s="10">
+      <c r="K32" s="8">
         <v>202425</v>
       </c>
-      <c r="L32" s="10">
+      <c r="L32" s="8">
         <v>202500</v>
       </c>
     </row>
@@ -2131,33 +2127,33 @@
       <c r="A33" s="5">
         <v>202603012895</v>
       </c>
-      <c r="B33" s="13">
+      <c r="B33" s="10">
         <v>46083</v>
       </c>
       <c r="C33" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="D33" s="17"/>
-      <c r="E33" s="18"/>
+      <c r="D33" s="15"/>
+      <c r="E33" s="16"/>
       <c r="F33" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="G33" s="8">
+      <c r="G33" s="23">
         <v>0.90634300000000001</v>
       </c>
-      <c r="H33" s="12">
+      <c r="H33" s="25">
         <v>0.94800899999999999</v>
       </c>
-      <c r="I33" s="10">
+      <c r="I33" s="8">
         <v>45000</v>
       </c>
-      <c r="J33" s="10">
+      <c r="J33" s="8">
         <v>5000</v>
       </c>
-      <c r="K33" s="10">
+      <c r="K33" s="8">
         <v>50000</v>
       </c>
-      <c r="L33" s="10">
+      <c r="L33" s="8">
         <v>50000</v>
       </c>
     </row>
@@ -2165,33 +2161,33 @@
       <c r="A34" s="5">
         <v>202603012896</v>
       </c>
-      <c r="B34" s="13">
+      <c r="B34" s="10">
         <v>46083</v>
       </c>
       <c r="C34" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="D34" s="17"/>
-      <c r="E34" s="18"/>
+      <c r="D34" s="15"/>
+      <c r="E34" s="16"/>
       <c r="F34" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="G34" s="8">
+      <c r="G34" s="23">
         <v>0.91400499999999996</v>
       </c>
-      <c r="H34" s="12">
+      <c r="H34" s="25">
         <v>0.98011599999999999</v>
       </c>
-      <c r="I34" s="10">
+      <c r="I34" s="8">
         <v>71250</v>
       </c>
-      <c r="J34" s="10">
+      <c r="J34" s="8">
         <v>32000</v>
       </c>
-      <c r="K34" s="10">
+      <c r="K34" s="8">
         <v>103250</v>
       </c>
-      <c r="L34" s="10">
+      <c r="L34" s="8">
         <v>103500</v>
       </c>
     </row>
@@ -2199,33 +2195,33 @@
       <c r="A35" s="5">
         <v>202603012897</v>
       </c>
-      <c r="B35" s="13">
+      <c r="B35" s="10">
         <v>46083</v>
       </c>
       <c r="C35" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="D35" s="17"/>
-      <c r="E35" s="18"/>
+      <c r="D35" s="15"/>
+      <c r="E35" s="16"/>
       <c r="F35" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="G35" s="8">
+      <c r="G35" s="23">
         <v>0.93620400000000004</v>
       </c>
-      <c r="H35" s="12">
+      <c r="H35" s="25">
         <v>4.2049000000000003E-2</v>
       </c>
-      <c r="I35" s="10">
+      <c r="I35" s="8">
         <v>114000</v>
       </c>
-      <c r="J35" s="10">
+      <c r="J35" s="8">
         <v>23000</v>
       </c>
-      <c r="K35" s="10">
+      <c r="K35" s="8">
         <v>137000</v>
       </c>
-      <c r="L35" s="10">
+      <c r="L35" s="8">
         <v>137000</v>
       </c>
     </row>
@@ -2233,33 +2229,33 @@
       <c r="A36" s="5">
         <v>202603012898</v>
       </c>
-      <c r="B36" s="13">
+      <c r="B36" s="10">
         <v>46083</v>
       </c>
       <c r="C36" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="D36" s="17"/>
-      <c r="E36" s="18"/>
+      <c r="D36" s="15"/>
+      <c r="E36" s="16"/>
       <c r="F36" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="G36" s="8">
+      <c r="G36" s="23">
         <v>0.95109999999999995</v>
       </c>
-      <c r="H36" s="12">
+      <c r="H36" s="25">
         <v>3.4432999999999998E-2</v>
       </c>
-      <c r="I36" s="10">
+      <c r="I36" s="8">
         <v>90000</v>
       </c>
-      <c r="J36" s="10">
+      <c r="J36" s="8">
         <v>20000</v>
       </c>
-      <c r="K36" s="10">
+      <c r="K36" s="8">
         <v>110000</v>
       </c>
-      <c r="L36" s="10">
+      <c r="L36" s="8">
         <v>110000</v>
       </c>
     </row>
@@ -2267,33 +2263,33 @@
       <c r="A37" s="5">
         <v>202603012899</v>
       </c>
-      <c r="B37" s="13">
+      <c r="B37" s="10">
         <v>46083</v>
       </c>
       <c r="C37" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="D37" s="17"/>
-      <c r="E37" s="18"/>
+      <c r="D37" s="15"/>
+      <c r="E37" s="16"/>
       <c r="F37" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="G37" s="8">
+      <c r="G37" s="23">
         <v>0.95123800000000003</v>
       </c>
-      <c r="H37" s="12">
+      <c r="H37" s="25">
         <v>4.1991000000000001E-2</v>
       </c>
-      <c r="I37" s="10">
+      <c r="I37" s="8">
         <v>97500</v>
       </c>
-      <c r="J37" s="10">
+      <c r="J37" s="8">
         <v>25000</v>
       </c>
-      <c r="K37" s="10">
+      <c r="K37" s="8">
         <v>122500</v>
       </c>
-      <c r="L37" s="10">
+      <c r="L37" s="8">
         <v>122500</v>
       </c>
     </row>
@@ -2301,33 +2297,33 @@
       <c r="A38" s="5">
         <v>202603012900</v>
       </c>
-      <c r="B38" s="13">
+      <c r="B38" s="10">
         <v>46083</v>
       </c>
       <c r="C38" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="D38" s="17"/>
-      <c r="E38" s="18"/>
+      <c r="D38" s="15"/>
+      <c r="E38" s="16"/>
       <c r="F38" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="G38" s="8">
+      <c r="G38" s="23">
         <v>0.95736100000000002</v>
       </c>
-      <c r="H38" s="12">
+      <c r="H38" s="25">
         <v>4.2014000000000003E-2</v>
       </c>
-      <c r="I38" s="10">
+      <c r="I38" s="8">
         <v>90750</v>
       </c>
-      <c r="J38" s="10">
+      <c r="J38" s="8">
         <v>20000</v>
       </c>
-      <c r="K38" s="10">
+      <c r="K38" s="8">
         <v>110750</v>
       </c>
-      <c r="L38" s="10">
+      <c r="L38" s="8">
         <v>111000</v>
       </c>
     </row>
@@ -2335,33 +2331,33 @@
       <c r="A39" s="5">
         <v>202603012901</v>
       </c>
-      <c r="B39" s="13">
+      <c r="B39" s="10">
         <v>46083</v>
       </c>
       <c r="C39" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="D39" s="17"/>
-      <c r="E39" s="18"/>
+      <c r="D39" s="15"/>
+      <c r="E39" s="16"/>
       <c r="F39" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="G39" s="8">
+      <c r="G39" s="23">
         <v>0.97253500000000004</v>
       </c>
-      <c r="H39" s="12">
+      <c r="H39" s="25">
         <v>1.3079999999999999E-3</v>
       </c>
-      <c r="I39" s="10">
+      <c r="I39" s="8">
         <v>45000</v>
       </c>
-      <c r="J39" s="11">
+      <c r="J39" s="9">
         <v>0</v>
       </c>
-      <c r="K39" s="10">
+      <c r="K39" s="8">
         <v>45000</v>
       </c>
-      <c r="L39" s="10">
+      <c r="L39" s="8">
         <v>45000</v>
       </c>
     </row>
@@ -2369,33 +2365,33 @@
       <c r="A40" s="5">
         <v>202603012902</v>
       </c>
-      <c r="B40" s="13">
+      <c r="B40" s="10">
         <v>46083</v>
       </c>
       <c r="C40" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="D40" s="17"/>
-      <c r="E40" s="18"/>
+      <c r="D40" s="15"/>
+      <c r="E40" s="16"/>
       <c r="F40" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="G40" s="8">
+      <c r="G40" s="23">
         <v>0.97442099999999998</v>
       </c>
-      <c r="H40" s="12">
+      <c r="H40" s="25">
         <v>4.1967999999999998E-2</v>
       </c>
-      <c r="I40" s="10">
+      <c r="I40" s="8">
         <v>72750</v>
       </c>
-      <c r="J40" s="10">
+      <c r="J40" s="8">
         <v>20000</v>
       </c>
-      <c r="K40" s="10">
+      <c r="K40" s="8">
         <v>92750</v>
       </c>
-      <c r="L40" s="10">
+      <c r="L40" s="8">
         <v>93000</v>
       </c>
     </row>
@@ -2403,33 +2399,33 @@
       <c r="A41" s="5">
         <v>202603012903</v>
       </c>
-      <c r="B41" s="13">
+      <c r="B41" s="10">
         <v>46083</v>
       </c>
       <c r="C41" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="D41" s="17"/>
-      <c r="E41" s="18"/>
+      <c r="D41" s="15"/>
+      <c r="E41" s="16"/>
       <c r="F41" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="G41" s="8">
+      <c r="G41" s="23">
         <v>0.984259</v>
       </c>
-      <c r="H41" s="12">
+      <c r="H41" s="25">
         <v>2.5926000000000001E-2</v>
       </c>
-      <c r="I41" s="10">
+      <c r="I41" s="8">
         <v>45000</v>
       </c>
-      <c r="J41" s="11">
+      <c r="J41" s="9">
         <v>0</v>
       </c>
-      <c r="K41" s="10">
+      <c r="K41" s="8">
         <v>45000</v>
       </c>
-      <c r="L41" s="10">
+      <c r="L41" s="8">
         <v>45000</v>
       </c>
     </row>
@@ -2437,407 +2433,407 @@
       <c r="A42" s="5">
         <v>202603022904</v>
       </c>
-      <c r="B42" s="13">
+      <c r="B42" s="10">
         <v>46083</v>
       </c>
       <c r="C42" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="D42" s="17"/>
-      <c r="E42" s="18"/>
+      <c r="D42" s="15"/>
+      <c r="E42" s="16"/>
       <c r="F42" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="G42" s="8">
+      <c r="G42" s="23">
         <v>1.2881999999999999E-2</v>
       </c>
-      <c r="H42" s="12">
+      <c r="H42" s="25">
         <v>4.2071999999999998E-2</v>
       </c>
-      <c r="I42" s="10">
+      <c r="I42" s="8">
         <v>45000</v>
       </c>
-      <c r="J42" s="11">
+      <c r="J42" s="9">
         <v>0</v>
       </c>
-      <c r="K42" s="10">
+      <c r="K42" s="8">
         <v>45000</v>
       </c>
-      <c r="L42" s="10">
+      <c r="L42" s="8">
         <v>45000</v>
       </c>
     </row>
     <row r="43" spans="1:12" ht="14" x14ac:dyDescent="0.15">
-      <c r="A43" s="14">
+      <c r="A43" s="11">
         <v>20260301843</v>
       </c>
-      <c r="B43" s="13">
+      <c r="B43" s="10">
         <v>46082</v>
       </c>
       <c r="C43" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="D43" s="17"/>
-      <c r="E43" s="18"/>
+      <c r="D43" s="15"/>
+      <c r="E43" s="16"/>
       <c r="F43" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="G43" s="15">
+        <v>33</v>
+      </c>
+      <c r="G43" s="26">
         <v>0.63826400000000005</v>
       </c>
-      <c r="H43" s="8">
+      <c r="H43" s="23">
         <v>0.697546</v>
       </c>
-      <c r="I43" s="10">
+      <c r="I43" s="8">
         <v>49555</v>
       </c>
-      <c r="J43" s="11">
+      <c r="J43" s="9">
         <v>0</v>
       </c>
-      <c r="K43" s="10">
+      <c r="K43" s="8">
         <v>49555</v>
       </c>
-      <c r="L43" s="16">
+      <c r="L43" s="12">
         <v>50000</v>
       </c>
     </row>
     <row r="44" spans="1:12" ht="14" x14ac:dyDescent="0.15">
-      <c r="A44" s="14">
+      <c r="A44" s="11">
         <v>20260301844</v>
       </c>
-      <c r="B44" s="13">
+      <c r="B44" s="10">
         <v>46082</v>
       </c>
       <c r="C44" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="D44" s="17"/>
-      <c r="E44" s="18"/>
+      <c r="D44" s="15"/>
+      <c r="E44" s="16"/>
       <c r="F44" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="G44" s="15">
+      <c r="G44" s="26">
         <v>0.67366899999999996</v>
       </c>
-      <c r="H44" s="8">
+      <c r="H44" s="23">
         <v>0.83510399999999996</v>
       </c>
-      <c r="I44" s="10">
+      <c r="I44" s="8">
         <v>174000</v>
       </c>
-      <c r="J44" s="10">
+      <c r="J44" s="8">
         <v>62000</v>
       </c>
-      <c r="K44" s="10">
+      <c r="K44" s="8">
         <v>236000</v>
       </c>
-      <c r="L44" s="16">
+      <c r="L44" s="12">
         <v>236000</v>
       </c>
     </row>
     <row r="45" spans="1:12" ht="14" x14ac:dyDescent="0.15">
-      <c r="A45" s="14">
+      <c r="A45" s="11">
         <v>20260301845</v>
       </c>
-      <c r="B45" s="13">
+      <c r="B45" s="10">
         <v>46082</v>
       </c>
       <c r="C45" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="D45" s="17"/>
-      <c r="E45" s="18"/>
+      <c r="D45" s="15"/>
+      <c r="E45" s="16"/>
       <c r="F45" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="G45" s="15">
+      <c r="G45" s="26">
         <v>0.693519</v>
       </c>
-      <c r="H45" s="8">
+      <c r="H45" s="23">
         <v>0.74922500000000003</v>
       </c>
-      <c r="I45" s="10">
+      <c r="I45" s="8">
         <v>60000</v>
       </c>
-      <c r="J45" s="11">
+      <c r="J45" s="9">
         <v>0</v>
       </c>
-      <c r="K45" s="10">
+      <c r="K45" s="8">
         <v>60000</v>
       </c>
-      <c r="L45" s="16">
+      <c r="L45" s="12">
         <v>60000</v>
       </c>
     </row>
     <row r="46" spans="1:12" ht="14" x14ac:dyDescent="0.15">
-      <c r="A46" s="14">
+      <c r="A46" s="11">
         <v>20260301846</v>
       </c>
-      <c r="B46" s="13">
+      <c r="B46" s="10">
         <v>46082</v>
       </c>
       <c r="C46" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="D46" s="17"/>
-      <c r="E46" s="18"/>
+      <c r="D46" s="15"/>
+      <c r="E46" s="16"/>
       <c r="F46" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="G46" s="15">
+      <c r="G46" s="26">
         <v>0.72903899999999999</v>
       </c>
-      <c r="H46" s="8">
+      <c r="H46" s="23">
         <v>0.770706</v>
       </c>
-      <c r="I46" s="10">
+      <c r="I46" s="8">
         <v>45000</v>
       </c>
-      <c r="J46" s="11">
+      <c r="J46" s="9">
         <v>0</v>
       </c>
-      <c r="K46" s="10">
+      <c r="K46" s="8">
         <v>45000</v>
       </c>
-      <c r="L46" s="16">
+      <c r="L46" s="12">
         <v>45000</v>
       </c>
     </row>
     <row r="47" spans="1:12" ht="14" x14ac:dyDescent="0.15">
-      <c r="A47" s="14">
+      <c r="A47" s="11">
         <v>20260301847</v>
       </c>
-      <c r="B47" s="13">
+      <c r="B47" s="10">
         <v>46082</v>
       </c>
       <c r="C47" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="D47" s="17"/>
-      <c r="E47" s="18"/>
+      <c r="D47" s="15"/>
+      <c r="E47" s="16"/>
       <c r="F47" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="G47" s="15">
+      <c r="G47" s="26">
         <v>0.80446799999999996</v>
       </c>
-      <c r="H47" s="8">
+      <c r="H47" s="23">
         <v>0.88780099999999995</v>
       </c>
-      <c r="I47" s="10">
+      <c r="I47" s="8">
         <v>90000</v>
       </c>
-      <c r="J47" s="10">
+      <c r="J47" s="8">
         <v>15000</v>
       </c>
-      <c r="K47" s="10">
+      <c r="K47" s="8">
         <v>105000</v>
       </c>
-      <c r="L47" s="16">
+      <c r="L47" s="12">
         <v>105000</v>
       </c>
     </row>
     <row r="48" spans="1:12" ht="14" x14ac:dyDescent="0.15">
-      <c r="A48" s="14">
+      <c r="A48" s="11">
         <v>20260301848</v>
       </c>
-      <c r="B48" s="13">
+      <c r="B48" s="10">
         <v>46082</v>
       </c>
       <c r="C48" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="D48" s="17"/>
-      <c r="E48" s="18"/>
+      <c r="D48" s="15"/>
+      <c r="E48" s="16"/>
       <c r="F48" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="G48" s="15">
+      <c r="G48" s="26">
         <v>0.81403899999999996</v>
       </c>
-      <c r="H48" s="8">
+      <c r="H48" s="23">
         <v>0.89737299999999998</v>
       </c>
-      <c r="I48" s="10">
+      <c r="I48" s="8">
         <v>90000</v>
       </c>
-      <c r="J48" s="10">
+      <c r="J48" s="8">
         <v>34000</v>
       </c>
-      <c r="K48" s="10">
+      <c r="K48" s="8">
         <v>124000</v>
       </c>
-      <c r="L48" s="16">
+      <c r="L48" s="12">
         <v>124000</v>
       </c>
     </row>
     <row r="49" spans="1:12" ht="14" x14ac:dyDescent="0.15">
-      <c r="A49" s="14">
+      <c r="A49" s="11">
         <v>20260301849</v>
       </c>
-      <c r="B49" s="13">
+      <c r="B49" s="10">
         <v>46082</v>
       </c>
       <c r="C49" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="D49" s="17"/>
-      <c r="E49" s="18"/>
+        <v>45</v>
+      </c>
+      <c r="D49" s="15"/>
+      <c r="E49" s="16"/>
       <c r="F49" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="G49" s="15">
+      <c r="G49" s="26">
         <v>0.838785</v>
       </c>
-      <c r="H49" s="8">
+      <c r="H49" s="23">
         <v>0.99857600000000002</v>
       </c>
-      <c r="I49" s="10">
+      <c r="I49" s="8">
         <v>172500</v>
       </c>
-      <c r="J49" s="10">
+      <c r="J49" s="8">
         <v>35000</v>
       </c>
-      <c r="K49" s="10">
+      <c r="K49" s="8">
         <v>207500</v>
       </c>
-      <c r="L49" s="16">
+      <c r="L49" s="12">
         <v>207500</v>
       </c>
     </row>
     <row r="50" spans="1:12" ht="14" x14ac:dyDescent="0.15">
-      <c r="A50" s="14">
+      <c r="A50" s="11">
         <v>20260301850</v>
       </c>
-      <c r="B50" s="13">
+      <c r="B50" s="10">
         <v>46083</v>
       </c>
       <c r="C50" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="D50" s="17"/>
-      <c r="E50" s="18"/>
+      <c r="D50" s="15"/>
+      <c r="E50" s="16"/>
       <c r="F50" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="G50" s="15">
+      <c r="G50" s="26">
         <v>0.84087999999999996</v>
       </c>
-      <c r="H50" s="8">
+      <c r="H50" s="23">
         <v>3.0173999999999999E-2</v>
       </c>
-      <c r="I50" s="10">
+      <c r="I50" s="8">
         <v>204000</v>
       </c>
-      <c r="J50" s="10">
+      <c r="J50" s="8">
         <v>66000</v>
       </c>
-      <c r="K50" s="10">
+      <c r="K50" s="8">
         <v>270000</v>
       </c>
-      <c r="L50" s="16">
+      <c r="L50" s="12">
         <v>270000</v>
       </c>
     </row>
     <row r="51" spans="1:12" ht="14" x14ac:dyDescent="0.15">
-      <c r="A51" s="14">
+      <c r="A51" s="11">
         <v>20260301851</v>
       </c>
-      <c r="B51" s="13">
+      <c r="B51" s="10">
         <v>46082</v>
       </c>
       <c r="C51" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="D51" s="17"/>
-      <c r="E51" s="18"/>
+      <c r="D51" s="15"/>
+      <c r="E51" s="16"/>
       <c r="F51" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="G51" s="15">
+      <c r="G51" s="26">
         <v>0.86985000000000001</v>
       </c>
-      <c r="H51" s="8">
+      <c r="H51" s="23">
         <v>0.953183</v>
       </c>
-      <c r="I51" s="10">
+      <c r="I51" s="8">
         <v>90000</v>
       </c>
-      <c r="J51" s="11">
+      <c r="J51" s="9">
         <v>0</v>
       </c>
-      <c r="K51" s="10">
+      <c r="K51" s="8">
         <v>90000</v>
       </c>
-      <c r="L51" s="16">
+      <c r="L51" s="12">
         <v>90000</v>
       </c>
     </row>
     <row r="52" spans="1:12" ht="14" x14ac:dyDescent="0.15">
-      <c r="A52" s="14">
+      <c r="A52" s="11">
         <v>20260301852</v>
       </c>
-      <c r="B52" s="13">
+      <c r="B52" s="10">
         <v>46083</v>
       </c>
       <c r="C52" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="D52" s="17"/>
-      <c r="E52" s="18"/>
+      <c r="D52" s="15"/>
+      <c r="E52" s="16"/>
       <c r="F52" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="G52" s="15">
+      <c r="G52" s="26">
         <v>0.91068300000000002</v>
       </c>
-      <c r="H52" s="8">
+      <c r="H52" s="23">
         <v>3.2835999999999997E-2</v>
       </c>
-      <c r="I52" s="10">
+      <c r="I52" s="8">
         <v>131250</v>
       </c>
-      <c r="J52" s="10">
+      <c r="J52" s="8">
         <v>18000</v>
       </c>
-      <c r="K52" s="10">
+      <c r="K52" s="8">
         <v>149250</v>
       </c>
-      <c r="L52" s="16">
+      <c r="L52" s="12">
         <v>149500</v>
       </c>
     </row>
     <row r="53" spans="1:12" ht="14" x14ac:dyDescent="0.15">
-      <c r="A53" s="14">
+      <c r="A53" s="11">
         <v>20260301853</v>
       </c>
-      <c r="B53" s="13">
+      <c r="B53" s="10">
         <v>46083</v>
       </c>
       <c r="C53" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="D53" s="17"/>
-      <c r="E53" s="18"/>
+      <c r="D53" s="15"/>
+      <c r="E53" s="16"/>
       <c r="F53" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="G53" s="15">
+      <c r="G53" s="26">
         <v>0.96832200000000002</v>
       </c>
-      <c r="H53" s="8">
+      <c r="H53" s="23">
         <v>5.1655E-2</v>
       </c>
-      <c r="I53" s="10">
+      <c r="I53" s="8">
         <v>90000</v>
       </c>
-      <c r="J53" s="10">
+      <c r="J53" s="8">
         <v>16000</v>
       </c>
-      <c r="K53" s="10">
+      <c r="K53" s="8">
         <v>106000</v>
       </c>
-      <c r="L53" s="16">
+      <c r="L53" s="12">
         <v>106000</v>
       </c>
     </row>
@@ -2845,33 +2841,33 @@
       <c r="A54" s="5">
         <v>202603022905</v>
       </c>
-      <c r="B54" s="13">
+      <c r="B54" s="10">
         <v>46083</v>
       </c>
       <c r="C54" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="D54" s="17"/>
-      <c r="E54" s="18"/>
+      <c r="D54" s="15"/>
+      <c r="E54" s="16"/>
       <c r="F54" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="G54" s="8">
+      <c r="G54" s="23">
         <v>0.510185</v>
       </c>
-      <c r="H54" s="9">
+      <c r="H54" s="24">
         <v>0.60430600000000001</v>
       </c>
-      <c r="I54" s="10">
+      <c r="I54" s="8">
         <v>101250</v>
       </c>
-      <c r="J54" s="11">
+      <c r="J54" s="9">
         <v>0</v>
       </c>
-      <c r="K54" s="10">
+      <c r="K54" s="8">
         <v>101250</v>
       </c>
-      <c r="L54" s="10">
+      <c r="L54" s="8">
         <v>101500</v>
       </c>
     </row>
@@ -2879,35 +2875,35 @@
       <c r="A55" s="5">
         <v>202603022906</v>
       </c>
-      <c r="B55" s="13">
+      <c r="B55" s="10">
         <v>46083</v>
       </c>
       <c r="C55" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="D55" s="21" t="s">
-        <v>35</v>
-      </c>
-      <c r="E55" s="22"/>
+      <c r="D55" s="19" t="s">
+        <v>34</v>
+      </c>
+      <c r="E55" s="20"/>
       <c r="F55" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="G55" s="8">
+      <c r="G55" s="23">
         <v>0.510602</v>
       </c>
-      <c r="H55" s="9">
+      <c r="H55" s="24">
         <v>0.59393499999999999</v>
       </c>
-      <c r="I55" s="10">
+      <c r="I55" s="8">
         <v>63000</v>
       </c>
-      <c r="J55" s="11">
+      <c r="J55" s="9">
         <v>0</v>
       </c>
-      <c r="K55" s="10">
+      <c r="K55" s="8">
         <v>63000</v>
       </c>
-      <c r="L55" s="10">
+      <c r="L55" s="8">
         <v>63000</v>
       </c>
     </row>
@@ -2915,33 +2911,33 @@
       <c r="A56" s="5">
         <v>202603022907</v>
       </c>
-      <c r="B56" s="13">
+      <c r="B56" s="10">
         <v>46083</v>
       </c>
       <c r="C56" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="D56" s="17"/>
-      <c r="E56" s="18"/>
+      <c r="D56" s="15"/>
+      <c r="E56" s="16"/>
       <c r="F56" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="G56" s="8">
+      <c r="G56" s="23">
         <v>0.52311300000000005</v>
       </c>
-      <c r="H56" s="9">
+      <c r="H56" s="24">
         <v>0.58381899999999998</v>
       </c>
-      <c r="I56" s="10">
+      <c r="I56" s="8">
         <v>50721</v>
       </c>
-      <c r="J56" s="10">
+      <c r="J56" s="8">
         <v>10000</v>
       </c>
-      <c r="K56" s="10">
+      <c r="K56" s="8">
         <v>60721</v>
       </c>
-      <c r="L56" s="10">
+      <c r="L56" s="8">
         <v>61000</v>
       </c>
     </row>
@@ -2949,33 +2945,33 @@
       <c r="A57" s="5">
         <v>202603022908</v>
       </c>
-      <c r="B57" s="13">
+      <c r="B57" s="10">
         <v>46083</v>
       </c>
       <c r="C57" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="D57" s="17"/>
-      <c r="E57" s="18"/>
+      <c r="D57" s="15"/>
+      <c r="E57" s="16"/>
       <c r="F57" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="G57" s="8">
+        <v>35</v>
+      </c>
+      <c r="G57" s="23">
         <v>0.53841399999999995</v>
       </c>
-      <c r="H57" s="9">
+      <c r="H57" s="24">
         <v>0.58008099999999996</v>
       </c>
-      <c r="I57" s="10">
+      <c r="I57" s="8">
         <v>20000</v>
       </c>
-      <c r="J57" s="11">
+      <c r="J57" s="9">
         <v>0</v>
       </c>
-      <c r="K57" s="10">
+      <c r="K57" s="8">
         <v>20000</v>
       </c>
-      <c r="L57" s="10">
+      <c r="L57" s="8">
         <v>20000</v>
       </c>
     </row>
@@ -2983,33 +2979,33 @@
       <c r="A58" s="5">
         <v>202603022909</v>
       </c>
-      <c r="B58" s="13">
+      <c r="B58" s="10">
         <v>46083</v>
       </c>
       <c r="C58" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="D58" s="17"/>
-      <c r="E58" s="18"/>
+      <c r="D58" s="15"/>
+      <c r="E58" s="16"/>
       <c r="F58" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="G58" s="8">
+        <v>35</v>
+      </c>
+      <c r="G58" s="23">
         <v>0.56173600000000001</v>
       </c>
-      <c r="H58" s="9">
+      <c r="H58" s="24">
         <v>0.645069</v>
       </c>
-      <c r="I58" s="10">
+      <c r="I58" s="8">
         <v>40000</v>
       </c>
-      <c r="J58" s="11">
+      <c r="J58" s="9">
         <v>0</v>
       </c>
-      <c r="K58" s="10">
+      <c r="K58" s="8">
         <v>40000</v>
       </c>
-      <c r="L58" s="10">
+      <c r="L58" s="8">
         <v>40000</v>
       </c>
     </row>
@@ -3017,33 +3013,33 @@
       <c r="A59" s="5">
         <v>202603022910</v>
       </c>
-      <c r="B59" s="13">
+      <c r="B59" s="10">
         <v>46083</v>
       </c>
       <c r="C59" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="D59" s="17"/>
-      <c r="E59" s="18"/>
+      <c r="D59" s="15"/>
+      <c r="E59" s="16"/>
       <c r="F59" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="G59" s="8">
+        <v>35</v>
+      </c>
+      <c r="G59" s="23">
         <v>0.58789400000000003</v>
       </c>
-      <c r="H59" s="9">
+      <c r="H59" s="24">
         <v>0.67122700000000002</v>
       </c>
-      <c r="I59" s="10">
+      <c r="I59" s="8">
         <v>40000</v>
       </c>
-      <c r="J59" s="11">
+      <c r="J59" s="9">
         <v>0</v>
       </c>
-      <c r="K59" s="10">
+      <c r="K59" s="8">
         <v>40000</v>
       </c>
-      <c r="L59" s="10">
+      <c r="L59" s="8">
         <v>40000</v>
       </c>
     </row>
@@ -3051,35 +3047,35 @@
       <c r="A60" s="5">
         <v>202603022911</v>
       </c>
-      <c r="B60" s="13">
+      <c r="B60" s="10">
         <v>46083</v>
       </c>
       <c r="C60" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="D60" s="21" t="s">
-        <v>37</v>
-      </c>
-      <c r="E60" s="22"/>
+      <c r="D60" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="E60" s="20"/>
       <c r="F60" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="G60" s="8">
+        <v>35</v>
+      </c>
+      <c r="G60" s="23">
         <v>0.59736100000000003</v>
       </c>
-      <c r="H60" s="9">
+      <c r="H60" s="24">
         <v>0.75083299999999997</v>
       </c>
-      <c r="I60" s="10">
+      <c r="I60" s="8">
         <v>66234</v>
       </c>
-      <c r="J60" s="11">
+      <c r="J60" s="9">
         <v>0</v>
       </c>
-      <c r="K60" s="10">
+      <c r="K60" s="8">
         <v>66234</v>
       </c>
-      <c r="L60" s="10">
+      <c r="L60" s="8">
         <v>66500</v>
       </c>
     </row>
@@ -3087,33 +3083,33 @@
       <c r="A61" s="5">
         <v>202603022912</v>
       </c>
-      <c r="B61" s="13">
+      <c r="B61" s="10">
         <v>46083</v>
       </c>
       <c r="C61" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="D61" s="17"/>
-      <c r="E61" s="18"/>
+      <c r="D61" s="15"/>
+      <c r="E61" s="16"/>
       <c r="F61" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="G61" s="8">
+        <v>35</v>
+      </c>
+      <c r="G61" s="23">
         <v>0.60461799999999999</v>
       </c>
-      <c r="H61" s="9">
+      <c r="H61" s="24">
         <v>0.65978000000000003</v>
       </c>
-      <c r="I61" s="10">
+      <c r="I61" s="8">
         <v>26307</v>
       </c>
-      <c r="J61" s="10">
+      <c r="J61" s="8">
         <v>8000</v>
       </c>
-      <c r="K61" s="10">
+      <c r="K61" s="8">
         <v>34307</v>
       </c>
-      <c r="L61" s="10">
+      <c r="L61" s="8">
         <v>34500</v>
       </c>
     </row>
@@ -3121,33 +3117,33 @@
       <c r="A62" s="5">
         <v>202603022913</v>
       </c>
-      <c r="B62" s="13">
+      <c r="B62" s="10">
         <v>46083</v>
       </c>
       <c r="C62" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="D62" s="17"/>
-      <c r="E62" s="18"/>
+      <c r="D62" s="15"/>
+      <c r="E62" s="16"/>
       <c r="F62" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="G62" s="8">
+        <v>35</v>
+      </c>
+      <c r="G62" s="23">
         <v>0.60675900000000005</v>
       </c>
-      <c r="H62" s="9">
+      <c r="H62" s="24">
         <v>0.64842599999999995</v>
       </c>
-      <c r="I62" s="10">
+      <c r="I62" s="8">
         <v>20000</v>
       </c>
-      <c r="J62" s="11">
+      <c r="J62" s="9">
         <v>0</v>
       </c>
-      <c r="K62" s="10">
+      <c r="K62" s="8">
         <v>20000</v>
       </c>
-      <c r="L62" s="10">
+      <c r="L62" s="8">
         <v>20000</v>
       </c>
     </row>
@@ -3155,33 +3151,33 @@
       <c r="A63" s="5">
         <v>202603022914</v>
       </c>
-      <c r="B63" s="13">
+      <c r="B63" s="10">
         <v>46083</v>
       </c>
       <c r="C63" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="D63" s="17"/>
-      <c r="E63" s="18"/>
+      <c r="D63" s="15"/>
+      <c r="E63" s="16"/>
       <c r="F63" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="G63" s="8">
+        <v>35</v>
+      </c>
+      <c r="G63" s="23">
         <v>0.62175899999999995</v>
       </c>
-      <c r="H63" s="9">
+      <c r="H63" s="24">
         <v>0.70509299999999997</v>
       </c>
-      <c r="I63" s="10">
+      <c r="I63" s="8">
         <v>40000</v>
       </c>
-      <c r="J63" s="10">
+      <c r="J63" s="8">
         <v>5000</v>
       </c>
-      <c r="K63" s="10">
+      <c r="K63" s="8">
         <v>45000</v>
       </c>
-      <c r="L63" s="10">
+      <c r="L63" s="8">
         <v>45000</v>
       </c>
     </row>
@@ -3189,35 +3185,35 @@
       <c r="A64" s="5">
         <v>202603022915</v>
       </c>
-      <c r="B64" s="13">
+      <c r="B64" s="10">
         <v>46083</v>
       </c>
       <c r="C64" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="D64" s="21" t="s">
+      <c r="D64" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="E64" s="20"/>
+      <c r="F64" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="E64" s="22"/>
-      <c r="F64" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="G64" s="8">
+      <c r="G64" s="23">
         <v>0.79901599999999995</v>
       </c>
-      <c r="H64" s="9">
+      <c r="H64" s="24">
         <v>0.91598400000000002</v>
       </c>
-      <c r="I64" s="10">
+      <c r="I64" s="8">
         <v>88150</v>
       </c>
-      <c r="J64" s="10">
+      <c r="J64" s="8">
         <v>36000</v>
       </c>
-      <c r="K64" s="10">
+      <c r="K64" s="8">
         <v>124150</v>
       </c>
-      <c r="L64" s="10">
+      <c r="L64" s="8">
         <v>124500</v>
       </c>
     </row>
@@ -3225,35 +3221,35 @@
       <c r="A65" s="5">
         <v>202603022916</v>
       </c>
-      <c r="B65" s="13">
+      <c r="B65" s="10">
         <v>46083</v>
       </c>
       <c r="C65" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="D65" s="21" t="s">
+      <c r="D65" s="19" t="s">
         <v>27</v>
       </c>
-      <c r="E65" s="22"/>
+      <c r="E65" s="20"/>
       <c r="F65" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="G65" s="8">
+        <v>38</v>
+      </c>
+      <c r="G65" s="23">
         <v>0.80394699999999997</v>
       </c>
-      <c r="H65" s="9">
+      <c r="H65" s="24">
         <v>0.93235000000000001</v>
       </c>
-      <c r="I65" s="10">
+      <c r="I65" s="8">
         <v>96545</v>
       </c>
-      <c r="J65" s="10">
+      <c r="J65" s="8">
         <v>38000</v>
       </c>
-      <c r="K65" s="10">
+      <c r="K65" s="8">
         <v>134545</v>
       </c>
-      <c r="L65" s="10">
+      <c r="L65" s="8">
         <v>135000</v>
       </c>
     </row>
@@ -3261,33 +3257,33 @@
       <c r="A66" s="5">
         <v>202603022917</v>
       </c>
-      <c r="B66" s="13">
+      <c r="B66" s="10">
         <v>46083</v>
       </c>
       <c r="C66" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="D66" s="17"/>
-      <c r="E66" s="18"/>
+      <c r="D66" s="15"/>
+      <c r="E66" s="16"/>
       <c r="F66" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="G66" s="8">
+        <v>38</v>
+      </c>
+      <c r="G66" s="23">
         <v>0.807037</v>
       </c>
-      <c r="H66" s="9">
+      <c r="H66" s="24">
         <v>0.89036999999999999</v>
       </c>
-      <c r="I66" s="10">
+      <c r="I66" s="8">
         <v>70000</v>
       </c>
-      <c r="J66" s="10">
+      <c r="J66" s="8">
         <v>55000</v>
       </c>
-      <c r="K66" s="10">
+      <c r="K66" s="8">
         <v>125000</v>
       </c>
-      <c r="L66" s="10">
+      <c r="L66" s="8">
         <v>125000</v>
       </c>
     </row>
@@ -3295,33 +3291,33 @@
       <c r="A67" s="5">
         <v>202603022918</v>
       </c>
-      <c r="B67" s="13">
+      <c r="B67" s="10">
         <v>46083</v>
       </c>
       <c r="C67" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="D67" s="17"/>
-      <c r="E67" s="18"/>
+      <c r="D67" s="15"/>
+      <c r="E67" s="16"/>
       <c r="F67" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="G67" s="8">
+        <v>38</v>
+      </c>
+      <c r="G67" s="23">
         <v>0.80881899999999995</v>
       </c>
-      <c r="H67" s="9">
+      <c r="H67" s="24">
         <v>0.87068299999999998</v>
       </c>
-      <c r="I67" s="10">
+      <c r="I67" s="8">
         <v>51887</v>
       </c>
-      <c r="J67" s="10">
+      <c r="J67" s="8">
         <v>22000</v>
       </c>
-      <c r="K67" s="10">
+      <c r="K67" s="8">
         <v>73887</v>
       </c>
-      <c r="L67" s="10">
+      <c r="L67" s="8">
         <v>74000</v>
       </c>
     </row>
@@ -3329,33 +3325,33 @@
       <c r="A68" s="5">
         <v>202603022919</v>
       </c>
-      <c r="B68" s="13">
+      <c r="B68" s="10">
         <v>46083</v>
       </c>
       <c r="C68" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="D68" s="17"/>
-      <c r="E68" s="18"/>
+      <c r="D68" s="15"/>
+      <c r="E68" s="16"/>
       <c r="F68" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="G68" s="8">
+        <v>38</v>
+      </c>
+      <c r="G68" s="23">
         <v>0.82744200000000001</v>
       </c>
-      <c r="H68" s="9">
+      <c r="H68" s="24">
         <v>0.896065</v>
       </c>
-      <c r="I68" s="10">
+      <c r="I68" s="8">
         <v>57134</v>
       </c>
-      <c r="J68" s="10">
+      <c r="J68" s="8">
         <v>5000</v>
       </c>
-      <c r="K68" s="10">
+      <c r="K68" s="8">
         <v>62134</v>
       </c>
-      <c r="L68" s="10">
+      <c r="L68" s="8">
         <v>62500</v>
       </c>
     </row>
@@ -3363,33 +3359,33 @@
       <c r="A69" s="5">
         <v>202603022920</v>
       </c>
-      <c r="B69" s="13">
+      <c r="B69" s="10">
         <v>46083</v>
       </c>
       <c r="C69" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="D69" s="17"/>
-      <c r="E69" s="18"/>
+      <c r="D69" s="15"/>
+      <c r="E69" s="16"/>
       <c r="F69" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="G69" s="8">
+        <v>38</v>
+      </c>
+      <c r="G69" s="23">
         <v>0.82923599999999997</v>
       </c>
-      <c r="H69" s="9">
+      <c r="H69" s="24">
         <v>0.87693299999999996</v>
       </c>
-      <c r="I69" s="10">
+      <c r="I69" s="8">
         <v>39644</v>
       </c>
-      <c r="J69" s="11">
+      <c r="J69" s="9">
         <v>0</v>
       </c>
-      <c r="K69" s="10">
+      <c r="K69" s="8">
         <v>39644</v>
       </c>
-      <c r="L69" s="10">
+      <c r="L69" s="8">
         <v>40000</v>
       </c>
     </row>
@@ -3397,33 +3393,33 @@
       <c r="A70" s="5">
         <v>202603022921</v>
       </c>
-      <c r="B70" s="13">
+      <c r="B70" s="10">
         <v>46083</v>
       </c>
       <c r="C70" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="D70" s="17"/>
-      <c r="E70" s="18"/>
+      <c r="D70" s="15"/>
+      <c r="E70" s="16"/>
       <c r="F70" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="G70" s="8">
+        <v>38</v>
+      </c>
+      <c r="G70" s="23">
         <v>0.85557899999999998</v>
       </c>
-      <c r="H70" s="9">
+      <c r="H70" s="24">
         <v>0.89724499999999996</v>
       </c>
-      <c r="I70" s="10">
+      <c r="I70" s="8">
         <v>35000</v>
       </c>
-      <c r="J70" s="11">
+      <c r="J70" s="9">
         <v>0</v>
       </c>
-      <c r="K70" s="10">
+      <c r="K70" s="8">
         <v>35000</v>
       </c>
-      <c r="L70" s="10">
+      <c r="L70" s="8">
         <v>35000</v>
       </c>
     </row>
@@ -3431,35 +3427,35 @@
       <c r="A71" s="5">
         <v>202603022922</v>
       </c>
-      <c r="B71" s="13">
+      <c r="B71" s="10">
         <v>46083</v>
       </c>
       <c r="C71" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="D71" s="21" t="s">
-        <v>40</v>
-      </c>
-      <c r="E71" s="22"/>
+      <c r="D71" s="19" t="s">
+        <v>39</v>
+      </c>
+      <c r="E71" s="20"/>
       <c r="F71" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="G71" s="8">
+        <v>38</v>
+      </c>
+      <c r="G71" s="23">
         <v>0.86092599999999997</v>
       </c>
-      <c r="H71" s="9">
+      <c r="H71" s="24">
         <v>0.932674</v>
       </c>
-      <c r="I71" s="10">
+      <c r="I71" s="8">
         <v>54044</v>
       </c>
-      <c r="J71" s="10">
+      <c r="J71" s="8">
         <v>12000</v>
       </c>
-      <c r="K71" s="10">
+      <c r="K71" s="8">
         <v>66044</v>
       </c>
-      <c r="L71" s="10">
+      <c r="L71" s="8">
         <v>66500</v>
       </c>
     </row>
@@ -3467,33 +3463,33 @@
       <c r="A72" s="5">
         <v>202603022923</v>
       </c>
-      <c r="B72" s="13">
+      <c r="B72" s="10">
         <v>46083</v>
       </c>
       <c r="C72" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="D72" s="17"/>
-      <c r="E72" s="18"/>
+      <c r="D72" s="15"/>
+      <c r="E72" s="16"/>
       <c r="F72" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="G72" s="8">
+        <v>38</v>
+      </c>
+      <c r="G72" s="23">
         <v>0.86571799999999999</v>
       </c>
-      <c r="H72" s="9">
+      <c r="H72" s="24">
         <v>0.90738399999999997</v>
       </c>
-      <c r="I72" s="10">
+      <c r="I72" s="8">
         <v>35000</v>
       </c>
-      <c r="J72" s="10">
+      <c r="J72" s="8">
         <v>10000</v>
       </c>
-      <c r="K72" s="10">
+      <c r="K72" s="8">
         <v>45000</v>
       </c>
-      <c r="L72" s="10">
+      <c r="L72" s="8">
         <v>45000</v>
       </c>
     </row>
@@ -3501,33 +3497,33 @@
       <c r="A73" s="5">
         <v>202603022924</v>
       </c>
-      <c r="B73" s="13">
+      <c r="B73" s="10">
         <v>46083</v>
       </c>
       <c r="C73" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="D73" s="17"/>
-      <c r="E73" s="18"/>
+      <c r="D73" s="15"/>
+      <c r="E73" s="16"/>
       <c r="F73" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="G73" s="8">
+        <v>38</v>
+      </c>
+      <c r="G73" s="23">
         <v>0.87425900000000001</v>
       </c>
-      <c r="H73" s="9">
+      <c r="H73" s="24">
         <v>0.99892400000000003</v>
       </c>
-      <c r="I73" s="10">
+      <c r="I73" s="8">
         <v>104357</v>
       </c>
-      <c r="J73" s="10">
+      <c r="J73" s="8">
         <v>28000</v>
       </c>
-      <c r="K73" s="10">
+      <c r="K73" s="8">
         <v>132357</v>
       </c>
-      <c r="L73" s="10">
+      <c r="L73" s="8">
         <v>132500</v>
       </c>
     </row>
@@ -3535,35 +3531,35 @@
       <c r="A74" s="5">
         <v>202603022925</v>
       </c>
-      <c r="B74" s="13">
+      <c r="B74" s="10">
         <v>46083</v>
       </c>
       <c r="C74" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="D74" s="19" t="s">
-        <v>41</v>
-      </c>
-      <c r="E74" s="20"/>
+      <c r="D74" s="21" t="s">
+        <v>40</v>
+      </c>
+      <c r="E74" s="22"/>
       <c r="F74" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="G74" s="8">
+        <v>38</v>
+      </c>
+      <c r="G74" s="23">
         <v>0.87993100000000002</v>
       </c>
-      <c r="H74" s="12">
+      <c r="H74" s="25">
         <v>3.2520000000000001E-3</v>
       </c>
-      <c r="I74" s="10">
+      <c r="I74" s="8">
         <v>92872</v>
       </c>
-      <c r="J74" s="10">
+      <c r="J74" s="8">
         <v>32000</v>
       </c>
-      <c r="K74" s="10">
+      <c r="K74" s="8">
         <v>124872</v>
       </c>
-      <c r="L74" s="10">
+      <c r="L74" s="8">
         <v>125000</v>
       </c>
     </row>
@@ -3571,33 +3567,33 @@
       <c r="A75" s="5">
         <v>202603022926</v>
       </c>
-      <c r="B75" s="13">
+      <c r="B75" s="10">
         <v>46083</v>
       </c>
       <c r="C75" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="D75" s="17"/>
-      <c r="E75" s="18"/>
+      <c r="D75" s="15"/>
+      <c r="E75" s="16"/>
       <c r="F75" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="G75" s="8">
+        <v>38</v>
+      </c>
+      <c r="G75" s="23">
         <v>0.89011600000000002</v>
       </c>
-      <c r="H75" s="12">
+      <c r="H75" s="25">
         <v>0.97344900000000001</v>
       </c>
-      <c r="I75" s="10">
+      <c r="I75" s="8">
         <v>70000</v>
       </c>
-      <c r="J75" s="10">
+      <c r="J75" s="8">
         <v>10000</v>
       </c>
-      <c r="K75" s="10">
+      <c r="K75" s="8">
         <v>80000</v>
       </c>
-      <c r="L75" s="10">
+      <c r="L75" s="8">
         <v>80000</v>
       </c>
     </row>
@@ -3605,33 +3601,33 @@
       <c r="A76" s="5">
         <v>202603022927</v>
       </c>
-      <c r="B76" s="13">
+      <c r="B76" s="10">
         <v>46083</v>
       </c>
       <c r="C76" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="D76" s="17"/>
-      <c r="E76" s="18"/>
+      <c r="D76" s="15"/>
+      <c r="E76" s="16"/>
       <c r="F76" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="G76" s="8">
+        <v>38</v>
+      </c>
+      <c r="G76" s="23">
         <v>0.89775499999999997</v>
       </c>
-      <c r="H76" s="12">
+      <c r="H76" s="25">
         <v>0.93942099999999995</v>
       </c>
-      <c r="I76" s="10">
+      <c r="I76" s="8">
         <v>35000</v>
       </c>
-      <c r="J76" s="10">
+      <c r="J76" s="8">
         <v>16000</v>
       </c>
-      <c r="K76" s="10">
+      <c r="K76" s="8">
         <v>51000</v>
       </c>
-      <c r="L76" s="10">
+      <c r="L76" s="8">
         <v>51000</v>
       </c>
     </row>
@@ -3639,35 +3635,35 @@
       <c r="A77" s="5">
         <v>202603022928</v>
       </c>
-      <c r="B77" s="13">
+      <c r="B77" s="10">
         <v>46084</v>
       </c>
       <c r="C77" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="D77" s="19" t="s">
-        <v>42</v>
-      </c>
-      <c r="E77" s="20"/>
+      <c r="D77" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="E77" s="22"/>
       <c r="F77" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="G77" s="8">
+        <v>38</v>
+      </c>
+      <c r="G77" s="23">
         <v>0.93898099999999995</v>
       </c>
-      <c r="H77" s="12">
+      <c r="H77" s="25">
         <v>3.7048999999999999E-2</v>
       </c>
-      <c r="I77" s="10">
+      <c r="I77" s="8">
         <v>73983</v>
       </c>
-      <c r="J77" s="10">
+      <c r="J77" s="8">
         <v>26000</v>
       </c>
-      <c r="K77" s="10">
+      <c r="K77" s="8">
         <v>99983</v>
       </c>
-      <c r="L77" s="10">
+      <c r="L77" s="8">
         <v>100000</v>
       </c>
     </row>
@@ -3675,33 +3671,33 @@
       <c r="A78" s="5">
         <v>202603022929</v>
       </c>
-      <c r="B78" s="13">
+      <c r="B78" s="10">
         <v>46084</v>
       </c>
       <c r="C78" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="D78" s="17"/>
-      <c r="E78" s="18"/>
+      <c r="D78" s="15"/>
+      <c r="E78" s="16"/>
       <c r="F78" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="G78" s="8">
+        <v>38</v>
+      </c>
+      <c r="G78" s="23">
         <v>0.94304399999999999</v>
       </c>
-      <c r="H78" s="12">
+      <c r="H78" s="25">
         <v>2.6424E-2</v>
       </c>
-      <c r="I78" s="10">
+      <c r="I78" s="8">
         <v>69960</v>
       </c>
-      <c r="J78" s="10">
+      <c r="J78" s="8">
         <v>16000</v>
       </c>
-      <c r="K78" s="10">
+      <c r="K78" s="8">
         <v>85960</v>
       </c>
-      <c r="L78" s="10">
+      <c r="L78" s="8">
         <v>86000</v>
       </c>
     </row>
@@ -3709,35 +3705,35 @@
       <c r="A79" s="5">
         <v>202603022930</v>
       </c>
-      <c r="B79" s="13">
+      <c r="B79" s="10">
         <v>46084</v>
       </c>
       <c r="C79" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="D79" s="19" t="s">
+      <c r="D79" s="21" t="s">
         <v>22</v>
       </c>
-      <c r="E79" s="20"/>
+      <c r="E79" s="22"/>
       <c r="F79" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="G79" s="8">
+        <v>38</v>
+      </c>
+      <c r="G79" s="23">
         <v>0.94370399999999999</v>
       </c>
-      <c r="H79" s="12">
+      <c r="H79" s="25">
         <v>2.4650000000000002E-3</v>
       </c>
-      <c r="I79" s="10">
+      <c r="I79" s="8">
         <v>44075</v>
       </c>
-      <c r="J79" s="11">
+      <c r="J79" s="9">
         <v>0</v>
       </c>
-      <c r="K79" s="10">
+      <c r="K79" s="8">
         <v>44075</v>
       </c>
-      <c r="L79" s="10">
+      <c r="L79" s="8">
         <v>44500</v>
       </c>
     </row>
@@ -3745,33 +3741,33 @@
       <c r="A80" s="5">
         <v>202603022931</v>
       </c>
-      <c r="B80" s="13">
+      <c r="B80" s="10">
         <v>46084</v>
       </c>
       <c r="C80" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="D80" s="17"/>
-      <c r="E80" s="18"/>
+      <c r="D80" s="15"/>
+      <c r="E80" s="16"/>
       <c r="F80" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="G80" s="8">
+        <v>38</v>
+      </c>
+      <c r="G80" s="23">
         <v>0.94821800000000001</v>
       </c>
-      <c r="H80" s="12">
+      <c r="H80" s="25">
         <v>1.4803E-2</v>
       </c>
-      <c r="I80" s="10">
+      <c r="I80" s="8">
         <v>55385</v>
       </c>
-      <c r="J80" s="10">
+      <c r="J80" s="8">
         <v>40000</v>
       </c>
-      <c r="K80" s="10">
+      <c r="K80" s="8">
         <v>95385</v>
       </c>
-      <c r="L80" s="10">
+      <c r="L80" s="8">
         <v>95500</v>
       </c>
     </row>
@@ -3779,33 +3775,33 @@
       <c r="A81" s="5">
         <v>202603022932</v>
       </c>
-      <c r="B81" s="13">
+      <c r="B81" s="10">
         <v>46084</v>
       </c>
       <c r="C81" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="D81" s="17"/>
-      <c r="E81" s="18"/>
+      <c r="D81" s="15"/>
+      <c r="E81" s="16"/>
       <c r="F81" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="G81" s="8">
+        <v>38</v>
+      </c>
+      <c r="G81" s="23">
         <v>0.94922499999999999</v>
       </c>
-      <c r="H81" s="12">
+      <c r="H81" s="25">
         <v>2.3599999999999999E-2</v>
       </c>
-      <c r="I81" s="10">
+      <c r="I81" s="8">
         <v>62381</v>
       </c>
-      <c r="J81" s="10">
+      <c r="J81" s="8">
         <v>20000</v>
       </c>
-      <c r="K81" s="10">
+      <c r="K81" s="8">
         <v>82381</v>
       </c>
-      <c r="L81" s="10">
+      <c r="L81" s="8">
         <v>82500</v>
       </c>
     </row>
@@ -3813,33 +3809,33 @@
       <c r="A82" s="5">
         <v>202603022933</v>
       </c>
-      <c r="B82" s="13">
+      <c r="B82" s="10">
         <v>46084</v>
       </c>
       <c r="C82" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="D82" s="17"/>
-      <c r="E82" s="18"/>
+      <c r="D82" s="15"/>
+      <c r="E82" s="16"/>
       <c r="F82" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="G82" s="8">
+        <v>38</v>
+      </c>
+      <c r="G82" s="23">
         <v>0.95225700000000002</v>
       </c>
-      <c r="H82" s="12">
+      <c r="H82" s="25">
         <v>1.9132E-2</v>
       </c>
-      <c r="I82" s="10">
+      <c r="I82" s="8">
         <v>55968</v>
       </c>
-      <c r="J82" s="10">
+      <c r="J82" s="8">
         <v>20000</v>
       </c>
-      <c r="K82" s="10">
+      <c r="K82" s="8">
         <v>75968</v>
       </c>
-      <c r="L82" s="10">
+      <c r="L82" s="8">
         <v>76000</v>
       </c>
     </row>
@@ -3847,33 +3843,33 @@
       <c r="A83" s="5">
         <v>202603022934</v>
       </c>
-      <c r="B83" s="13">
+      <c r="B83" s="10">
         <v>46083</v>
       </c>
       <c r="C83" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="D83" s="17"/>
-      <c r="E83" s="18"/>
+      <c r="D83" s="15"/>
+      <c r="E83" s="16"/>
       <c r="F83" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="G83" s="8">
+        <v>38</v>
+      </c>
+      <c r="G83" s="23">
         <v>0.95493099999999997</v>
       </c>
-      <c r="H83" s="12">
+      <c r="H83" s="25">
         <v>0.99659699999999996</v>
       </c>
-      <c r="I83" s="10">
+      <c r="I83" s="8">
         <v>35000</v>
       </c>
-      <c r="J83" s="11">
+      <c r="J83" s="9">
         <v>0</v>
       </c>
-      <c r="K83" s="10">
+      <c r="K83" s="8">
         <v>35000</v>
       </c>
-      <c r="L83" s="10">
+      <c r="L83" s="8">
         <v>35000</v>
       </c>
     </row>
@@ -3881,519 +3877,536 @@
       <c r="A84" s="5">
         <v>202603022935</v>
       </c>
-      <c r="B84" s="13">
+      <c r="B84" s="10">
         <v>46084</v>
       </c>
       <c r="C84" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="D84" s="17"/>
-      <c r="E84" s="18"/>
+      <c r="D84" s="15"/>
+      <c r="E84" s="16"/>
       <c r="F84" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="G84" s="8">
+        <v>38</v>
+      </c>
+      <c r="G84" s="23">
         <v>0.96503499999999998</v>
       </c>
-      <c r="H84" s="12">
+      <c r="H84" s="25">
         <v>4.2835999999999999E-2</v>
       </c>
-      <c r="I84" s="10">
+      <c r="I84" s="8">
         <v>65296</v>
       </c>
-      <c r="J84" s="11">
+      <c r="J84" s="9">
         <v>0</v>
       </c>
-      <c r="K84" s="10">
+      <c r="K84" s="8">
         <v>65296</v>
       </c>
-      <c r="L84" s="10">
+      <c r="L84" s="8">
         <v>65500</v>
       </c>
     </row>
     <row r="85" spans="1:12" ht="14" x14ac:dyDescent="0.15">
-      <c r="A85" s="14">
+      <c r="A85" s="11">
         <v>20260302854</v>
       </c>
-      <c r="B85" s="13">
+      <c r="B85" s="10">
         <v>46083</v>
       </c>
       <c r="C85" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="D85" s="17"/>
-      <c r="E85" s="18"/>
+        <v>45</v>
+      </c>
+      <c r="D85" s="15"/>
+      <c r="E85" s="16"/>
       <c r="F85" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="G85" s="15">
+        <v>43</v>
+      </c>
+      <c r="G85" s="26">
         <v>0.54884299999999997</v>
       </c>
-      <c r="H85" s="8">
+      <c r="H85" s="23">
         <v>0.67384299999999997</v>
       </c>
-      <c r="I85" s="10">
+      <c r="I85" s="8">
         <v>90000</v>
       </c>
-      <c r="J85" s="10">
+      <c r="J85" s="8">
         <v>60000</v>
       </c>
-      <c r="K85" s="10">
+      <c r="K85" s="8">
         <v>150000</v>
       </c>
-      <c r="L85" s="16">
+      <c r="L85" s="12">
         <v>150000</v>
       </c>
     </row>
     <row r="86" spans="1:12" ht="14" x14ac:dyDescent="0.15">
-      <c r="A86" s="14">
+      <c r="A86" s="11">
         <v>20260302855</v>
       </c>
-      <c r="B86" s="13">
+      <c r="B86" s="10">
         <v>46083</v>
       </c>
       <c r="C86" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="D86" s="17"/>
-      <c r="E86" s="18"/>
+      <c r="D86" s="15"/>
+      <c r="E86" s="16"/>
       <c r="F86" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="G86" s="15">
+        <v>35</v>
+      </c>
+      <c r="G86" s="26">
         <v>0.57535899999999995</v>
       </c>
-      <c r="H86" s="8">
+      <c r="H86" s="23">
         <v>0.65869200000000006</v>
       </c>
-      <c r="I86" s="10">
+      <c r="I86" s="8">
         <v>40000</v>
       </c>
-      <c r="J86" s="10">
+      <c r="J86" s="8">
         <v>16000</v>
       </c>
-      <c r="K86" s="10">
+      <c r="K86" s="8">
         <v>56000</v>
       </c>
-      <c r="L86" s="16">
+      <c r="L86" s="12">
         <v>56000</v>
       </c>
     </row>
     <row r="87" spans="1:12" ht="14" x14ac:dyDescent="0.15">
-      <c r="A87" s="14">
+      <c r="A87" s="11">
         <v>20260302856</v>
       </c>
-      <c r="B87" s="13">
+      <c r="B87" s="10">
         <v>46083</v>
       </c>
       <c r="C87" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="D87" s="17"/>
-      <c r="E87" s="18"/>
+      <c r="D87" s="15"/>
+      <c r="E87" s="16"/>
       <c r="F87" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="G87" s="15">
+        <v>35</v>
+      </c>
+      <c r="G87" s="26">
         <v>0.60737300000000005</v>
       </c>
-      <c r="H87" s="8">
+      <c r="H87" s="23">
         <v>0.64903900000000003</v>
       </c>
-      <c r="I87" s="10">
+      <c r="I87" s="8">
         <v>20000</v>
       </c>
-      <c r="J87" s="10">
+      <c r="J87" s="8">
         <v>8000</v>
       </c>
-      <c r="K87" s="10">
+      <c r="K87" s="8">
         <v>28000</v>
       </c>
-      <c r="L87" s="16">
+      <c r="L87" s="12">
         <v>28000</v>
       </c>
     </row>
     <row r="88" spans="1:12" ht="14" x14ac:dyDescent="0.15">
-      <c r="A88" s="14">
+      <c r="A88" s="11">
         <v>20260302857</v>
       </c>
-      <c r="B88" s="13">
+      <c r="B88" s="10">
         <v>46083</v>
       </c>
       <c r="C88" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="D88" s="17"/>
-      <c r="E88" s="18"/>
+      <c r="D88" s="15"/>
+      <c r="E88" s="16"/>
       <c r="F88" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="G88" s="15">
+        <v>35</v>
+      </c>
+      <c r="G88" s="26">
         <v>0.65005800000000002</v>
       </c>
-      <c r="H88" s="8">
+      <c r="H88" s="23">
         <v>0.69172500000000003</v>
       </c>
-      <c r="I88" s="10">
+      <c r="I88" s="8">
         <v>20000</v>
       </c>
-      <c r="J88" s="11">
+      <c r="J88" s="9">
         <v>0</v>
       </c>
-      <c r="K88" s="10">
+      <c r="K88" s="8">
         <v>20000</v>
       </c>
-      <c r="L88" s="16">
+      <c r="L88" s="12">
         <v>20000</v>
       </c>
     </row>
     <row r="89" spans="1:12" ht="14" x14ac:dyDescent="0.15">
-      <c r="A89" s="14">
+      <c r="A89" s="11">
         <v>20260302858</v>
       </c>
-      <c r="B89" s="13">
+      <c r="B89" s="10">
         <v>46083</v>
       </c>
       <c r="C89" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="D89" s="17"/>
-      <c r="E89" s="18"/>
+      <c r="D89" s="15"/>
+      <c r="E89" s="16"/>
       <c r="F89" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="G89" s="15">
+        <v>38</v>
+      </c>
+      <c r="G89" s="26">
         <v>0.84517399999999998</v>
       </c>
-      <c r="H89" s="8">
+      <c r="H89" s="23">
         <v>0.89557900000000001</v>
       </c>
-      <c r="I89" s="10">
+      <c r="I89" s="8">
         <v>41976</v>
       </c>
-      <c r="J89" s="10">
+      <c r="J89" s="8">
         <v>5000</v>
       </c>
-      <c r="K89" s="10">
+      <c r="K89" s="8">
         <v>46976</v>
       </c>
-      <c r="L89" s="16">
+      <c r="L89" s="12">
         <v>47000</v>
       </c>
     </row>
     <row r="90" spans="1:12" ht="14" x14ac:dyDescent="0.15">
-      <c r="A90" s="14">
+      <c r="A90" s="11">
         <v>20260302859</v>
       </c>
-      <c r="B90" s="13">
+      <c r="B90" s="10">
         <v>46083</v>
       </c>
       <c r="C90" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="D90" s="17"/>
-      <c r="E90" s="18"/>
+      <c r="D90" s="15"/>
+      <c r="E90" s="16"/>
       <c r="F90" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="G90" s="15">
+        <v>38</v>
+      </c>
+      <c r="G90" s="26">
         <v>0.85474499999999998</v>
       </c>
-      <c r="H90" s="8">
+      <c r="H90" s="23">
         <v>0.938079</v>
       </c>
-      <c r="I90" s="10">
+      <c r="I90" s="8">
         <v>70000</v>
       </c>
-      <c r="J90" s="10">
+      <c r="J90" s="8">
         <v>16000</v>
       </c>
-      <c r="K90" s="10">
+      <c r="K90" s="8">
         <v>86000</v>
       </c>
-      <c r="L90" s="16">
+      <c r="L90" s="12">
         <v>86000</v>
       </c>
     </row>
     <row r="91" spans="1:12" ht="14" x14ac:dyDescent="0.15">
-      <c r="A91" s="14">
+      <c r="A91" s="11">
         <v>20260302860</v>
       </c>
-      <c r="B91" s="13">
+      <c r="B91" s="10">
         <v>46083</v>
       </c>
       <c r="C91" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="D91" s="17"/>
-      <c r="E91" s="18"/>
+        <v>45</v>
+      </c>
+      <c r="D91" s="15"/>
+      <c r="E91" s="16"/>
       <c r="F91" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="G91" s="15">
+        <v>42</v>
+      </c>
+      <c r="G91" s="26">
         <v>0.88667799999999997</v>
       </c>
-      <c r="H91" s="8">
+      <c r="H91" s="23">
         <v>0.97001199999999999</v>
       </c>
-      <c r="I91" s="10">
+      <c r="I91" s="8">
         <v>90000</v>
       </c>
-      <c r="J91" s="10">
+      <c r="J91" s="8">
         <v>18000</v>
       </c>
-      <c r="K91" s="10">
+      <c r="K91" s="8">
         <v>108000</v>
       </c>
-      <c r="L91" s="16">
+      <c r="L91" s="12">
         <v>108000</v>
       </c>
     </row>
     <row r="92" spans="1:12" ht="14" x14ac:dyDescent="0.15">
-      <c r="A92" s="14">
+      <c r="A92" s="11">
         <v>20260302861</v>
       </c>
-      <c r="B92" s="13">
+      <c r="B92" s="10">
         <v>46083</v>
       </c>
       <c r="C92" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="D92" s="17"/>
-      <c r="E92" s="18"/>
+      <c r="D92" s="15"/>
+      <c r="E92" s="16"/>
       <c r="F92" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="G92" s="15">
+        <v>38</v>
+      </c>
+      <c r="G92" s="26">
         <v>0.88875000000000004</v>
       </c>
-      <c r="H92" s="8">
+      <c r="H92" s="23">
         <v>0.93041700000000005</v>
       </c>
-      <c r="I92" s="10">
+      <c r="I92" s="8">
         <v>35000</v>
       </c>
-      <c r="J92" s="10">
+      <c r="J92" s="8">
         <v>20000</v>
       </c>
-      <c r="K92" s="10">
+      <c r="K92" s="8">
         <v>55000</v>
       </c>
-      <c r="L92" s="16">
+      <c r="L92" s="12">
         <v>55000</v>
       </c>
     </row>
     <row r="93" spans="1:12" ht="14" x14ac:dyDescent="0.15">
-      <c r="A93" s="14">
+      <c r="A93" s="11">
         <v>20260302862</v>
       </c>
-      <c r="B93" s="13">
+      <c r="B93" s="10">
         <v>46083</v>
       </c>
       <c r="C93" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="D93" s="17"/>
-      <c r="E93" s="18"/>
+      <c r="D93" s="15"/>
+      <c r="E93" s="16"/>
       <c r="F93" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="G93" s="15">
+        <v>38</v>
+      </c>
+      <c r="G93" s="26">
         <v>0.89759299999999997</v>
       </c>
-      <c r="H93" s="8">
+      <c r="H93" s="23">
         <v>0.93925899999999996</v>
       </c>
-      <c r="I93" s="10">
+      <c r="I93" s="8">
         <v>35000</v>
       </c>
-      <c r="J93" s="10">
+      <c r="J93" s="8">
         <v>25000</v>
       </c>
-      <c r="K93" s="10">
+      <c r="K93" s="8">
         <v>60000</v>
       </c>
-      <c r="L93" s="16">
+      <c r="L93" s="12">
         <v>60000</v>
       </c>
     </row>
     <row r="94" spans="1:12" ht="14" x14ac:dyDescent="0.15">
-      <c r="A94" s="14">
+      <c r="A94" s="11">
         <v>20260302863</v>
       </c>
-      <c r="B94" s="13">
+      <c r="B94" s="10">
         <v>46083</v>
       </c>
       <c r="C94" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="D94" s="17"/>
-      <c r="E94" s="18"/>
+      <c r="D94" s="15"/>
+      <c r="E94" s="16"/>
       <c r="F94" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="G94" s="15">
+        <v>38</v>
+      </c>
+      <c r="G94" s="26">
         <v>0.93209500000000001</v>
       </c>
-      <c r="H94" s="8">
+      <c r="H94" s="23">
         <v>0.97376200000000002</v>
       </c>
-      <c r="I94" s="10">
+      <c r="I94" s="8">
         <v>35000</v>
       </c>
-      <c r="J94" s="10">
+      <c r="J94" s="8">
         <v>51000</v>
       </c>
-      <c r="K94" s="10">
+      <c r="K94" s="8">
         <v>86000</v>
       </c>
-      <c r="L94" s="16">
+      <c r="L94" s="12">
         <v>86000</v>
       </c>
     </row>
     <row r="95" spans="1:12" ht="14" x14ac:dyDescent="0.15">
-      <c r="A95" s="14">
+      <c r="A95" s="11">
         <v>20260302864</v>
       </c>
-      <c r="B95" s="13">
+      <c r="B95" s="10">
         <v>46084</v>
       </c>
       <c r="C95" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="D95" s="17"/>
-      <c r="E95" s="18"/>
+      <c r="D95" s="15"/>
+      <c r="E95" s="16"/>
       <c r="F95" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="G95" s="15">
+        <v>38</v>
+      </c>
+      <c r="G95" s="26">
         <v>0.97517399999999999</v>
       </c>
-      <c r="H95" s="8">
+      <c r="H95" s="23">
         <v>5.8507000000000003E-2</v>
       </c>
-      <c r="I95" s="10">
+      <c r="I95" s="8">
         <v>70000</v>
       </c>
-      <c r="J95" s="10">
+      <c r="J95" s="8">
         <v>20000</v>
       </c>
-      <c r="K95" s="10">
+      <c r="K95" s="8">
         <v>90000</v>
       </c>
-      <c r="L95" s="16">
+      <c r="L95" s="12">
         <v>90000</v>
       </c>
     </row>
     <row r="96" spans="1:12" ht="14" x14ac:dyDescent="0.15">
-      <c r="A96" s="14">
+      <c r="A96" s="11">
         <v>20260302865</v>
       </c>
-      <c r="B96" s="13">
+      <c r="B96" s="10">
         <v>46084</v>
       </c>
       <c r="C96" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="D96" s="17"/>
-      <c r="E96" s="18"/>
+      <c r="D96" s="15"/>
+      <c r="E96" s="16"/>
       <c r="F96" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="G96" s="15">
+        <v>38</v>
+      </c>
+      <c r="G96" s="26">
         <v>0.97772000000000003</v>
       </c>
-      <c r="H96" s="8">
+      <c r="H96" s="23">
         <v>1.9387000000000001E-2</v>
       </c>
-      <c r="I96" s="10">
+      <c r="I96" s="8">
         <v>35000</v>
       </c>
-      <c r="J96" s="11">
+      <c r="J96" s="9">
         <v>0</v>
       </c>
-      <c r="K96" s="10">
+      <c r="K96" s="8">
         <v>35000</v>
       </c>
-      <c r="L96" s="16">
+      <c r="L96" s="12">
         <v>35000</v>
       </c>
     </row>
     <row r="97" spans="1:12" ht="14" x14ac:dyDescent="0.15">
-      <c r="A97" s="14">
+      <c r="A97" s="11">
         <v>20260302866</v>
       </c>
-      <c r="B97" s="13">
+      <c r="B97" s="10">
         <v>46084</v>
       </c>
       <c r="C97" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="D97" s="17" t="s">
-        <v>45</v>
-      </c>
-      <c r="E97" s="18"/>
+      <c r="D97" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="E97" s="16"/>
       <c r="F97" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="G97" s="15">
+        <v>38</v>
+      </c>
+      <c r="G97" s="26">
         <v>0.99612299999999998</v>
       </c>
-      <c r="H97" s="8">
+      <c r="H97" s="23">
         <v>3.3946999999999998E-2</v>
       </c>
-      <c r="I97" s="10">
+      <c r="I97" s="8">
         <v>31500</v>
       </c>
-      <c r="J97" s="11">
+      <c r="J97" s="9">
         <v>0</v>
       </c>
-      <c r="K97" s="10">
+      <c r="K97" s="8">
         <v>31500</v>
       </c>
-      <c r="L97" s="16">
+      <c r="L97" s="12">
         <v>31500</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:L97" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <filterColumn colId="3" showButton="0"/>
+  </autoFilter>
   <mergeCells count="97">
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="D2:E2"/>
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="D4:E4"/>
-    <mergeCell ref="D5:E5"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="D7:E7"/>
-    <mergeCell ref="D8:E8"/>
-    <mergeCell ref="D9:E9"/>
-    <mergeCell ref="D10:E10"/>
-    <mergeCell ref="D11:E11"/>
-    <mergeCell ref="D12:E12"/>
-    <mergeCell ref="D13:E13"/>
-    <mergeCell ref="D19:E19"/>
-    <mergeCell ref="D20:E20"/>
-    <mergeCell ref="D21:E21"/>
-    <mergeCell ref="D22:E22"/>
-    <mergeCell ref="D14:E14"/>
-    <mergeCell ref="D15:E15"/>
-    <mergeCell ref="D16:E16"/>
-    <mergeCell ref="D17:E17"/>
-    <mergeCell ref="D18:E18"/>
-    <mergeCell ref="D23:E23"/>
-    <mergeCell ref="D24:E24"/>
-    <mergeCell ref="D25:E25"/>
-    <mergeCell ref="D26:E26"/>
-    <mergeCell ref="D27:E27"/>
-    <mergeCell ref="D28:E28"/>
-    <mergeCell ref="D29:E29"/>
-    <mergeCell ref="D30:E30"/>
-    <mergeCell ref="D31:E31"/>
-    <mergeCell ref="D32:E32"/>
-    <mergeCell ref="D33:E33"/>
-    <mergeCell ref="D34:E34"/>
-    <mergeCell ref="D35:E35"/>
-    <mergeCell ref="D36:E36"/>
-    <mergeCell ref="D37:E37"/>
+    <mergeCell ref="D97:E97"/>
+    <mergeCell ref="D92:E92"/>
+    <mergeCell ref="D93:E93"/>
+    <mergeCell ref="D94:E94"/>
+    <mergeCell ref="D95:E95"/>
+    <mergeCell ref="D96:E96"/>
+    <mergeCell ref="D87:E87"/>
+    <mergeCell ref="D88:E88"/>
+    <mergeCell ref="D89:E89"/>
+    <mergeCell ref="D90:E90"/>
+    <mergeCell ref="D91:E91"/>
+    <mergeCell ref="D82:E82"/>
+    <mergeCell ref="D83:E83"/>
+    <mergeCell ref="D84:E84"/>
+    <mergeCell ref="D85:E85"/>
+    <mergeCell ref="D86:E86"/>
+    <mergeCell ref="D77:E77"/>
+    <mergeCell ref="D78:E78"/>
+    <mergeCell ref="D79:E79"/>
+    <mergeCell ref="D80:E80"/>
+    <mergeCell ref="D81:E81"/>
+    <mergeCell ref="D72:E72"/>
+    <mergeCell ref="D73:E73"/>
+    <mergeCell ref="D74:E74"/>
+    <mergeCell ref="D75:E75"/>
+    <mergeCell ref="D76:E76"/>
+    <mergeCell ref="D67:E67"/>
+    <mergeCell ref="D68:E68"/>
+    <mergeCell ref="D69:E69"/>
+    <mergeCell ref="D70:E70"/>
+    <mergeCell ref="D71:E71"/>
+    <mergeCell ref="D62:E62"/>
+    <mergeCell ref="D63:E63"/>
+    <mergeCell ref="D64:E64"/>
+    <mergeCell ref="D65:E65"/>
+    <mergeCell ref="D66:E66"/>
+    <mergeCell ref="D57:E57"/>
+    <mergeCell ref="D58:E58"/>
+    <mergeCell ref="D59:E59"/>
+    <mergeCell ref="D60:E60"/>
+    <mergeCell ref="D61:E61"/>
+    <mergeCell ref="D52:E52"/>
+    <mergeCell ref="D53:E53"/>
+    <mergeCell ref="D54:E54"/>
+    <mergeCell ref="D55:E55"/>
+    <mergeCell ref="D56:E56"/>
+    <mergeCell ref="D47:E47"/>
+    <mergeCell ref="D48:E48"/>
+    <mergeCell ref="D49:E49"/>
+    <mergeCell ref="D50:E50"/>
+    <mergeCell ref="D51:E51"/>
     <mergeCell ref="D43:E43"/>
     <mergeCell ref="D44:E44"/>
     <mergeCell ref="D45:E45"/>
@@ -4403,57 +4416,43 @@
     <mergeCell ref="D40:E40"/>
     <mergeCell ref="D41:E41"/>
     <mergeCell ref="D42:E42"/>
-    <mergeCell ref="D47:E47"/>
-    <mergeCell ref="D48:E48"/>
-    <mergeCell ref="D49:E49"/>
-    <mergeCell ref="D50:E50"/>
-    <mergeCell ref="D51:E51"/>
-    <mergeCell ref="D52:E52"/>
-    <mergeCell ref="D53:E53"/>
-    <mergeCell ref="D54:E54"/>
-    <mergeCell ref="D55:E55"/>
-    <mergeCell ref="D56:E56"/>
-    <mergeCell ref="D57:E57"/>
-    <mergeCell ref="D58:E58"/>
-    <mergeCell ref="D59:E59"/>
-    <mergeCell ref="D60:E60"/>
-    <mergeCell ref="D61:E61"/>
-    <mergeCell ref="D62:E62"/>
-    <mergeCell ref="D63:E63"/>
-    <mergeCell ref="D64:E64"/>
-    <mergeCell ref="D65:E65"/>
-    <mergeCell ref="D66:E66"/>
-    <mergeCell ref="D67:E67"/>
-    <mergeCell ref="D68:E68"/>
-    <mergeCell ref="D69:E69"/>
-    <mergeCell ref="D70:E70"/>
-    <mergeCell ref="D71:E71"/>
-    <mergeCell ref="D72:E72"/>
-    <mergeCell ref="D73:E73"/>
-    <mergeCell ref="D74:E74"/>
-    <mergeCell ref="D75:E75"/>
-    <mergeCell ref="D76:E76"/>
-    <mergeCell ref="D77:E77"/>
-    <mergeCell ref="D78:E78"/>
-    <mergeCell ref="D79:E79"/>
-    <mergeCell ref="D80:E80"/>
-    <mergeCell ref="D81:E81"/>
-    <mergeCell ref="D82:E82"/>
-    <mergeCell ref="D83:E83"/>
-    <mergeCell ref="D84:E84"/>
-    <mergeCell ref="D85:E85"/>
-    <mergeCell ref="D86:E86"/>
-    <mergeCell ref="D87:E87"/>
-    <mergeCell ref="D88:E88"/>
-    <mergeCell ref="D89:E89"/>
-    <mergeCell ref="D90:E90"/>
-    <mergeCell ref="D91:E91"/>
-    <mergeCell ref="D97:E97"/>
-    <mergeCell ref="D92:E92"/>
-    <mergeCell ref="D93:E93"/>
-    <mergeCell ref="D94:E94"/>
-    <mergeCell ref="D95:E95"/>
-    <mergeCell ref="D96:E96"/>
+    <mergeCell ref="D33:E33"/>
+    <mergeCell ref="D34:E34"/>
+    <mergeCell ref="D35:E35"/>
+    <mergeCell ref="D36:E36"/>
+    <mergeCell ref="D37:E37"/>
+    <mergeCell ref="D28:E28"/>
+    <mergeCell ref="D29:E29"/>
+    <mergeCell ref="D30:E30"/>
+    <mergeCell ref="D31:E31"/>
+    <mergeCell ref="D32:E32"/>
+    <mergeCell ref="D23:E23"/>
+    <mergeCell ref="D24:E24"/>
+    <mergeCell ref="D25:E25"/>
+    <mergeCell ref="D26:E26"/>
+    <mergeCell ref="D27:E27"/>
+    <mergeCell ref="D21:E21"/>
+    <mergeCell ref="D22:E22"/>
+    <mergeCell ref="D14:E14"/>
+    <mergeCell ref="D15:E15"/>
+    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="D17:E17"/>
+    <mergeCell ref="D18:E18"/>
+    <mergeCell ref="D11:E11"/>
+    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="D13:E13"/>
+    <mergeCell ref="D19:E19"/>
+    <mergeCell ref="D20:E20"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="D9:E9"/>
+    <mergeCell ref="D10:E10"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="D2:E2"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="D4:E4"/>
+    <mergeCell ref="D5:E5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
